--- a/equip_rca/Equip cohort validation - before vs after.xlsx
+++ b/equip_rca/Equip cohort validation - before vs after.xlsx
@@ -632,28 +632,28 @@
         <v>7920</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>93.90000000000001</v>
+        <v>93.89</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>110.32</v>
+        <v>110.31</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>135.47</v>
+        <v>135.46</v>
       </c>
       <c r="F7" s="9" t="n">
-        <v>152.38</v>
+        <v>152.37</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>167.16</v>
+        <v>167.15</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>180.4</v>
+        <v>180.38</v>
       </c>
       <c r="I7" s="9" t="n">
-        <v>196.82</v>
+        <v>196.81</v>
       </c>
       <c r="J7" s="9" t="n">
-        <v>209.83</v>
+        <v>209.82</v>
       </c>
       <c r="K7" s="9" t="n">
         <v>225.48</v>
@@ -675,7 +675,7 @@
         <v>7704</v>
       </c>
       <c r="C8" s="9" t="n">
-        <v>94.90000000000001</v>
+        <v>94.87</v>
       </c>
       <c r="D8" s="9" t="n">
         <v>117.71</v>
@@ -718,25 +718,25 @@
         <v>11977</v>
       </c>
       <c r="C9" s="9" t="n">
-        <v>100.19</v>
+        <v>100.17</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>116.3</v>
+        <v>116.27</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>134.58</v>
+        <v>134.55</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>153.47</v>
+        <v>153.43</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>170.72</v>
+        <v>170.69</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>184.2</v>
+        <v>184.17</v>
       </c>
       <c r="I9" s="9" t="n">
-        <v>202.59</v>
+        <v>202.58</v>
       </c>
       <c r="J9" s="9" t="n">
         <v>212.91</v>
@@ -761,28 +761,28 @@
         <v>9094</v>
       </c>
       <c r="C10" s="9" t="n">
-        <v>97.88</v>
+        <v>97.87</v>
       </c>
       <c r="D10" s="9" t="n">
-        <v>113.25</v>
+        <v>113.23</v>
       </c>
       <c r="E10" s="9" t="n">
-        <v>128.42</v>
+        <v>128.4</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>147.94</v>
+        <v>147.92</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>161.57</v>
+        <v>161.55</v>
       </c>
       <c r="H10" s="9" t="n">
         <v>177.74</v>
       </c>
       <c r="I10" s="9" t="n">
-        <v>188.42</v>
+        <v>188.41</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>199.34</v>
+        <v>199.32</v>
       </c>
       <c r="K10" s="9" t="n">
         <v>209.58</v>
@@ -802,16 +802,16 @@
         <v>12292</v>
       </c>
       <c r="C11" s="9" t="n">
-        <v>93.06999999999999</v>
+        <v>93.06</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>107.76</v>
+        <v>107.75</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>128.59</v>
+        <v>128.58</v>
       </c>
       <c r="F11" s="9" t="n">
-        <v>149.2</v>
+        <v>149.19</v>
       </c>
       <c r="G11" s="9" t="n">
         <v>168.23</v>
@@ -820,7 +820,7 @@
         <v>178.73</v>
       </c>
       <c r="I11" s="9" t="n">
-        <v>192.62</v>
+        <v>192.61</v>
       </c>
       <c r="J11" s="9" t="n">
         <v>202.79</v>
@@ -841,16 +841,16 @@
         <v>11886</v>
       </c>
       <c r="C12" s="9" t="n">
-        <v>95.7</v>
+        <v>95.69</v>
       </c>
       <c r="D12" s="9" t="n">
-        <v>115.9</v>
+        <v>115.88</v>
       </c>
       <c r="E12" s="9" t="n">
-        <v>135.95</v>
+        <v>135.94</v>
       </c>
       <c r="F12" s="9" t="n">
-        <v>159.77</v>
+        <v>159.76</v>
       </c>
       <c r="G12" s="9" t="n">
         <v>173.05</v>
@@ -878,7 +878,7 @@
         <v>11220</v>
       </c>
       <c r="C13" s="9" t="n">
-        <v>97.45999999999999</v>
+        <v>97.45</v>
       </c>
       <c r="D13" s="9" t="n">
         <v>118.33</v>
@@ -913,13 +913,13 @@
         <v>11165</v>
       </c>
       <c r="C14" s="9" t="n">
-        <v>97.93000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="D14" s="9" t="n">
-        <v>124.66</v>
+        <v>124.63</v>
       </c>
       <c r="E14" s="9" t="n">
-        <v>143.08</v>
+        <v>143.07</v>
       </c>
       <c r="F14" s="9" t="n">
         <v>163.05</v>
@@ -946,13 +946,13 @@
         <v>15938</v>
       </c>
       <c r="C15" s="9" t="n">
-        <v>98.73999999999999</v>
+        <v>98.72</v>
       </c>
       <c r="D15" s="9" t="n">
         <v>115.81</v>
       </c>
       <c r="E15" s="9" t="n">
-        <v>135.65</v>
+        <v>135.64</v>
       </c>
       <c r="F15" s="9" t="n">
         <v>156.31</v>
@@ -977,10 +977,10 @@
         <v>8985</v>
       </c>
       <c r="C16" s="9" t="n">
-        <v>98.68000000000001</v>
+        <v>98.64</v>
       </c>
       <c r="D16" s="9" t="n">
-        <v>118.12</v>
+        <v>118.09</v>
       </c>
       <c r="E16" s="9" t="n">
         <v>137.9</v>
@@ -1006,10 +1006,10 @@
         <v>10850</v>
       </c>
       <c r="C17" s="9" t="n">
-        <v>100.67</v>
+        <v>100.63</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>120.02</v>
+        <v>120.01</v>
       </c>
       <c r="E17" s="9" t="n">
         <v>139.16</v>
@@ -1107,37 +1107,37 @@
         <v>7945</v>
       </c>
       <c r="C21" s="9" t="n">
-        <v>92.88980239144014</v>
+        <v>92.88980239</v>
       </c>
       <c r="D21" s="9" t="n">
-        <v>109.2581913152916</v>
+        <v>109.2581913</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>134.4189804908738</v>
+        <v>134.4189805</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v>151.2283310258015</v>
+        <v>151.228331</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>165.9129616110752</v>
+        <v>165.9129616</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>179.0687212083062</v>
+        <v>179.0687212</v>
       </c>
       <c r="I21" s="9" t="n">
-        <v>195.4255909376958</v>
+        <v>195.4255909</v>
       </c>
       <c r="J21" s="9" t="n">
-        <v>208.4516224040268</v>
+        <v>208.4516224</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>224.0902353681552</v>
+        <v>224.0902354</v>
       </c>
       <c r="L21" s="9" t="n">
-        <v>234.4451642542471</v>
+        <v>234.4451643</v>
       </c>
       <c r="M21" s="9" t="n">
-        <v>244.7189037130262</v>
+        <v>244.7189037</v>
       </c>
     </row>
     <row r="22">
@@ -1150,34 +1150,34 @@
         <v>7757</v>
       </c>
       <c r="C22" s="9" t="n">
-        <v>93.58246358128143</v>
+        <v>93.58246358</v>
       </c>
       <c r="D22" s="9" t="n">
-        <v>116.2646371019725</v>
+        <v>116.2646371</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>133.8571690086374</v>
+        <v>133.857169</v>
       </c>
       <c r="F22" s="9" t="n">
-        <v>151.5381603712776</v>
+        <v>151.5381604</v>
       </c>
       <c r="G22" s="9" t="n">
-        <v>165.8278483949981</v>
+        <v>165.8278484</v>
       </c>
       <c r="H22" s="9" t="n">
-        <v>181.5058398865541</v>
+        <v>181.5058399</v>
       </c>
       <c r="I22" s="9" t="n">
-        <v>195.7418770143097</v>
+        <v>195.741877</v>
       </c>
       <c r="J22" s="9" t="n">
-        <v>210.602847750419</v>
+        <v>210.6028478</v>
       </c>
       <c r="K22" s="9" t="n">
-        <v>220.5761570194663</v>
+        <v>220.576157</v>
       </c>
       <c r="L22" s="9" t="n">
-        <v>232.4624223282197</v>
+        <v>232.4624223</v>
       </c>
       <c r="M22" s="9" t="n"/>
     </row>
@@ -1191,31 +1191,31 @@
         <v>11950</v>
       </c>
       <c r="C23" s="9" t="n">
-        <v>99.84738912133761</v>
+        <v>99.84738912</v>
       </c>
       <c r="D23" s="9" t="n">
-        <v>115.9622242677812</v>
+        <v>115.9622243</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>134.1972309623419</v>
+        <v>134.197231</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>153.2141514644341</v>
+        <v>153.2141515</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>170.4690359832626</v>
+        <v>170.469036</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>183.8624058577396</v>
+        <v>183.8624059</v>
       </c>
       <c r="I23" s="9" t="n">
-        <v>202.3255531380745</v>
+        <v>202.3255531</v>
       </c>
       <c r="J23" s="9" t="n">
-        <v>212.7203707112963</v>
+        <v>212.7203707</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>224.8946527196645</v>
+        <v>224.8946527</v>
       </c>
       <c r="L23" s="9" t="n"/>
       <c r="M23" s="9" t="n"/>
@@ -1230,28 +1230,28 @@
         <v>9056</v>
       </c>
       <c r="C24" s="9" t="n">
-        <v>97.87320229681924</v>
+        <v>97.8732023</v>
       </c>
       <c r="D24" s="9" t="n">
-        <v>113.3810479240277</v>
+        <v>113.3810479</v>
       </c>
       <c r="E24" s="9" t="n">
-        <v>128.7157906360419</v>
+        <v>128.7157906</v>
       </c>
       <c r="F24" s="9" t="n">
-        <v>148.340142446996</v>
+        <v>148.3401424</v>
       </c>
       <c r="G24" s="9" t="n">
-        <v>162.0841409010597</v>
+        <v>162.0841409</v>
       </c>
       <c r="H24" s="9" t="n">
-        <v>178.4198332597169</v>
+        <v>178.4198333</v>
       </c>
       <c r="I24" s="9" t="n">
-        <v>189.0977120141339</v>
+        <v>189.097712</v>
       </c>
       <c r="J24" s="9" t="n">
-        <v>200.147360865724</v>
+        <v>200.1473609</v>
       </c>
       <c r="K24" s="9" t="n"/>
       <c r="L24" s="9" t="n"/>
@@ -1267,25 +1267,25 @@
         <v>12255</v>
       </c>
       <c r="C25" s="9" t="n">
-        <v>92.98071889024696</v>
+        <v>92.98071889000001</v>
       </c>
       <c r="D25" s="9" t="n">
-        <v>107.8431676866566</v>
+        <v>107.8431677</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>128.9879110567099</v>
+        <v>128.9879111</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>149.8797813137481</v>
+        <v>149.8797813</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>169.1570199918388</v>
+        <v>169.15702</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>180.0422284781709</v>
+        <v>180.0422285</v>
       </c>
       <c r="I25" s="9" t="n">
-        <v>194.0367311301497</v>
+        <v>194.0367311</v>
       </c>
       <c r="J25" s="9" t="n"/>
       <c r="K25" s="9" t="n"/>
@@ -1302,22 +1302,22 @@
         <v>11963</v>
       </c>
       <c r="C26" s="9" t="n">
-        <v>95.05778400066698</v>
+        <v>95.057784</v>
       </c>
       <c r="D26" s="9" t="n">
-        <v>115.2037139513485</v>
+        <v>115.203714</v>
       </c>
       <c r="E26" s="9" t="n">
-        <v>135.3271879963206</v>
+        <v>135.327188</v>
       </c>
       <c r="F26" s="9" t="n">
-        <v>159.0452428320644</v>
+        <v>159.0452428</v>
       </c>
       <c r="G26" s="9" t="n">
-        <v>172.4782328847267</v>
+        <v>172.4782329</v>
       </c>
       <c r="H26" s="9" t="n">
-        <v>185.405334782244</v>
+        <v>185.4053348</v>
       </c>
       <c r="I26" s="9" t="n"/>
       <c r="J26" s="9" t="n"/>
@@ -1335,19 +1335,19 @@
         <v>11207</v>
       </c>
       <c r="C27" s="9" t="n">
-        <v>98.34834746140596</v>
+        <v>98.34834746</v>
       </c>
       <c r="D27" s="9" t="n">
-        <v>120.0648906933147</v>
+        <v>120.0648907</v>
       </c>
       <c r="E27" s="9" t="n">
-        <v>146.8181056482539</v>
+        <v>146.8181056</v>
       </c>
       <c r="F27" s="9" t="n">
-        <v>166.452576068527</v>
+        <v>166.4525761</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>182.7494565896299</v>
+        <v>182.7494566</v>
       </c>
       <c r="H27" s="9" t="n"/>
       <c r="I27" s="9" t="n"/>
@@ -1366,16 +1366,16 @@
         <v>11145</v>
       </c>
       <c r="C28" s="9" t="n">
-        <v>98.49222969941405</v>
+        <v>98.4922297</v>
       </c>
       <c r="D28" s="9" t="n">
-        <v>125.6861327949728</v>
+        <v>125.6861328</v>
       </c>
       <c r="E28" s="9" t="n">
-        <v>143.6859282189298</v>
+        <v>143.6859282</v>
       </c>
       <c r="F28" s="9" t="n">
-        <v>163.8259416778801</v>
+        <v>163.8259417</v>
       </c>
       <c r="G28" s="9" t="n"/>
       <c r="H28" s="9" t="n"/>
@@ -1395,13 +1395,13 @@
         <v>15934</v>
       </c>
       <c r="C29" s="9" t="n">
-        <v>99.61277143215585</v>
+        <v>99.61277143</v>
       </c>
       <c r="D29" s="9" t="n">
-        <v>117.2355064641631</v>
+        <v>117.2355065</v>
       </c>
       <c r="E29" s="9" t="n">
-        <v>139.2069336011021</v>
+        <v>139.2069336</v>
       </c>
       <c r="F29" s="9" t="n"/>
       <c r="G29" s="9" t="n"/>
@@ -1422,10 +1422,10 @@
         <v>8978</v>
       </c>
       <c r="C30" s="9" t="n">
-        <v>99.66080530184823</v>
+        <v>99.66080530000001</v>
       </c>
       <c r="D30" s="9" t="n">
-        <v>120.0241412341272</v>
+        <v>120.0241412</v>
       </c>
       <c r="E30" s="9" t="n"/>
       <c r="F30" s="9" t="n"/>
@@ -1447,7 +1447,7 @@
         <v>10832</v>
       </c>
       <c r="C31" s="9" t="n">
-        <v>101.9177206425389</v>
+        <v>101.9177206</v>
       </c>
       <c r="D31" s="9" t="n"/>
       <c r="E31" s="9" t="n"/>
@@ -2279,7 +2279,7 @@
         <v>111.61</v>
       </c>
       <c r="E52" s="9" t="n">
-        <v>123.03</v>
+        <v>123.02</v>
       </c>
       <c r="F52" s="9" t="n">
         <v>134.36</v>
@@ -2316,22 +2316,22 @@
         <v>6704</v>
       </c>
       <c r="C53" s="9" t="n">
-        <v>95.98</v>
+        <v>95.95</v>
       </c>
       <c r="D53" s="9" t="n">
-        <v>107.95</v>
+        <v>107.91</v>
       </c>
       <c r="E53" s="9" t="n">
-        <v>119.69</v>
+        <v>119.65</v>
       </c>
       <c r="F53" s="9" t="n">
-        <v>130.12</v>
+        <v>130.08</v>
       </c>
       <c r="G53" s="9" t="n">
-        <v>141.84</v>
+        <v>141.8</v>
       </c>
       <c r="H53" s="9" t="n">
-        <v>152</v>
+        <v>151.96</v>
       </c>
       <c r="I53" s="9" t="n">
         <v>164.51</v>
@@ -2346,7 +2346,7 @@
         <v>188.49</v>
       </c>
       <c r="M53" s="9" t="n">
-        <v>195.46</v>
+        <v>195.45</v>
       </c>
     </row>
     <row r="54">
@@ -2362,16 +2362,16 @@
         <v>95.42</v>
       </c>
       <c r="D54" s="9" t="n">
-        <v>105.79</v>
+        <v>105.77</v>
       </c>
       <c r="E54" s="9" t="n">
-        <v>116.37</v>
+        <v>116.35</v>
       </c>
       <c r="F54" s="9" t="n">
-        <v>127.44</v>
+        <v>127.42</v>
       </c>
       <c r="G54" s="9" t="n">
-        <v>137.3</v>
+        <v>137.28</v>
       </c>
       <c r="H54" s="9" t="n">
         <v>149.57</v>
@@ -2448,7 +2448,7 @@
         <v>119.05</v>
       </c>
       <c r="F56" s="9" t="n">
-        <v>134.55</v>
+        <v>134.54</v>
       </c>
       <c r="G56" s="9" t="n">
         <v>143.49</v>
@@ -2511,10 +2511,10 @@
         <v>6687</v>
       </c>
       <c r="C58" s="9" t="n">
-        <v>94.26000000000001</v>
+        <v>94.23999999999999</v>
       </c>
       <c r="D58" s="9" t="n">
-        <v>112.99</v>
+        <v>112.97</v>
       </c>
       <c r="E58" s="9" t="n">
         <v>125.36</v>
@@ -2575,10 +2575,10 @@
         <v>5526</v>
       </c>
       <c r="C60" s="9" t="n">
-        <v>94.92</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="D60" s="9" t="n">
-        <v>105.36</v>
+        <v>105.35</v>
       </c>
       <c r="E60" s="9" t="n">
         <v>117.13</v>
@@ -2705,37 +2705,37 @@
         <v>4807</v>
       </c>
       <c r="C65" s="9" t="n">
-        <v>90.62231121281255</v>
+        <v>90.62231121000001</v>
       </c>
       <c r="D65" s="9" t="n">
-        <v>97.2652818805887</v>
+        <v>97.26528188</v>
       </c>
       <c r="E65" s="9" t="n">
-        <v>107.2642812564989</v>
+        <v>107.2642813</v>
       </c>
       <c r="F65" s="9" t="n">
-        <v>112.0940420220491</v>
+        <v>112.094042</v>
       </c>
       <c r="G65" s="9" t="n">
-        <v>116.1993030996443</v>
+        <v>116.1993031</v>
       </c>
       <c r="H65" s="9" t="n">
-        <v>120.2562221759913</v>
+        <v>120.2562222</v>
       </c>
       <c r="I65" s="9" t="n">
-        <v>123.9518036197192</v>
+        <v>123.9518036</v>
       </c>
       <c r="J65" s="9" t="n">
-        <v>126.8641460370273</v>
+        <v>126.864146</v>
       </c>
       <c r="K65" s="9" t="n">
-        <v>130.5286810900749</v>
+        <v>130.5286811</v>
       </c>
       <c r="L65" s="9" t="n">
-        <v>132.6220074890764</v>
+        <v>132.6220075</v>
       </c>
       <c r="M65" s="9" t="n">
-        <v>134.7860619929249</v>
+        <v>134.786062</v>
       </c>
     </row>
     <row r="66">
@@ -2748,34 +2748,34 @@
         <v>4678</v>
       </c>
       <c r="C66" s="9" t="n">
-        <v>90.42786447199624</v>
+        <v>90.42786447</v>
       </c>
       <c r="D66" s="9" t="n">
-        <v>102.6423343309103</v>
+        <v>102.6423343</v>
       </c>
       <c r="E66" s="9" t="n">
-        <v>109.4862291577594</v>
+        <v>109.4862292</v>
       </c>
       <c r="F66" s="9" t="n">
-        <v>114.9926891834114</v>
+        <v>114.9926892</v>
       </c>
       <c r="G66" s="9" t="n">
-        <v>119.9567464728513</v>
+        <v>119.9567465</v>
       </c>
       <c r="H66" s="9" t="n">
-        <v>123.8893758016243</v>
+        <v>123.8893758</v>
       </c>
       <c r="I66" s="9" t="n">
-        <v>126.6275780247966</v>
+        <v>126.627578</v>
       </c>
       <c r="J66" s="9" t="n">
-        <v>130.7604382214618</v>
+        <v>130.7604382</v>
       </c>
       <c r="K66" s="9" t="n">
-        <v>132.670275758871</v>
+        <v>132.6702758</v>
       </c>
       <c r="L66" s="9" t="n">
-        <v>135.4952415562203</v>
+        <v>135.4952416</v>
       </c>
       <c r="M66" s="9" t="n"/>
     </row>
@@ -2789,31 +2789,31 @@
         <v>6676</v>
       </c>
       <c r="C67" s="9" t="n">
-        <v>94.18704613540861</v>
+        <v>94.18704614000001</v>
       </c>
       <c r="D67" s="9" t="n">
-        <v>102.9185230677034</v>
+        <v>102.9185231</v>
       </c>
       <c r="E67" s="9" t="n">
-        <v>109.2991087477514</v>
+        <v>109.2991087</v>
       </c>
       <c r="F67" s="9" t="n">
-        <v>114.8393214499683</v>
+        <v>114.8393214</v>
       </c>
       <c r="G67" s="9" t="n">
-        <v>120.1615128819635</v>
+        <v>120.1615129</v>
       </c>
       <c r="H67" s="9" t="n">
-        <v>124.1814799280989</v>
+        <v>124.1814799</v>
       </c>
       <c r="I67" s="9" t="n">
-        <v>129.1226647693211</v>
+        <v>129.1226648</v>
       </c>
       <c r="J67" s="9" t="n">
-        <v>131.4143693828622</v>
+        <v>131.4143694</v>
       </c>
       <c r="K67" s="9" t="n">
-        <v>134.7352007189916</v>
+        <v>134.7352007</v>
       </c>
       <c r="L67" s="9" t="n"/>
       <c r="M67" s="9" t="n"/>
@@ -2828,28 +2828,28 @@
         <v>5940</v>
       </c>
       <c r="C68" s="9" t="n">
-        <v>94.74573905723807</v>
+        <v>94.74573906000001</v>
       </c>
       <c r="D68" s="9" t="n">
-        <v>100.5904562289552</v>
+        <v>100.5904562</v>
       </c>
       <c r="E68" s="9" t="n">
-        <v>106.0014343434333</v>
+        <v>106.0014343</v>
       </c>
       <c r="F68" s="9" t="n">
-        <v>110.5965656565646</v>
+        <v>110.5965657</v>
       </c>
       <c r="G68" s="9" t="n">
-        <v>114.1523181818172</v>
+        <v>114.1523182</v>
       </c>
       <c r="H68" s="9" t="n">
-        <v>118.4902828282818</v>
+        <v>118.4902828</v>
       </c>
       <c r="I68" s="9" t="n">
-        <v>120.463664983164</v>
+        <v>120.463665</v>
       </c>
       <c r="J68" s="9" t="n">
-        <v>123.0067542087532</v>
+        <v>123.0067542</v>
       </c>
       <c r="K68" s="9" t="n"/>
       <c r="L68" s="9" t="n"/>
@@ -2865,25 +2865,25 @@
         <v>6902</v>
       </c>
       <c r="C69" s="9" t="n">
-        <v>89.6252419588498</v>
+        <v>89.62524196</v>
       </c>
       <c r="D69" s="9" t="n">
-        <v>96.15848884381069</v>
+        <v>96.15848884</v>
       </c>
       <c r="E69" s="9" t="n">
-        <v>103.0960286873343</v>
+        <v>103.0960287</v>
       </c>
       <c r="F69" s="9" t="n">
-        <v>108.1027644161086</v>
+        <v>108.1027644</v>
       </c>
       <c r="G69" s="9" t="n">
-        <v>114.1196841495192</v>
+        <v>114.1196841</v>
       </c>
       <c r="H69" s="9" t="n">
-        <v>117.2070718632254</v>
+        <v>117.2070719</v>
       </c>
       <c r="I69" s="9" t="n">
-        <v>120.2618849608782</v>
+        <v>120.261885</v>
       </c>
       <c r="J69" s="9" t="n"/>
       <c r="K69" s="9" t="n"/>
@@ -2900,22 +2900,22 @@
         <v>6761</v>
       </c>
       <c r="C70" s="9" t="n">
-        <v>92.62598580091441</v>
+        <v>92.6259858</v>
       </c>
       <c r="D70" s="9" t="n">
-        <v>100.2615840851919</v>
+        <v>100.2615841</v>
       </c>
       <c r="E70" s="9" t="n">
-        <v>107.6074619139155</v>
+        <v>107.6074619</v>
       </c>
       <c r="F70" s="9" t="n">
-        <v>115.0565256618818</v>
+        <v>115.0565257</v>
       </c>
       <c r="G70" s="9" t="n">
-        <v>118.9863378198466</v>
+        <v>118.9863378</v>
       </c>
       <c r="H70" s="9" t="n">
-        <v>123.1475654488955</v>
+        <v>123.1475654</v>
       </c>
       <c r="I70" s="9" t="n"/>
       <c r="J70" s="9" t="n"/>
@@ -2933,19 +2933,19 @@
         <v>6599</v>
       </c>
       <c r="C71" s="9" t="n">
-        <v>95.38632520078555</v>
+        <v>95.3863252</v>
       </c>
       <c r="D71" s="9" t="n">
-        <v>104.7795969086201</v>
+        <v>104.7795969</v>
       </c>
       <c r="E71" s="9" t="n">
-        <v>116.0663858160303</v>
+        <v>116.0663858</v>
       </c>
       <c r="F71" s="9" t="n">
-        <v>123.6721094105144</v>
+        <v>123.6721094</v>
       </c>
       <c r="G71" s="9" t="n">
-        <v>130.7052644340028</v>
+        <v>130.7052644</v>
       </c>
       <c r="H71" s="9" t="n"/>
       <c r="I71" s="9" t="n"/>
@@ -2964,16 +2964,16 @@
         <v>6637</v>
       </c>
       <c r="C72" s="9" t="n">
-        <v>94.12089950278373</v>
+        <v>94.12089949999999</v>
       </c>
       <c r="D72" s="9" t="n">
-        <v>105.6088157299948</v>
+        <v>105.6088157</v>
       </c>
       <c r="E72" s="9" t="n">
-        <v>112.0478303450318</v>
+        <v>112.0478303</v>
       </c>
       <c r="F72" s="9" t="n">
-        <v>118.5014735573265</v>
+        <v>118.5014736</v>
       </c>
       <c r="G72" s="9" t="n"/>
       <c r="H72" s="9" t="n"/>
@@ -2993,13 +2993,13 @@
         <v>8081</v>
       </c>
       <c r="C73" s="9" t="n">
-        <v>96.3285521593813</v>
+        <v>96.32855216</v>
       </c>
       <c r="D73" s="9" t="n">
-        <v>102.5448533597278</v>
+        <v>102.5448534</v>
       </c>
       <c r="E73" s="9" t="n">
-        <v>109.2826729365129</v>
+        <v>109.2826729</v>
       </c>
       <c r="F73" s="9" t="n"/>
       <c r="G73" s="9" t="n"/>
@@ -3020,10 +3020,10 @@
         <v>5486</v>
       </c>
       <c r="C74" s="9" t="n">
-        <v>95.35924352898165</v>
+        <v>95.35924353</v>
       </c>
       <c r="D74" s="9" t="n">
-        <v>103.2586365293462</v>
+        <v>103.2586365</v>
       </c>
       <c r="E74" s="9" t="n"/>
       <c r="F74" s="9" t="n"/>
@@ -3045,7 +3045,7 @@
         <v>6385</v>
       </c>
       <c r="C75" s="9" t="n">
-        <v>99.29728739232308</v>
+        <v>99.29728738999999</v>
       </c>
       <c r="D75" s="9" t="n"/>
       <c r="E75" s="9" t="n"/>
@@ -3828,28 +3828,28 @@
         <v>3153</v>
       </c>
       <c r="C95" s="9" t="n">
-        <v>96.01000000000001</v>
+        <v>95.98</v>
       </c>
       <c r="D95" s="9" t="n">
-        <v>119.92</v>
+        <v>119.91</v>
       </c>
       <c r="E95" s="9" t="n">
-        <v>154.5</v>
+        <v>154.47</v>
       </c>
       <c r="F95" s="9" t="n">
-        <v>180.42</v>
+        <v>180.39</v>
       </c>
       <c r="G95" s="9" t="n">
-        <v>201.03</v>
+        <v>201</v>
       </c>
       <c r="H95" s="9" t="n">
-        <v>218.81</v>
+        <v>218.78</v>
       </c>
       <c r="I95" s="9" t="n">
-        <v>243.04</v>
+        <v>243.02</v>
       </c>
       <c r="J95" s="9" t="n">
-        <v>260.73</v>
+        <v>260.7</v>
       </c>
       <c r="K95" s="9" t="n">
         <v>281.9</v>
@@ -3871,7 +3871,7 @@
         <v>3063</v>
       </c>
       <c r="C96" s="9" t="n">
-        <v>97.73</v>
+        <v>97.67</v>
       </c>
       <c r="D96" s="9" t="n">
         <v>126.95</v>
@@ -3917,19 +3917,19 @@
         <v>105.54</v>
       </c>
       <c r="D97" s="9" t="n">
-        <v>126.93</v>
+        <v>126.89</v>
       </c>
       <c r="E97" s="9" t="n">
-        <v>153.52</v>
+        <v>153.49</v>
       </c>
       <c r="F97" s="9" t="n">
-        <v>183.16</v>
+        <v>183.12</v>
       </c>
       <c r="G97" s="9" t="n">
-        <v>207.44</v>
+        <v>207.42</v>
       </c>
       <c r="H97" s="9" t="n">
-        <v>225.13</v>
+        <v>225.12</v>
       </c>
       <c r="I97" s="9" t="n">
         <v>250.99</v>
@@ -3957,28 +3957,28 @@
         <v>3138</v>
       </c>
       <c r="C98" s="9" t="n">
-        <v>102.56</v>
+        <v>102.53</v>
       </c>
       <c r="D98" s="9" t="n">
-        <v>127.42</v>
+        <v>127.39</v>
       </c>
       <c r="E98" s="9" t="n">
-        <v>151.31</v>
+        <v>151.28</v>
       </c>
       <c r="F98" s="9" t="n">
-        <v>186.87</v>
+        <v>186.84</v>
       </c>
       <c r="G98" s="9" t="n">
-        <v>207.65</v>
+        <v>207.6</v>
       </c>
       <c r="H98" s="9" t="n">
         <v>231.2</v>
       </c>
       <c r="I98" s="9" t="n">
-        <v>248.81</v>
+        <v>248.78</v>
       </c>
       <c r="J98" s="9" t="n">
-        <v>264.16</v>
+        <v>264.1</v>
       </c>
       <c r="K98" s="9" t="n">
         <v>280.39</v>
@@ -3998,16 +3998,16 @@
         <v>5363</v>
       </c>
       <c r="C99" s="9" t="n">
-        <v>96.34999999999999</v>
+        <v>96.33</v>
       </c>
       <c r="D99" s="9" t="n">
-        <v>116.38</v>
+        <v>116.37</v>
       </c>
       <c r="E99" s="9" t="n">
-        <v>148.25</v>
+        <v>148.23</v>
       </c>
       <c r="F99" s="9" t="n">
-        <v>182.17</v>
+        <v>182.15</v>
       </c>
       <c r="G99" s="9" t="n">
         <v>209.23</v>
@@ -4016,7 +4016,7 @@
         <v>223.82</v>
       </c>
       <c r="I99" s="9" t="n">
-        <v>245.05</v>
+        <v>245.04</v>
       </c>
       <c r="J99" s="9" t="n">
         <v>259.43</v>
@@ -4037,16 +4037,16 @@
         <v>5192</v>
       </c>
       <c r="C100" s="9" t="n">
-        <v>97.53</v>
+        <v>97.51000000000001</v>
       </c>
       <c r="D100" s="9" t="n">
-        <v>127.57</v>
+        <v>127.52</v>
       </c>
       <c r="E100" s="9" t="n">
-        <v>157.74</v>
+        <v>157.72</v>
       </c>
       <c r="F100" s="9" t="n">
-        <v>192.3</v>
+        <v>192.28</v>
       </c>
       <c r="G100" s="9" t="n">
         <v>211.16</v>
@@ -4074,7 +4074,7 @@
         <v>4577</v>
       </c>
       <c r="C101" s="9" t="n">
-        <v>101.02</v>
+        <v>101.01</v>
       </c>
       <c r="D101" s="9" t="n">
         <v>132.75</v>
@@ -4109,13 +4109,13 @@
         <v>4478</v>
       </c>
       <c r="C102" s="9" t="n">
-        <v>103.41</v>
+        <v>103.38</v>
       </c>
       <c r="D102" s="9" t="n">
-        <v>142.08</v>
+        <v>142.06</v>
       </c>
       <c r="E102" s="9" t="n">
-        <v>169.54</v>
+        <v>169.53</v>
       </c>
       <c r="F102" s="9" t="n">
         <v>200.93</v>
@@ -4142,16 +4142,16 @@
         <v>7765</v>
       </c>
       <c r="C103" s="9" t="n">
-        <v>101.62</v>
+        <v>101.59</v>
       </c>
       <c r="D103" s="9" t="n">
         <v>128.08</v>
       </c>
       <c r="E103" s="9" t="n">
-        <v>158</v>
+        <v>157.97</v>
       </c>
       <c r="F103" s="9" t="n">
-        <v>190.41</v>
+        <v>190.4</v>
       </c>
       <c r="G103" s="9" t="n">
         <v>208.49</v>
@@ -4173,10 +4173,10 @@
         <v>3459</v>
       </c>
       <c r="C104" s="9" t="n">
-        <v>104.69</v>
+        <v>104.61</v>
       </c>
       <c r="D104" s="9" t="n">
-        <v>138.5</v>
+        <v>138.43</v>
       </c>
       <c r="E104" s="9" t="n">
         <v>171.08</v>
@@ -4202,10 +4202,10 @@
         <v>4437</v>
       </c>
       <c r="C105" s="9" t="n">
-        <v>104.44</v>
+        <v>104.36</v>
       </c>
       <c r="D105" s="9" t="n">
-        <v>134.49</v>
+        <v>134.46</v>
       </c>
       <c r="E105" s="9" t="n">
         <v>165.18</v>
@@ -4303,37 +4303,37 @@
         <v>3138</v>
       </c>
       <c r="C109" s="9" t="n">
-        <v>96.36329827915934</v>
+        <v>96.36329828</v>
       </c>
       <c r="D109" s="9" t="n">
-        <v>127.6297386870625</v>
+        <v>127.6297387</v>
       </c>
       <c r="E109" s="9" t="n">
-        <v>176.0163798597841</v>
+        <v>176.0163799</v>
       </c>
       <c r="F109" s="9" t="n">
-        <v>211.1768738049721</v>
+        <v>211.1768738</v>
       </c>
       <c r="G109" s="9" t="n">
-        <v>242.0676959847045</v>
+        <v>242.067696</v>
       </c>
       <c r="H109" s="9" t="n">
-        <v>269.1616730401539</v>
+        <v>269.161673</v>
       </c>
       <c r="I109" s="9" t="n">
-        <v>304.9139579349914</v>
+        <v>304.9139579</v>
       </c>
       <c r="J109" s="9" t="n">
-        <v>333.4328202676874</v>
+        <v>333.4328203</v>
       </c>
       <c r="K109" s="9" t="n">
-        <v>367.4141332058646</v>
+        <v>367.4141332</v>
       </c>
       <c r="L109" s="9" t="n">
-        <v>390.4247418738059</v>
+        <v>390.4247419</v>
       </c>
       <c r="M109" s="9" t="n">
-        <v>413.1214435946472</v>
+        <v>413.1214436</v>
       </c>
     </row>
     <row r="110">
@@ -4346,34 +4346,34 @@
         <v>3079</v>
       </c>
       <c r="C110" s="9" t="n">
-        <v>98.37532315686964</v>
+        <v>98.37532315999999</v>
       </c>
       <c r="D110" s="9" t="n">
-        <v>136.9613348489775</v>
+        <v>136.9613348</v>
       </c>
       <c r="E110" s="9" t="n">
-        <v>170.8845339395914</v>
+        <v>170.8845339</v>
       </c>
       <c r="F110" s="9" t="n">
-        <v>207.0625885027612</v>
+        <v>207.0625885</v>
       </c>
       <c r="G110" s="9" t="n">
-        <v>235.5209353686268</v>
+        <v>235.5209354</v>
       </c>
       <c r="H110" s="9" t="n">
-        <v>269.0439428385845</v>
+        <v>269.0439428</v>
       </c>
       <c r="I110" s="9" t="n">
-        <v>300.7489217278343</v>
+        <v>300.7489217</v>
       </c>
       <c r="J110" s="9" t="n">
-        <v>331.9093731731088</v>
+        <v>331.9093732</v>
       </c>
       <c r="K110" s="9" t="n">
-        <v>354.1337122442357</v>
+        <v>354.1337122</v>
       </c>
       <c r="L110" s="9" t="n">
-        <v>379.7870315037356</v>
+        <v>379.7870315</v>
       </c>
       <c r="M110" s="9" t="n"/>
     </row>
@@ -4387,31 +4387,31 @@
         <v>5274</v>
       </c>
       <c r="C111" s="9" t="n">
-        <v>107.0124345847548</v>
+        <v>107.0124346</v>
       </c>
       <c r="D111" s="9" t="n">
-        <v>132.4733636708375</v>
+        <v>132.4733637</v>
       </c>
       <c r="E111" s="9" t="n">
-        <v>165.7140803943871</v>
+        <v>165.7140804</v>
       </c>
       <c r="F111" s="9" t="n">
-        <v>201.790254076602</v>
+        <v>201.7902541</v>
       </c>
       <c r="G111" s="9" t="n">
-        <v>234.1499279484263</v>
+        <v>234.1499279</v>
       </c>
       <c r="H111" s="9" t="n">
-        <v>259.4084546833524</v>
+        <v>259.4084547</v>
       </c>
       <c r="I111" s="9" t="n">
-        <v>294.988139931741</v>
+        <v>294.9881399</v>
       </c>
       <c r="J111" s="9" t="n">
-        <v>315.6401403109599</v>
+        <v>315.6401403</v>
       </c>
       <c r="K111" s="9" t="n">
-        <v>339.0214069017828</v>
+        <v>339.0214069</v>
       </c>
       <c r="L111" s="9" t="n"/>
       <c r="M111" s="9" t="n"/>
@@ -4426,28 +4426,28 @@
         <v>3116</v>
       </c>
       <c r="C112" s="9" t="n">
-        <v>103.8350545571248</v>
+        <v>103.8350546</v>
       </c>
       <c r="D112" s="9" t="n">
-        <v>137.7636264441595</v>
+        <v>137.7636264</v>
       </c>
       <c r="E112" s="9" t="n">
-        <v>172.0159435173303</v>
+        <v>172.0159435</v>
       </c>
       <c r="F112" s="9" t="n">
-        <v>220.2903498074461</v>
+        <v>220.2903498</v>
       </c>
       <c r="G112" s="9" t="n">
-        <v>253.456100770219</v>
+        <v>253.4561008</v>
       </c>
       <c r="H112" s="9" t="n">
-        <v>292.6629428754821</v>
+        <v>292.6629429</v>
       </c>
       <c r="I112" s="9" t="n">
-        <v>319.9341174582806</v>
+        <v>319.9341175</v>
       </c>
       <c r="J112" s="9" t="n">
-        <v>347.1997368421059</v>
+        <v>347.1997368</v>
       </c>
       <c r="K112" s="9" t="n"/>
       <c r="L112" s="9" t="n"/>
@@ -4463,25 +4463,25 @@
         <v>5353</v>
       </c>
       <c r="C113" s="9" t="n">
-        <v>97.30717167943119</v>
+        <v>97.30717168</v>
       </c>
       <c r="D113" s="9" t="n">
-        <v>122.9090472632161</v>
+        <v>122.9090473</v>
       </c>
       <c r="E113" s="9" t="n">
-        <v>162.3721389874834</v>
+        <v>162.372139</v>
       </c>
       <c r="F113" s="9" t="n">
-        <v>203.745832243602</v>
+        <v>203.7458322</v>
       </c>
       <c r="G113" s="9" t="n">
-        <v>240.1205342798436</v>
+        <v>240.1205343</v>
       </c>
       <c r="H113" s="9" t="n">
-        <v>261.0600224173367</v>
+        <v>261.0600224</v>
       </c>
       <c r="I113" s="9" t="n">
-        <v>289.1598374743142</v>
+        <v>289.1598375</v>
       </c>
       <c r="J113" s="9" t="n"/>
       <c r="K113" s="9" t="n"/>
@@ -4498,22 +4498,22 @@
         <v>5202</v>
       </c>
       <c r="C114" s="9" t="n">
-        <v>98.2183737024215</v>
+        <v>98.2183737</v>
       </c>
       <c r="D114" s="9" t="n">
-        <v>134.6238869665511</v>
+        <v>134.623887</v>
       </c>
       <c r="E114" s="9" t="n">
-        <v>171.3543060361401</v>
+        <v>171.354306</v>
       </c>
       <c r="F114" s="9" t="n">
-        <v>216.2170453671671</v>
+        <v>216.2170454</v>
       </c>
       <c r="G114" s="9" t="n">
-        <v>242.0012437524036</v>
+        <v>242.0012438</v>
       </c>
       <c r="H114" s="9" t="n">
-        <v>266.3212860438299</v>
+        <v>266.321286</v>
       </c>
       <c r="I114" s="9" t="n"/>
       <c r="J114" s="9" t="n"/>
@@ -4531,19 +4531,19 @@
         <v>4608</v>
       </c>
       <c r="C115" s="9" t="n">
-        <v>102.590184461804</v>
+        <v>102.5901845</v>
       </c>
       <c r="D115" s="9" t="n">
-        <v>141.9545724826377</v>
+        <v>141.9545725</v>
       </c>
       <c r="E115" s="9" t="n">
-        <v>190.8568641493049</v>
+        <v>190.8568641</v>
       </c>
       <c r="F115" s="9" t="n">
-        <v>227.7173980034718</v>
+        <v>227.717398</v>
       </c>
       <c r="G115" s="9" t="n">
-        <v>257.2806249999996</v>
+        <v>257.280625</v>
       </c>
       <c r="H115" s="9" t="n"/>
       <c r="I115" s="9" t="n"/>
@@ -4562,16 +4562,16 @@
         <v>4508</v>
       </c>
       <c r="C116" s="9" t="n">
-        <v>104.9280146406376</v>
+        <v>104.9280146</v>
       </c>
       <c r="D116" s="9" t="n">
-        <v>155.2453948535928</v>
+        <v>155.2453949</v>
       </c>
       <c r="E116" s="9" t="n">
-        <v>190.265798580301</v>
+        <v>190.2657986</v>
       </c>
       <c r="F116" s="9" t="n">
-        <v>230.5558651286598</v>
+        <v>230.5558651</v>
       </c>
       <c r="G116" s="9" t="n"/>
       <c r="H116" s="9" t="n"/>
@@ -4591,13 +4591,13 @@
         <v>7853</v>
       </c>
       <c r="C117" s="9" t="n">
-        <v>102.9923430536115</v>
+        <v>102.9923431</v>
       </c>
       <c r="D117" s="9" t="n">
-        <v>132.3526805042677</v>
+        <v>132.3526805</v>
       </c>
       <c r="E117" s="9" t="n">
-        <v>166.2611829873957</v>
+        <v>166.261183</v>
       </c>
       <c r="F117" s="9" t="n"/>
       <c r="G117" s="9" t="n"/>
@@ -4618,10 +4618,10 @@
         <v>3492</v>
       </c>
       <c r="C118" s="9" t="n">
-        <v>106.4186426116839</v>
+        <v>106.4186426</v>
       </c>
       <c r="D118" s="9" t="n">
-        <v>146.3630756013748</v>
+        <v>146.3630756</v>
       </c>
       <c r="E118" s="9" t="n"/>
       <c r="F118" s="9" t="n"/>
@@ -4643,7 +4643,7 @@
         <v>4447</v>
       </c>
       <c r="C119" s="9" t="n">
-        <v>105.6801371711262</v>
+        <v>105.6801372</v>
       </c>
       <c r="D119" s="9" t="n"/>
       <c r="E119" s="9" t="n"/>
@@ -5977,37 +5977,37 @@
         <v>7945</v>
       </c>
       <c r="C21" s="9" t="n">
-        <v>92.88980239144014</v>
+        <v>92.88980239</v>
       </c>
       <c r="D21" s="9" t="n">
-        <v>109.2581913152916</v>
+        <v>109.2581913</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>134.4189804908738</v>
+        <v>134.4189805</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v>151.2283310258015</v>
+        <v>151.228331</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>165.9129616110752</v>
+        <v>165.9129616</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>179.0687212083062</v>
+        <v>179.0687212</v>
       </c>
       <c r="I21" s="9" t="n">
-        <v>195.4255909376958</v>
+        <v>195.4255909</v>
       </c>
       <c r="J21" s="9" t="n">
-        <v>208.4516224040268</v>
+        <v>208.4516224</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>224.0902353681552</v>
+        <v>224.0902354</v>
       </c>
       <c r="L21" s="9" t="n">
-        <v>234.4451642542471</v>
+        <v>234.4451643</v>
       </c>
       <c r="M21" s="9" t="n">
-        <v>244.7189037130262</v>
+        <v>244.7189037</v>
       </c>
     </row>
     <row r="22">
@@ -6020,34 +6020,34 @@
         <v>7757</v>
       </c>
       <c r="C22" s="9" t="n">
-        <v>93.58246358128143</v>
+        <v>93.58246358</v>
       </c>
       <c r="D22" s="9" t="n">
-        <v>116.2646371019725</v>
+        <v>116.2646371</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>133.8571690086374</v>
+        <v>133.857169</v>
       </c>
       <c r="F22" s="9" t="n">
-        <v>151.5381603712776</v>
+        <v>151.5381604</v>
       </c>
       <c r="G22" s="9" t="n">
-        <v>165.8278483949981</v>
+        <v>165.8278484</v>
       </c>
       <c r="H22" s="9" t="n">
-        <v>181.5058398865541</v>
+        <v>181.5058399</v>
       </c>
       <c r="I22" s="9" t="n">
-        <v>195.7418770143097</v>
+        <v>195.741877</v>
       </c>
       <c r="J22" s="9" t="n">
-        <v>210.602847750419</v>
+        <v>210.6028478</v>
       </c>
       <c r="K22" s="9" t="n">
-        <v>220.5761570194663</v>
+        <v>220.576157</v>
       </c>
       <c r="L22" s="9" t="n">
-        <v>232.4624223282197</v>
+        <v>232.4624223</v>
       </c>
       <c r="M22" s="9" t="n"/>
     </row>
@@ -6061,31 +6061,31 @@
         <v>11950</v>
       </c>
       <c r="C23" s="9" t="n">
-        <v>99.84738912133761</v>
+        <v>99.84738912</v>
       </c>
       <c r="D23" s="9" t="n">
-        <v>115.9622242677812</v>
+        <v>115.9622243</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>134.1972309623419</v>
+        <v>134.197231</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>153.2141514644341</v>
+        <v>153.2141515</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>170.4690359832626</v>
+        <v>170.469036</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>183.8624058577396</v>
+        <v>183.8624059</v>
       </c>
       <c r="I23" s="9" t="n">
-        <v>202.3255531380745</v>
+        <v>202.3255531</v>
       </c>
       <c r="J23" s="9" t="n">
-        <v>212.7203707112963</v>
+        <v>212.7203707</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>224.8946527196645</v>
+        <v>224.8946527</v>
       </c>
       <c r="L23" s="9" t="n"/>
       <c r="M23" s="9" t="n"/>
@@ -6100,28 +6100,28 @@
         <v>9056</v>
       </c>
       <c r="C24" s="9" t="n">
-        <v>97.87320229681924</v>
+        <v>97.8732023</v>
       </c>
       <c r="D24" s="9" t="n">
-        <v>113.3810479240277</v>
+        <v>113.3810479</v>
       </c>
       <c r="E24" s="9" t="n">
-        <v>128.7157906360419</v>
+        <v>128.7157906</v>
       </c>
       <c r="F24" s="9" t="n">
-        <v>148.340142446996</v>
+        <v>148.3401424</v>
       </c>
       <c r="G24" s="9" t="n">
-        <v>162.0841409010597</v>
+        <v>162.0841409</v>
       </c>
       <c r="H24" s="9" t="n">
-        <v>178.4198332597169</v>
+        <v>178.4198333</v>
       </c>
       <c r="I24" s="9" t="n">
-        <v>189.0977120141339</v>
+        <v>189.097712</v>
       </c>
       <c r="J24" s="9" t="n">
-        <v>200.147360865724</v>
+        <v>200.1473609</v>
       </c>
       <c r="K24" s="9" t="n"/>
       <c r="L24" s="9" t="n"/>
@@ -6137,25 +6137,25 @@
         <v>12255</v>
       </c>
       <c r="C25" s="9" t="n">
-        <v>92.98071889024696</v>
+        <v>92.98071889000001</v>
       </c>
       <c r="D25" s="9" t="n">
-        <v>107.8431676866566</v>
+        <v>107.8431677</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>128.9879110567099</v>
+        <v>128.9879111</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>149.8797813137481</v>
+        <v>149.8797813</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>169.1570199918388</v>
+        <v>169.15702</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>180.0422284781709</v>
+        <v>180.0422285</v>
       </c>
       <c r="I25" s="9" t="n">
-        <v>194.0367311301497</v>
+        <v>194.0367311</v>
       </c>
       <c r="J25" s="9" t="n"/>
       <c r="K25" s="9" t="n"/>
@@ -6172,22 +6172,22 @@
         <v>11963</v>
       </c>
       <c r="C26" s="9" t="n">
-        <v>95.05778400066698</v>
+        <v>95.057784</v>
       </c>
       <c r="D26" s="9" t="n">
-        <v>115.2037139513485</v>
+        <v>115.203714</v>
       </c>
       <c r="E26" s="9" t="n">
-        <v>135.3271879963206</v>
+        <v>135.327188</v>
       </c>
       <c r="F26" s="9" t="n">
-        <v>159.0452428320644</v>
+        <v>159.0452428</v>
       </c>
       <c r="G26" s="9" t="n">
-        <v>172.4782328847267</v>
+        <v>172.4782329</v>
       </c>
       <c r="H26" s="9" t="n">
-        <v>185.405334782244</v>
+        <v>185.4053348</v>
       </c>
       <c r="I26" s="9" t="n"/>
       <c r="J26" s="9" t="n"/>
@@ -6205,19 +6205,19 @@
         <v>11207</v>
       </c>
       <c r="C27" s="9" t="n">
-        <v>98.34834746140596</v>
+        <v>98.34834746</v>
       </c>
       <c r="D27" s="9" t="n">
-        <v>120.0648906933147</v>
+        <v>120.0648907</v>
       </c>
       <c r="E27" s="9" t="n">
-        <v>146.8181056482539</v>
+        <v>146.8181056</v>
       </c>
       <c r="F27" s="9" t="n">
-        <v>166.452576068527</v>
+        <v>166.4525761</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>182.7494565896299</v>
+        <v>182.7494566</v>
       </c>
       <c r="H27" s="9" t="n"/>
       <c r="I27" s="9" t="n"/>
@@ -6236,16 +6236,16 @@
         <v>11145</v>
       </c>
       <c r="C28" s="9" t="n">
-        <v>98.49222969941405</v>
+        <v>98.4922297</v>
       </c>
       <c r="D28" s="9" t="n">
-        <v>125.6861327949728</v>
+        <v>125.6861328</v>
       </c>
       <c r="E28" s="9" t="n">
-        <v>143.6859282189298</v>
+        <v>143.6859282</v>
       </c>
       <c r="F28" s="9" t="n">
-        <v>163.8259416778801</v>
+        <v>163.8259417</v>
       </c>
       <c r="G28" s="9" t="n"/>
       <c r="H28" s="9" t="n"/>
@@ -6265,13 +6265,13 @@
         <v>15934</v>
       </c>
       <c r="C29" s="9" t="n">
-        <v>99.61277143215585</v>
+        <v>99.61277143</v>
       </c>
       <c r="D29" s="9" t="n">
-        <v>117.2355064641631</v>
+        <v>117.2355065</v>
       </c>
       <c r="E29" s="9" t="n">
-        <v>139.2069336011021</v>
+        <v>139.2069336</v>
       </c>
       <c r="F29" s="9" t="n"/>
       <c r="G29" s="9" t="n"/>
@@ -6292,10 +6292,10 @@
         <v>8978</v>
       </c>
       <c r="C30" s="9" t="n">
-        <v>99.66080530184823</v>
+        <v>99.66080530000001</v>
       </c>
       <c r="D30" s="9" t="n">
-        <v>120.0241412341272</v>
+        <v>120.0241412</v>
       </c>
       <c r="E30" s="9" t="n"/>
       <c r="F30" s="9" t="n"/>
@@ -6317,7 +6317,7 @@
         <v>10832</v>
       </c>
       <c r="C31" s="9" t="n">
-        <v>101.9177206425389</v>
+        <v>101.9177206</v>
       </c>
       <c r="D31" s="9" t="n"/>
       <c r="E31" s="9" t="n"/>
@@ -7575,37 +7575,37 @@
         <v>4807</v>
       </c>
       <c r="C65" s="9" t="n">
-        <v>90.62231121281255</v>
+        <v>90.62231121000001</v>
       </c>
       <c r="D65" s="9" t="n">
-        <v>97.2652818805887</v>
+        <v>97.26528188</v>
       </c>
       <c r="E65" s="9" t="n">
-        <v>107.2642812564989</v>
+        <v>107.2642813</v>
       </c>
       <c r="F65" s="9" t="n">
-        <v>112.0940420220491</v>
+        <v>112.094042</v>
       </c>
       <c r="G65" s="9" t="n">
-        <v>116.1993030996443</v>
+        <v>116.1993031</v>
       </c>
       <c r="H65" s="9" t="n">
-        <v>120.2562221759913</v>
+        <v>120.2562222</v>
       </c>
       <c r="I65" s="9" t="n">
-        <v>123.9518036197192</v>
+        <v>123.9518036</v>
       </c>
       <c r="J65" s="9" t="n">
-        <v>126.8641460370273</v>
+        <v>126.864146</v>
       </c>
       <c r="K65" s="9" t="n">
-        <v>130.5286810900749</v>
+        <v>130.5286811</v>
       </c>
       <c r="L65" s="9" t="n">
-        <v>132.6220074890764</v>
+        <v>132.6220075</v>
       </c>
       <c r="M65" s="9" t="n">
-        <v>134.7860619929249</v>
+        <v>134.786062</v>
       </c>
     </row>
     <row r="66">
@@ -7618,34 +7618,34 @@
         <v>4678</v>
       </c>
       <c r="C66" s="9" t="n">
-        <v>90.42786447199624</v>
+        <v>90.42786447</v>
       </c>
       <c r="D66" s="9" t="n">
-        <v>102.6423343309103</v>
+        <v>102.6423343</v>
       </c>
       <c r="E66" s="9" t="n">
-        <v>109.4862291577594</v>
+        <v>109.4862292</v>
       </c>
       <c r="F66" s="9" t="n">
-        <v>114.9926891834114</v>
+        <v>114.9926892</v>
       </c>
       <c r="G66" s="9" t="n">
-        <v>119.9567464728513</v>
+        <v>119.9567465</v>
       </c>
       <c r="H66" s="9" t="n">
-        <v>123.8893758016243</v>
+        <v>123.8893758</v>
       </c>
       <c r="I66" s="9" t="n">
-        <v>126.6275780247966</v>
+        <v>126.627578</v>
       </c>
       <c r="J66" s="9" t="n">
-        <v>130.7604382214618</v>
+        <v>130.7604382</v>
       </c>
       <c r="K66" s="9" t="n">
-        <v>132.670275758871</v>
+        <v>132.6702758</v>
       </c>
       <c r="L66" s="9" t="n">
-        <v>135.4952415562203</v>
+        <v>135.4952416</v>
       </c>
       <c r="M66" s="9" t="n"/>
     </row>
@@ -7659,31 +7659,31 @@
         <v>6676</v>
       </c>
       <c r="C67" s="9" t="n">
-        <v>94.18704613540861</v>
+        <v>94.18704614000001</v>
       </c>
       <c r="D67" s="9" t="n">
-        <v>102.9185230677034</v>
+        <v>102.9185231</v>
       </c>
       <c r="E67" s="9" t="n">
-        <v>109.2991087477514</v>
+        <v>109.2991087</v>
       </c>
       <c r="F67" s="9" t="n">
-        <v>114.8393214499683</v>
+        <v>114.8393214</v>
       </c>
       <c r="G67" s="9" t="n">
-        <v>120.1615128819635</v>
+        <v>120.1615129</v>
       </c>
       <c r="H67" s="9" t="n">
-        <v>124.1814799280989</v>
+        <v>124.1814799</v>
       </c>
       <c r="I67" s="9" t="n">
-        <v>129.1226647693211</v>
+        <v>129.1226648</v>
       </c>
       <c r="J67" s="9" t="n">
-        <v>131.4143693828622</v>
+        <v>131.4143694</v>
       </c>
       <c r="K67" s="9" t="n">
-        <v>134.7352007189916</v>
+        <v>134.7352007</v>
       </c>
       <c r="L67" s="9" t="n"/>
       <c r="M67" s="9" t="n"/>
@@ -7698,28 +7698,28 @@
         <v>5940</v>
       </c>
       <c r="C68" s="9" t="n">
-        <v>94.74573905723807</v>
+        <v>94.74573906000001</v>
       </c>
       <c r="D68" s="9" t="n">
-        <v>100.5904562289552</v>
+        <v>100.5904562</v>
       </c>
       <c r="E68" s="9" t="n">
-        <v>106.0014343434333</v>
+        <v>106.0014343</v>
       </c>
       <c r="F68" s="9" t="n">
-        <v>110.5965656565646</v>
+        <v>110.5965657</v>
       </c>
       <c r="G68" s="9" t="n">
-        <v>114.1523181818172</v>
+        <v>114.1523182</v>
       </c>
       <c r="H68" s="9" t="n">
-        <v>118.4902828282818</v>
+        <v>118.4902828</v>
       </c>
       <c r="I68" s="9" t="n">
-        <v>120.463664983164</v>
+        <v>120.463665</v>
       </c>
       <c r="J68" s="9" t="n">
-        <v>123.0067542087532</v>
+        <v>123.0067542</v>
       </c>
       <c r="K68" s="9" t="n"/>
       <c r="L68" s="9" t="n"/>
@@ -7735,25 +7735,25 @@
         <v>6902</v>
       </c>
       <c r="C69" s="9" t="n">
-        <v>89.6252419588498</v>
+        <v>89.62524196</v>
       </c>
       <c r="D69" s="9" t="n">
-        <v>96.15848884381069</v>
+        <v>96.15848884</v>
       </c>
       <c r="E69" s="9" t="n">
-        <v>103.0960286873343</v>
+        <v>103.0960287</v>
       </c>
       <c r="F69" s="9" t="n">
-        <v>108.1027644161086</v>
+        <v>108.1027644</v>
       </c>
       <c r="G69" s="9" t="n">
-        <v>114.1196841495192</v>
+        <v>114.1196841</v>
       </c>
       <c r="H69" s="9" t="n">
-        <v>117.2070718632254</v>
+        <v>117.2070719</v>
       </c>
       <c r="I69" s="9" t="n">
-        <v>120.2618849608782</v>
+        <v>120.261885</v>
       </c>
       <c r="J69" s="9" t="n"/>
       <c r="K69" s="9" t="n"/>
@@ -7770,22 +7770,22 @@
         <v>6761</v>
       </c>
       <c r="C70" s="9" t="n">
-        <v>92.62598580091441</v>
+        <v>92.6259858</v>
       </c>
       <c r="D70" s="9" t="n">
-        <v>100.2615840851919</v>
+        <v>100.2615841</v>
       </c>
       <c r="E70" s="9" t="n">
-        <v>107.6074619139155</v>
+        <v>107.6074619</v>
       </c>
       <c r="F70" s="9" t="n">
-        <v>115.0565256618818</v>
+        <v>115.0565257</v>
       </c>
       <c r="G70" s="9" t="n">
-        <v>118.9863378198466</v>
+        <v>118.9863378</v>
       </c>
       <c r="H70" s="9" t="n">
-        <v>123.1475654488955</v>
+        <v>123.1475654</v>
       </c>
       <c r="I70" s="9" t="n"/>
       <c r="J70" s="9" t="n"/>
@@ -7803,19 +7803,19 @@
         <v>6599</v>
       </c>
       <c r="C71" s="9" t="n">
-        <v>95.38632520078555</v>
+        <v>95.3863252</v>
       </c>
       <c r="D71" s="9" t="n">
-        <v>104.7795969086201</v>
+        <v>104.7795969</v>
       </c>
       <c r="E71" s="9" t="n">
-        <v>116.0663858160303</v>
+        <v>116.0663858</v>
       </c>
       <c r="F71" s="9" t="n">
-        <v>123.6721094105144</v>
+        <v>123.6721094</v>
       </c>
       <c r="G71" s="9" t="n">
-        <v>130.7052644340028</v>
+        <v>130.7052644</v>
       </c>
       <c r="H71" s="9" t="n"/>
       <c r="I71" s="9" t="n"/>
@@ -7834,16 +7834,16 @@
         <v>6637</v>
       </c>
       <c r="C72" s="9" t="n">
-        <v>94.12089950278373</v>
+        <v>94.12089949999999</v>
       </c>
       <c r="D72" s="9" t="n">
-        <v>105.6088157299948</v>
+        <v>105.6088157</v>
       </c>
       <c r="E72" s="9" t="n">
-        <v>112.0478303450318</v>
+        <v>112.0478303</v>
       </c>
       <c r="F72" s="9" t="n">
-        <v>118.5014735573265</v>
+        <v>118.5014736</v>
       </c>
       <c r="G72" s="9" t="n"/>
       <c r="H72" s="9" t="n"/>
@@ -7863,13 +7863,13 @@
         <v>8081</v>
       </c>
       <c r="C73" s="9" t="n">
-        <v>96.3285521593813</v>
+        <v>96.32855216</v>
       </c>
       <c r="D73" s="9" t="n">
-        <v>102.5448533597278</v>
+        <v>102.5448534</v>
       </c>
       <c r="E73" s="9" t="n">
-        <v>109.2826729365129</v>
+        <v>109.2826729</v>
       </c>
       <c r="F73" s="9" t="n"/>
       <c r="G73" s="9" t="n"/>
@@ -7890,10 +7890,10 @@
         <v>5486</v>
       </c>
       <c r="C74" s="9" t="n">
-        <v>95.35924352898165</v>
+        <v>95.35924353</v>
       </c>
       <c r="D74" s="9" t="n">
-        <v>103.2586365293462</v>
+        <v>103.2586365</v>
       </c>
       <c r="E74" s="9" t="n"/>
       <c r="F74" s="9" t="n"/>
@@ -7915,7 +7915,7 @@
         <v>6385</v>
       </c>
       <c r="C75" s="9" t="n">
-        <v>99.29728739232308</v>
+        <v>99.29728738999999</v>
       </c>
       <c r="D75" s="9" t="n"/>
       <c r="E75" s="9" t="n"/>
@@ -9173,37 +9173,37 @@
         <v>3138</v>
       </c>
       <c r="C109" s="9" t="n">
-        <v>96.36329827915934</v>
+        <v>96.36329828</v>
       </c>
       <c r="D109" s="9" t="n">
-        <v>127.6297386870625</v>
+        <v>127.6297387</v>
       </c>
       <c r="E109" s="9" t="n">
-        <v>176.0163798597841</v>
+        <v>176.0163799</v>
       </c>
       <c r="F109" s="9" t="n">
-        <v>211.1768738049721</v>
+        <v>211.1768738</v>
       </c>
       <c r="G109" s="9" t="n">
-        <v>242.0676959847045</v>
+        <v>242.067696</v>
       </c>
       <c r="H109" s="9" t="n">
-        <v>269.1616730401539</v>
+        <v>269.161673</v>
       </c>
       <c r="I109" s="9" t="n">
-        <v>304.9139579349914</v>
+        <v>304.9139579</v>
       </c>
       <c r="J109" s="9" t="n">
-        <v>333.4328202676874</v>
+        <v>333.4328203</v>
       </c>
       <c r="K109" s="9" t="n">
-        <v>367.4141332058646</v>
+        <v>367.4141332</v>
       </c>
       <c r="L109" s="9" t="n">
-        <v>390.4247418738059</v>
+        <v>390.4247419</v>
       </c>
       <c r="M109" s="9" t="n">
-        <v>413.1214435946472</v>
+        <v>413.1214436</v>
       </c>
     </row>
     <row r="110">
@@ -9216,34 +9216,34 @@
         <v>3079</v>
       </c>
       <c r="C110" s="9" t="n">
-        <v>98.37532315686964</v>
+        <v>98.37532315999999</v>
       </c>
       <c r="D110" s="9" t="n">
-        <v>136.9613348489775</v>
+        <v>136.9613348</v>
       </c>
       <c r="E110" s="9" t="n">
-        <v>170.8845339395914</v>
+        <v>170.8845339</v>
       </c>
       <c r="F110" s="9" t="n">
-        <v>207.0625885027612</v>
+        <v>207.0625885</v>
       </c>
       <c r="G110" s="9" t="n">
-        <v>235.5209353686268</v>
+        <v>235.5209354</v>
       </c>
       <c r="H110" s="9" t="n">
-        <v>269.0439428385845</v>
+        <v>269.0439428</v>
       </c>
       <c r="I110" s="9" t="n">
-        <v>300.7489217278343</v>
+        <v>300.7489217</v>
       </c>
       <c r="J110" s="9" t="n">
-        <v>331.9093731731088</v>
+        <v>331.9093732</v>
       </c>
       <c r="K110" s="9" t="n">
-        <v>354.1337122442357</v>
+        <v>354.1337122</v>
       </c>
       <c r="L110" s="9" t="n">
-        <v>379.7870315037356</v>
+        <v>379.7870315</v>
       </c>
       <c r="M110" s="9" t="n"/>
     </row>
@@ -9257,31 +9257,31 @@
         <v>5274</v>
       </c>
       <c r="C111" s="9" t="n">
-        <v>107.0124345847548</v>
+        <v>107.0124346</v>
       </c>
       <c r="D111" s="9" t="n">
-        <v>132.4733636708375</v>
+        <v>132.4733637</v>
       </c>
       <c r="E111" s="9" t="n">
-        <v>165.7140803943871</v>
+        <v>165.7140804</v>
       </c>
       <c r="F111" s="9" t="n">
-        <v>201.790254076602</v>
+        <v>201.7902541</v>
       </c>
       <c r="G111" s="9" t="n">
-        <v>234.1499279484263</v>
+        <v>234.1499279</v>
       </c>
       <c r="H111" s="9" t="n">
-        <v>259.4084546833524</v>
+        <v>259.4084547</v>
       </c>
       <c r="I111" s="9" t="n">
-        <v>294.988139931741</v>
+        <v>294.9881399</v>
       </c>
       <c r="J111" s="9" t="n">
-        <v>315.6401403109599</v>
+        <v>315.6401403</v>
       </c>
       <c r="K111" s="9" t="n">
-        <v>339.0214069017828</v>
+        <v>339.0214069</v>
       </c>
       <c r="L111" s="9" t="n"/>
       <c r="M111" s="9" t="n"/>
@@ -9296,28 +9296,28 @@
         <v>3116</v>
       </c>
       <c r="C112" s="9" t="n">
-        <v>103.8350545571248</v>
+        <v>103.8350546</v>
       </c>
       <c r="D112" s="9" t="n">
-        <v>137.7636264441595</v>
+        <v>137.7636264</v>
       </c>
       <c r="E112" s="9" t="n">
-        <v>172.0159435173303</v>
+        <v>172.0159435</v>
       </c>
       <c r="F112" s="9" t="n">
-        <v>220.2903498074461</v>
+        <v>220.2903498</v>
       </c>
       <c r="G112" s="9" t="n">
-        <v>253.456100770219</v>
+        <v>253.4561008</v>
       </c>
       <c r="H112" s="9" t="n">
-        <v>292.6629428754821</v>
+        <v>292.6629429</v>
       </c>
       <c r="I112" s="9" t="n">
-        <v>319.9341174582806</v>
+        <v>319.9341175</v>
       </c>
       <c r="J112" s="9" t="n">
-        <v>347.1997368421059</v>
+        <v>347.1997368</v>
       </c>
       <c r="K112" s="9" t="n"/>
       <c r="L112" s="9" t="n"/>
@@ -9333,25 +9333,25 @@
         <v>5353</v>
       </c>
       <c r="C113" s="9" t="n">
-        <v>97.30717167943119</v>
+        <v>97.30717168</v>
       </c>
       <c r="D113" s="9" t="n">
-        <v>122.9090472632161</v>
+        <v>122.9090473</v>
       </c>
       <c r="E113" s="9" t="n">
-        <v>162.3721389874834</v>
+        <v>162.372139</v>
       </c>
       <c r="F113" s="9" t="n">
-        <v>203.745832243602</v>
+        <v>203.7458322</v>
       </c>
       <c r="G113" s="9" t="n">
-        <v>240.1205342798436</v>
+        <v>240.1205343</v>
       </c>
       <c r="H113" s="9" t="n">
-        <v>261.0600224173367</v>
+        <v>261.0600224</v>
       </c>
       <c r="I113" s="9" t="n">
-        <v>289.1598374743142</v>
+        <v>289.1598375</v>
       </c>
       <c r="J113" s="9" t="n"/>
       <c r="K113" s="9" t="n"/>
@@ -9368,22 +9368,22 @@
         <v>5202</v>
       </c>
       <c r="C114" s="9" t="n">
-        <v>98.2183737024215</v>
+        <v>98.2183737</v>
       </c>
       <c r="D114" s="9" t="n">
-        <v>134.6238869665511</v>
+        <v>134.623887</v>
       </c>
       <c r="E114" s="9" t="n">
-        <v>171.3543060361401</v>
+        <v>171.354306</v>
       </c>
       <c r="F114" s="9" t="n">
-        <v>216.2170453671671</v>
+        <v>216.2170454</v>
       </c>
       <c r="G114" s="9" t="n">
-        <v>242.0012437524036</v>
+        <v>242.0012438</v>
       </c>
       <c r="H114" s="9" t="n">
-        <v>266.3212860438299</v>
+        <v>266.321286</v>
       </c>
       <c r="I114" s="9" t="n"/>
       <c r="J114" s="9" t="n"/>
@@ -9401,19 +9401,19 @@
         <v>4608</v>
       </c>
       <c r="C115" s="9" t="n">
-        <v>102.590184461804</v>
+        <v>102.5901845</v>
       </c>
       <c r="D115" s="9" t="n">
-        <v>141.9545724826377</v>
+        <v>141.9545725</v>
       </c>
       <c r="E115" s="9" t="n">
-        <v>190.8568641493049</v>
+        <v>190.8568641</v>
       </c>
       <c r="F115" s="9" t="n">
-        <v>227.7173980034718</v>
+        <v>227.717398</v>
       </c>
       <c r="G115" s="9" t="n">
-        <v>257.2806249999996</v>
+        <v>257.280625</v>
       </c>
       <c r="H115" s="9" t="n"/>
       <c r="I115" s="9" t="n"/>
@@ -9432,16 +9432,16 @@
         <v>4508</v>
       </c>
       <c r="C116" s="9" t="n">
-        <v>104.9280146406376</v>
+        <v>104.9280146</v>
       </c>
       <c r="D116" s="9" t="n">
-        <v>155.2453948535928</v>
+        <v>155.2453949</v>
       </c>
       <c r="E116" s="9" t="n">
-        <v>190.265798580301</v>
+        <v>190.2657986</v>
       </c>
       <c r="F116" s="9" t="n">
-        <v>230.5558651286598</v>
+        <v>230.5558651</v>
       </c>
       <c r="G116" s="9" t="n"/>
       <c r="H116" s="9" t="n"/>
@@ -9461,13 +9461,13 @@
         <v>7853</v>
       </c>
       <c r="C117" s="9" t="n">
-        <v>102.9923430536115</v>
+        <v>102.9923431</v>
       </c>
       <c r="D117" s="9" t="n">
-        <v>132.3526805042677</v>
+        <v>132.3526805</v>
       </c>
       <c r="E117" s="9" t="n">
-        <v>166.2611829873957</v>
+        <v>166.261183</v>
       </c>
       <c r="F117" s="9" t="n"/>
       <c r="G117" s="9" t="n"/>
@@ -9488,10 +9488,10 @@
         <v>3492</v>
       </c>
       <c r="C118" s="9" t="n">
-        <v>106.4186426116839</v>
+        <v>106.4186426</v>
       </c>
       <c r="D118" s="9" t="n">
-        <v>146.3630756013748</v>
+        <v>146.3630756</v>
       </c>
       <c r="E118" s="9" t="n"/>
       <c r="F118" s="9" t="n"/>
@@ -9513,7 +9513,7 @@
         <v>4447</v>
       </c>
       <c r="C119" s="9" t="n">
-        <v>105.6801371711262</v>
+        <v>105.6801372</v>
       </c>
       <c r="D119" s="9" t="n"/>
       <c r="E119" s="9" t="n"/>
@@ -10249,7 +10249,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A28"/>
+  <dimension ref="A1:A29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="130" customWidth="1" min="1" max="1"/>
@@ -10296,140 +10296,147 @@
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
         <is>
-          <t>SOURCES - the two tabs are built from different tables, and this is deliberate.</t>
+          <t>SOURCES - both tabs come from LineItemMaster, so only the logic differs between them.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Before tab: OrderLinesMaster + ReturnLinesMaster (sql/05a, logic "A old").</t>
+          <t xml:space="preserve">  Before tab: sql/10_before_logic_lim.sql - acquisition bucket for life, no Faire.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  After tab:  LineItemMaster (sql/09_production_lim.sql), the production query.</t>
+          <t xml:space="preserve">  After tab:  sql/09_production_lim.sql   - attribution fixed, Faire included.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  The two tables agree to within 0.08% on identical logic, verified across all 11 cohorts and both buckets, so the tabs are comparable. LineItemMaster is simply the other two tables combined.</t>
+          <t xml:space="preserve">  Both were validated against the earlier OrderLinesMaster + ReturnLinesMaster build, which they reproduce to within 0.08% across all 11 cohorts and both buckets. LineItemMaster is simply those two tables combined, so this is a change of source, not of method.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="12" t="inlineStr"/>
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Cross-check that holds in the data: the two tabs have IDENTICAL customer counts before 2026-02, and from 2026-02 the After tab is higher by exactly the Faire retailers - +17 Feb, +33 Mar, +25 Apr, +37 May, +33 Jun, +46 Jul. Subscription M0 is identical on both tabs in every cohort, because every Faire order is OTP.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="13" t="inlineStr">
+      <c r="A12" s="12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="13" t="inlineStr">
         <is>
           <t>METHOD</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="12" t="inlineStr">
-        <is>
-          <t>LTR = gross sales - item discounts + shipping - shipping tax, net of returns. Shopify only; test orders and gift cards excluded; founding-order revenue bucket "TT New" (TikTok) excluded.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>The $0 founding-order rule removes a 2026-07-09 free-product promotion (936 customers in July).</t>
+          <t>LTR = gross sales - item discounts + shipping - shipping tax, net of returns. Shopify only; test orders and gift cards excluded; founding-order revenue bucket "TT New" (TikTok) excluded.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>The Customers column differs between tabs: the After tab adds Faire retailers, who are excluded from the presentation layer by a channel filter and so appear in neither table.</t>
+          <t>The $0 founding-order rule removes a 2026-07-09 free-product promotion (936 customers in July).</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
         <is>
-          <t>October 2026 is a partial month and is excluded, so the last month shown varies by cohort.</t>
+          <t>The Customers column differs between tabs: the After tab adds Faire retailers, who are excluded from the presentation layer by a channel filter and so appear in neither table.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
+          <t>October 2026 is a partial month and is excluded, so the last month shown varies by cohort.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="12" t="inlineStr">
+        <is>
           <t>Client rows are from Cohorts_Dashboard_Complete_Validation_Sheet "Month View", identical on both tabs.</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="12" t="inlineStr"/>
-    </row>
     <row r="19">
-      <c r="A19" s="13" t="inlineStr">
+      <c r="A19" s="12" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="13" t="inlineStr">
         <is>
           <t>RESULT</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="12" t="inlineStr">
-        <is>
-          <t>Before: 102 of 198 cells are more than 5% out, worst 51.1%, mean 9.7%.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>After: NO cell above 5%, worst 3.6%, mean 0.94% across all 198 cells (1.11% if measured only at each cohort-s latest month, which is the figure quoted in the RCA document).</t>
+          <t>Before: 102 of 198 cells are more than 5% out, worst 51.1%, mean 9.7%.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
         <is>
+          <t>After: NO cell above 5%, worst 3.6%, mean 0.94% across all 198 cells (1.11% if measured only at each cohort-s latest month, which is the figure quoted in the RCA document).</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
           <t>The attribution rule was chosen by scoring four variants across all eleven cohorts, not on March alone.</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="12" t="inlineStr"/>
-    </row>
     <row r="24">
-      <c r="A24" s="13" t="inlineStr">
+      <c r="A24" s="12" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="13" t="inlineStr">
         <is>
           <t>OPEN</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="12" t="inlineStr">
-        <is>
-          <t>Roughly 115 customers across the non-July cohorts are classified OTP by us and Subscription by the client. 0.10% of base. No exclusion rule can fix a classification difference.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>465 of the 936 July customers removed have a second order. Believed to be a second $0 promotional item rather than a real purchase. Unconfirmed.</t>
+          <t>Roughly 115 customers across the non-July cohorts are classified OTP by us and Subscription by the client. 0.10% of base. No exclusion rule can fix a classification difference.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
         <is>
-          <t>LineItemMaster currently adds refunded shipping on return rows instead of subtracting it - an upstream sign error raised with the DE team. The After tab is built with that shipping ignored, which matches the OrderLinesMaster build. When the fix lands, expect March M4 to move about -425 (OTP) and -1,046 (Subscription).</t>
+          <t>465 of the 936 July customers removed have a second order. Believed to be a second $0 promotional item rather than a real purchase. Unconfirmed.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>LineItemMaster currently adds refunded shipping on return rows instead of subtracting it - an upstream sign error raised with the DE team. The After tab is built with that shipping ignored, which matches the OrderLinesMaster build. When the fix lands, expect March M4 to move about -425 (OTP) and -1,046 (Subscription).</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="12" t="inlineStr">
         <is>
           <t>Nobody has confirmed which model the live dashboard reads, and the published figures these were originally checked against came from our own brief, not a dashboard read.</t>
         </is>

--- a/equip_rca/Equip cohort validation - before vs after.xlsx
+++ b/equip_rca/Equip cohort validation - before vs after.xlsx
@@ -127,23 +127,36 @@
   </cellStyles>
   <dxfs count="3">
     <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FF912018"/>
+        <sz val="10"/>
+      </font>
       <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00FEE4E2"/>
+        <patternFill>
+          <bgColor rgb="FFFEE4E2"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <color rgb="FF93370D"/>
+        <sz val="10"/>
+      </font>
       <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00FEF0C7"/>
+        <patternFill>
+          <bgColor rgb="FFFEF0C7"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <color rgb="FF05603A"/>
+        <sz val="10"/>
+      </font>
       <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00D1FADF"/>
+        <patternFill>
+          <bgColor rgb="FFD1FADF"/>
         </patternFill>
       </fill>
     </dxf>

--- a/equip_rca/Equip cohort validation - before vs after.xlsx
+++ b/equip_rca/Equip cohort validation - before vs after.xlsx
@@ -1476,7 +1476,7 @@
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>% Diff  =  (ours − client) ÷ client      [green ≤2%  ·  amber 2–5%  ·  red &gt;5%]</t>
+          <t>% Diff  =  (ours − client) ÷ ours      [green ≤2%  ·  amber 2–5%  ·  red &gt;5%]</t>
         </is>
       </c>
     </row>
@@ -1554,51 +1554,51 @@
         </is>
       </c>
       <c r="B35" s="10">
-        <f>IFERROR((B7-B21)/B21,"")</f>
+        <f>IFERROR((B7-B21)/B7,"")</f>
         <v/>
       </c>
       <c r="C35" s="10">
-        <f>IFERROR((C7-C21)/C21,"")</f>
+        <f>IFERROR((C7-C21)/C7,"")</f>
         <v/>
       </c>
       <c r="D35" s="10">
-        <f>IFERROR((D7-D21)/D21,"")</f>
+        <f>IFERROR((D7-D21)/D7,"")</f>
         <v/>
       </c>
       <c r="E35" s="10">
-        <f>IFERROR((E7-E21)/E21,"")</f>
+        <f>IFERROR((E7-E21)/E7,"")</f>
         <v/>
       </c>
       <c r="F35" s="10">
-        <f>IFERROR((F7-F21)/F21,"")</f>
+        <f>IFERROR((F7-F21)/F7,"")</f>
         <v/>
       </c>
       <c r="G35" s="10">
-        <f>IFERROR((G7-G21)/G21,"")</f>
+        <f>IFERROR((G7-G21)/G7,"")</f>
         <v/>
       </c>
       <c r="H35" s="10">
-        <f>IFERROR((H7-H21)/H21,"")</f>
+        <f>IFERROR((H7-H21)/H7,"")</f>
         <v/>
       </c>
       <c r="I35" s="10">
-        <f>IFERROR((I7-I21)/I21,"")</f>
+        <f>IFERROR((I7-I21)/I7,"")</f>
         <v/>
       </c>
       <c r="J35" s="10">
-        <f>IFERROR((J7-J21)/J21,"")</f>
+        <f>IFERROR((J7-J21)/J7,"")</f>
         <v/>
       </c>
       <c r="K35" s="10">
-        <f>IFERROR((K7-K21)/K21,"")</f>
+        <f>IFERROR((K7-K21)/K7,"")</f>
         <v/>
       </c>
       <c r="L35" s="10">
-        <f>IFERROR((L7-L21)/L21,"")</f>
+        <f>IFERROR((L7-L21)/L7,"")</f>
         <v/>
       </c>
       <c r="M35" s="10">
-        <f>IFERROR((M7-M21)/M21,"")</f>
+        <f>IFERROR((M7-M21)/M7,"")</f>
         <v/>
       </c>
     </row>
@@ -1609,51 +1609,51 @@
         </is>
       </c>
       <c r="B36" s="10">
-        <f>IFERROR((B8-B22)/B22,"")</f>
+        <f>IFERROR((B8-B22)/B8,"")</f>
         <v/>
       </c>
       <c r="C36" s="10">
-        <f>IFERROR((C8-C22)/C22,"")</f>
+        <f>IFERROR((C8-C22)/C8,"")</f>
         <v/>
       </c>
       <c r="D36" s="10">
-        <f>IFERROR((D8-D22)/D22,"")</f>
+        <f>IFERROR((D8-D22)/D8,"")</f>
         <v/>
       </c>
       <c r="E36" s="10">
-        <f>IFERROR((E8-E22)/E22,"")</f>
+        <f>IFERROR((E8-E22)/E8,"")</f>
         <v/>
       </c>
       <c r="F36" s="10">
-        <f>IFERROR((F8-F22)/F22,"")</f>
+        <f>IFERROR((F8-F22)/F8,"")</f>
         <v/>
       </c>
       <c r="G36" s="10">
-        <f>IFERROR((G8-G22)/G22,"")</f>
+        <f>IFERROR((G8-G22)/G8,"")</f>
         <v/>
       </c>
       <c r="H36" s="10">
-        <f>IFERROR((H8-H22)/H22,"")</f>
+        <f>IFERROR((H8-H22)/H8,"")</f>
         <v/>
       </c>
       <c r="I36" s="10">
-        <f>IFERROR((I8-I22)/I22,"")</f>
+        <f>IFERROR((I8-I22)/I8,"")</f>
         <v/>
       </c>
       <c r="J36" s="10">
-        <f>IFERROR((J8-J22)/J22,"")</f>
+        <f>IFERROR((J8-J22)/J8,"")</f>
         <v/>
       </c>
       <c r="K36" s="10">
-        <f>IFERROR((K8-K22)/K22,"")</f>
+        <f>IFERROR((K8-K22)/K8,"")</f>
         <v/>
       </c>
       <c r="L36" s="10">
-        <f>IFERROR((L8-L22)/L22,"")</f>
+        <f>IFERROR((L8-L22)/L8,"")</f>
         <v/>
       </c>
       <c r="M36" s="10">
-        <f>IFERROR((M8-M22)/M22,"")</f>
+        <f>IFERROR((M8-M22)/M8,"")</f>
         <v/>
       </c>
     </row>
@@ -1664,51 +1664,51 @@
         </is>
       </c>
       <c r="B37" s="10">
-        <f>IFERROR((B9-B23)/B23,"")</f>
+        <f>IFERROR((B9-B23)/B9,"")</f>
         <v/>
       </c>
       <c r="C37" s="10">
-        <f>IFERROR((C9-C23)/C23,"")</f>
+        <f>IFERROR((C9-C23)/C9,"")</f>
         <v/>
       </c>
       <c r="D37" s="10">
-        <f>IFERROR((D9-D23)/D23,"")</f>
+        <f>IFERROR((D9-D23)/D9,"")</f>
         <v/>
       </c>
       <c r="E37" s="10">
-        <f>IFERROR((E9-E23)/E23,"")</f>
+        <f>IFERROR((E9-E23)/E9,"")</f>
         <v/>
       </c>
       <c r="F37" s="10">
-        <f>IFERROR((F9-F23)/F23,"")</f>
+        <f>IFERROR((F9-F23)/F9,"")</f>
         <v/>
       </c>
       <c r="G37" s="10">
-        <f>IFERROR((G9-G23)/G23,"")</f>
+        <f>IFERROR((G9-G23)/G9,"")</f>
         <v/>
       </c>
       <c r="H37" s="10">
-        <f>IFERROR((H9-H23)/H23,"")</f>
+        <f>IFERROR((H9-H23)/H9,"")</f>
         <v/>
       </c>
       <c r="I37" s="10">
-        <f>IFERROR((I9-I23)/I23,"")</f>
+        <f>IFERROR((I9-I23)/I9,"")</f>
         <v/>
       </c>
       <c r="J37" s="10">
-        <f>IFERROR((J9-J23)/J23,"")</f>
+        <f>IFERROR((J9-J23)/J9,"")</f>
         <v/>
       </c>
       <c r="K37" s="10">
-        <f>IFERROR((K9-K23)/K23,"")</f>
+        <f>IFERROR((K9-K23)/K9,"")</f>
         <v/>
       </c>
       <c r="L37" s="10">
-        <f>IFERROR((L9-L23)/L23,"")</f>
+        <f>IFERROR((L9-L23)/L9,"")</f>
         <v/>
       </c>
       <c r="M37" s="10">
-        <f>IFERROR((M9-M23)/M23,"")</f>
+        <f>IFERROR((M9-M23)/M9,"")</f>
         <v/>
       </c>
     </row>
@@ -1719,51 +1719,51 @@
         </is>
       </c>
       <c r="B38" s="10">
-        <f>IFERROR((B10-B24)/B24,"")</f>
+        <f>IFERROR((B10-B24)/B10,"")</f>
         <v/>
       </c>
       <c r="C38" s="10">
-        <f>IFERROR((C10-C24)/C24,"")</f>
+        <f>IFERROR((C10-C24)/C10,"")</f>
         <v/>
       </c>
       <c r="D38" s="10">
-        <f>IFERROR((D10-D24)/D24,"")</f>
+        <f>IFERROR((D10-D24)/D10,"")</f>
         <v/>
       </c>
       <c r="E38" s="10">
-        <f>IFERROR((E10-E24)/E24,"")</f>
+        <f>IFERROR((E10-E24)/E10,"")</f>
         <v/>
       </c>
       <c r="F38" s="10">
-        <f>IFERROR((F10-F24)/F24,"")</f>
+        <f>IFERROR((F10-F24)/F10,"")</f>
         <v/>
       </c>
       <c r="G38" s="10">
-        <f>IFERROR((G10-G24)/G24,"")</f>
+        <f>IFERROR((G10-G24)/G10,"")</f>
         <v/>
       </c>
       <c r="H38" s="10">
-        <f>IFERROR((H10-H24)/H24,"")</f>
+        <f>IFERROR((H10-H24)/H10,"")</f>
         <v/>
       </c>
       <c r="I38" s="10">
-        <f>IFERROR((I10-I24)/I24,"")</f>
+        <f>IFERROR((I10-I24)/I10,"")</f>
         <v/>
       </c>
       <c r="J38" s="10">
-        <f>IFERROR((J10-J24)/J24,"")</f>
+        <f>IFERROR((J10-J24)/J10,"")</f>
         <v/>
       </c>
       <c r="K38" s="10">
-        <f>IFERROR((K10-K24)/K24,"")</f>
+        <f>IFERROR((K10-K24)/K10,"")</f>
         <v/>
       </c>
       <c r="L38" s="10">
-        <f>IFERROR((L10-L24)/L24,"")</f>
+        <f>IFERROR((L10-L24)/L10,"")</f>
         <v/>
       </c>
       <c r="M38" s="10">
-        <f>IFERROR((M10-M24)/M24,"")</f>
+        <f>IFERROR((M10-M24)/M10,"")</f>
         <v/>
       </c>
     </row>
@@ -1774,51 +1774,51 @@
         </is>
       </c>
       <c r="B39" s="10">
-        <f>IFERROR((B11-B25)/B25,"")</f>
+        <f>IFERROR((B11-B25)/B11,"")</f>
         <v/>
       </c>
       <c r="C39" s="10">
-        <f>IFERROR((C11-C25)/C25,"")</f>
+        <f>IFERROR((C11-C25)/C11,"")</f>
         <v/>
       </c>
       <c r="D39" s="10">
-        <f>IFERROR((D11-D25)/D25,"")</f>
+        <f>IFERROR((D11-D25)/D11,"")</f>
         <v/>
       </c>
       <c r="E39" s="10">
-        <f>IFERROR((E11-E25)/E25,"")</f>
+        <f>IFERROR((E11-E25)/E11,"")</f>
         <v/>
       </c>
       <c r="F39" s="10">
-        <f>IFERROR((F11-F25)/F25,"")</f>
+        <f>IFERROR((F11-F25)/F11,"")</f>
         <v/>
       </c>
       <c r="G39" s="10">
-        <f>IFERROR((G11-G25)/G25,"")</f>
+        <f>IFERROR((G11-G25)/G11,"")</f>
         <v/>
       </c>
       <c r="H39" s="10">
-        <f>IFERROR((H11-H25)/H25,"")</f>
+        <f>IFERROR((H11-H25)/H11,"")</f>
         <v/>
       </c>
       <c r="I39" s="10">
-        <f>IFERROR((I11-I25)/I25,"")</f>
+        <f>IFERROR((I11-I25)/I11,"")</f>
         <v/>
       </c>
       <c r="J39" s="10">
-        <f>IFERROR((J11-J25)/J25,"")</f>
+        <f>IFERROR((J11-J25)/J11,"")</f>
         <v/>
       </c>
       <c r="K39" s="10">
-        <f>IFERROR((K11-K25)/K25,"")</f>
+        <f>IFERROR((K11-K25)/K11,"")</f>
         <v/>
       </c>
       <c r="L39" s="10">
-        <f>IFERROR((L11-L25)/L25,"")</f>
+        <f>IFERROR((L11-L25)/L11,"")</f>
         <v/>
       </c>
       <c r="M39" s="10">
-        <f>IFERROR((M11-M25)/M25,"")</f>
+        <f>IFERROR((M11-M25)/M11,"")</f>
         <v/>
       </c>
     </row>
@@ -1829,51 +1829,51 @@
         </is>
       </c>
       <c r="B40" s="10">
-        <f>IFERROR((B12-B26)/B26,"")</f>
+        <f>IFERROR((B12-B26)/B12,"")</f>
         <v/>
       </c>
       <c r="C40" s="10">
-        <f>IFERROR((C12-C26)/C26,"")</f>
+        <f>IFERROR((C12-C26)/C12,"")</f>
         <v/>
       </c>
       <c r="D40" s="10">
-        <f>IFERROR((D12-D26)/D26,"")</f>
+        <f>IFERROR((D12-D26)/D12,"")</f>
         <v/>
       </c>
       <c r="E40" s="10">
-        <f>IFERROR((E12-E26)/E26,"")</f>
+        <f>IFERROR((E12-E26)/E12,"")</f>
         <v/>
       </c>
       <c r="F40" s="10">
-        <f>IFERROR((F12-F26)/F26,"")</f>
+        <f>IFERROR((F12-F26)/F12,"")</f>
         <v/>
       </c>
       <c r="G40" s="10">
-        <f>IFERROR((G12-G26)/G26,"")</f>
+        <f>IFERROR((G12-G26)/G12,"")</f>
         <v/>
       </c>
       <c r="H40" s="10">
-        <f>IFERROR((H12-H26)/H26,"")</f>
+        <f>IFERROR((H12-H26)/H12,"")</f>
         <v/>
       </c>
       <c r="I40" s="10">
-        <f>IFERROR((I12-I26)/I26,"")</f>
+        <f>IFERROR((I12-I26)/I12,"")</f>
         <v/>
       </c>
       <c r="J40" s="10">
-        <f>IFERROR((J12-J26)/J26,"")</f>
+        <f>IFERROR((J12-J26)/J12,"")</f>
         <v/>
       </c>
       <c r="K40" s="10">
-        <f>IFERROR((K12-K26)/K26,"")</f>
+        <f>IFERROR((K12-K26)/K12,"")</f>
         <v/>
       </c>
       <c r="L40" s="10">
-        <f>IFERROR((L12-L26)/L26,"")</f>
+        <f>IFERROR((L12-L26)/L12,"")</f>
         <v/>
       </c>
       <c r="M40" s="10">
-        <f>IFERROR((M12-M26)/M26,"")</f>
+        <f>IFERROR((M12-M26)/M12,"")</f>
         <v/>
       </c>
     </row>
@@ -1884,51 +1884,51 @@
         </is>
       </c>
       <c r="B41" s="10">
-        <f>IFERROR((B13-B27)/B27,"")</f>
+        <f>IFERROR((B13-B27)/B13,"")</f>
         <v/>
       </c>
       <c r="C41" s="10">
-        <f>IFERROR((C13-C27)/C27,"")</f>
+        <f>IFERROR((C13-C27)/C13,"")</f>
         <v/>
       </c>
       <c r="D41" s="10">
-        <f>IFERROR((D13-D27)/D27,"")</f>
+        <f>IFERROR((D13-D27)/D13,"")</f>
         <v/>
       </c>
       <c r="E41" s="10">
-        <f>IFERROR((E13-E27)/E27,"")</f>
+        <f>IFERROR((E13-E27)/E13,"")</f>
         <v/>
       </c>
       <c r="F41" s="10">
-        <f>IFERROR((F13-F27)/F27,"")</f>
+        <f>IFERROR((F13-F27)/F13,"")</f>
         <v/>
       </c>
       <c r="G41" s="10">
-        <f>IFERROR((G13-G27)/G27,"")</f>
+        <f>IFERROR((G13-G27)/G13,"")</f>
         <v/>
       </c>
       <c r="H41" s="10">
-        <f>IFERROR((H13-H27)/H27,"")</f>
+        <f>IFERROR((H13-H27)/H13,"")</f>
         <v/>
       </c>
       <c r="I41" s="10">
-        <f>IFERROR((I13-I27)/I27,"")</f>
+        <f>IFERROR((I13-I27)/I13,"")</f>
         <v/>
       </c>
       <c r="J41" s="10">
-        <f>IFERROR((J13-J27)/J27,"")</f>
+        <f>IFERROR((J13-J27)/J13,"")</f>
         <v/>
       </c>
       <c r="K41" s="10">
-        <f>IFERROR((K13-K27)/K27,"")</f>
+        <f>IFERROR((K13-K27)/K13,"")</f>
         <v/>
       </c>
       <c r="L41" s="10">
-        <f>IFERROR((L13-L27)/L27,"")</f>
+        <f>IFERROR((L13-L27)/L13,"")</f>
         <v/>
       </c>
       <c r="M41" s="10">
-        <f>IFERROR((M13-M27)/M27,"")</f>
+        <f>IFERROR((M13-M27)/M13,"")</f>
         <v/>
       </c>
     </row>
@@ -1939,51 +1939,51 @@
         </is>
       </c>
       <c r="B42" s="10">
-        <f>IFERROR((B14-B28)/B28,"")</f>
+        <f>IFERROR((B14-B28)/B14,"")</f>
         <v/>
       </c>
       <c r="C42" s="10">
-        <f>IFERROR((C14-C28)/C28,"")</f>
+        <f>IFERROR((C14-C28)/C14,"")</f>
         <v/>
       </c>
       <c r="D42" s="10">
-        <f>IFERROR((D14-D28)/D28,"")</f>
+        <f>IFERROR((D14-D28)/D14,"")</f>
         <v/>
       </c>
       <c r="E42" s="10">
-        <f>IFERROR((E14-E28)/E28,"")</f>
+        <f>IFERROR((E14-E28)/E14,"")</f>
         <v/>
       </c>
       <c r="F42" s="10">
-        <f>IFERROR((F14-F28)/F28,"")</f>
+        <f>IFERROR((F14-F28)/F14,"")</f>
         <v/>
       </c>
       <c r="G42" s="10">
-        <f>IFERROR((G14-G28)/G28,"")</f>
+        <f>IFERROR((G14-G28)/G14,"")</f>
         <v/>
       </c>
       <c r="H42" s="10">
-        <f>IFERROR((H14-H28)/H28,"")</f>
+        <f>IFERROR((H14-H28)/H14,"")</f>
         <v/>
       </c>
       <c r="I42" s="10">
-        <f>IFERROR((I14-I28)/I28,"")</f>
+        <f>IFERROR((I14-I28)/I14,"")</f>
         <v/>
       </c>
       <c r="J42" s="10">
-        <f>IFERROR((J14-J28)/J28,"")</f>
+        <f>IFERROR((J14-J28)/J14,"")</f>
         <v/>
       </c>
       <c r="K42" s="10">
-        <f>IFERROR((K14-K28)/K28,"")</f>
+        <f>IFERROR((K14-K28)/K14,"")</f>
         <v/>
       </c>
       <c r="L42" s="10">
-        <f>IFERROR((L14-L28)/L28,"")</f>
+        <f>IFERROR((L14-L28)/L14,"")</f>
         <v/>
       </c>
       <c r="M42" s="10">
-        <f>IFERROR((M14-M28)/M28,"")</f>
+        <f>IFERROR((M14-M28)/M14,"")</f>
         <v/>
       </c>
     </row>
@@ -1994,51 +1994,51 @@
         </is>
       </c>
       <c r="B43" s="10">
-        <f>IFERROR((B15-B29)/B29,"")</f>
+        <f>IFERROR((B15-B29)/B15,"")</f>
         <v/>
       </c>
       <c r="C43" s="10">
-        <f>IFERROR((C15-C29)/C29,"")</f>
+        <f>IFERROR((C15-C29)/C15,"")</f>
         <v/>
       </c>
       <c r="D43" s="10">
-        <f>IFERROR((D15-D29)/D29,"")</f>
+        <f>IFERROR((D15-D29)/D15,"")</f>
         <v/>
       </c>
       <c r="E43" s="10">
-        <f>IFERROR((E15-E29)/E29,"")</f>
+        <f>IFERROR((E15-E29)/E15,"")</f>
         <v/>
       </c>
       <c r="F43" s="10">
-        <f>IFERROR((F15-F29)/F29,"")</f>
+        <f>IFERROR((F15-F29)/F15,"")</f>
         <v/>
       </c>
       <c r="G43" s="10">
-        <f>IFERROR((G15-G29)/G29,"")</f>
+        <f>IFERROR((G15-G29)/G15,"")</f>
         <v/>
       </c>
       <c r="H43" s="10">
-        <f>IFERROR((H15-H29)/H29,"")</f>
+        <f>IFERROR((H15-H29)/H15,"")</f>
         <v/>
       </c>
       <c r="I43" s="10">
-        <f>IFERROR((I15-I29)/I29,"")</f>
+        <f>IFERROR((I15-I29)/I15,"")</f>
         <v/>
       </c>
       <c r="J43" s="10">
-        <f>IFERROR((J15-J29)/J29,"")</f>
+        <f>IFERROR((J15-J29)/J15,"")</f>
         <v/>
       </c>
       <c r="K43" s="10">
-        <f>IFERROR((K15-K29)/K29,"")</f>
+        <f>IFERROR((K15-K29)/K15,"")</f>
         <v/>
       </c>
       <c r="L43" s="10">
-        <f>IFERROR((L15-L29)/L29,"")</f>
+        <f>IFERROR((L15-L29)/L15,"")</f>
         <v/>
       </c>
       <c r="M43" s="10">
-        <f>IFERROR((M15-M29)/M29,"")</f>
+        <f>IFERROR((M15-M29)/M15,"")</f>
         <v/>
       </c>
     </row>
@@ -2049,51 +2049,51 @@
         </is>
       </c>
       <c r="B44" s="10">
-        <f>IFERROR((B16-B30)/B30,"")</f>
+        <f>IFERROR((B16-B30)/B16,"")</f>
         <v/>
       </c>
       <c r="C44" s="10">
-        <f>IFERROR((C16-C30)/C30,"")</f>
+        <f>IFERROR((C16-C30)/C16,"")</f>
         <v/>
       </c>
       <c r="D44" s="10">
-        <f>IFERROR((D16-D30)/D30,"")</f>
+        <f>IFERROR((D16-D30)/D16,"")</f>
         <v/>
       </c>
       <c r="E44" s="10">
-        <f>IFERROR((E16-E30)/E30,"")</f>
+        <f>IFERROR((E16-E30)/E16,"")</f>
         <v/>
       </c>
       <c r="F44" s="10">
-        <f>IFERROR((F16-F30)/F30,"")</f>
+        <f>IFERROR((F16-F30)/F16,"")</f>
         <v/>
       </c>
       <c r="G44" s="10">
-        <f>IFERROR((G16-G30)/G30,"")</f>
+        <f>IFERROR((G16-G30)/G16,"")</f>
         <v/>
       </c>
       <c r="H44" s="10">
-        <f>IFERROR((H16-H30)/H30,"")</f>
+        <f>IFERROR((H16-H30)/H16,"")</f>
         <v/>
       </c>
       <c r="I44" s="10">
-        <f>IFERROR((I16-I30)/I30,"")</f>
+        <f>IFERROR((I16-I30)/I16,"")</f>
         <v/>
       </c>
       <c r="J44" s="10">
-        <f>IFERROR((J16-J30)/J30,"")</f>
+        <f>IFERROR((J16-J30)/J16,"")</f>
         <v/>
       </c>
       <c r="K44" s="10">
-        <f>IFERROR((K16-K30)/K30,"")</f>
+        <f>IFERROR((K16-K30)/K16,"")</f>
         <v/>
       </c>
       <c r="L44" s="10">
-        <f>IFERROR((L16-L30)/L30,"")</f>
+        <f>IFERROR((L16-L30)/L16,"")</f>
         <v/>
       </c>
       <c r="M44" s="10">
-        <f>IFERROR((M16-M30)/M30,"")</f>
+        <f>IFERROR((M16-M30)/M16,"")</f>
         <v/>
       </c>
     </row>
@@ -2104,51 +2104,51 @@
         </is>
       </c>
       <c r="B45" s="10">
-        <f>IFERROR((B17-B31)/B31,"")</f>
+        <f>IFERROR((B17-B31)/B17,"")</f>
         <v/>
       </c>
       <c r="C45" s="10">
-        <f>IFERROR((C17-C31)/C31,"")</f>
+        <f>IFERROR((C17-C31)/C17,"")</f>
         <v/>
       </c>
       <c r="D45" s="10">
-        <f>IFERROR((D17-D31)/D31,"")</f>
+        <f>IFERROR((D17-D31)/D17,"")</f>
         <v/>
       </c>
       <c r="E45" s="10">
-        <f>IFERROR((E17-E31)/E31,"")</f>
+        <f>IFERROR((E17-E31)/E17,"")</f>
         <v/>
       </c>
       <c r="F45" s="10">
-        <f>IFERROR((F17-F31)/F31,"")</f>
+        <f>IFERROR((F17-F31)/F17,"")</f>
         <v/>
       </c>
       <c r="G45" s="10">
-        <f>IFERROR((G17-G31)/G31,"")</f>
+        <f>IFERROR((G17-G31)/G17,"")</f>
         <v/>
       </c>
       <c r="H45" s="10">
-        <f>IFERROR((H17-H31)/H31,"")</f>
+        <f>IFERROR((H17-H31)/H17,"")</f>
         <v/>
       </c>
       <c r="I45" s="10">
-        <f>IFERROR((I17-I31)/I31,"")</f>
+        <f>IFERROR((I17-I31)/I17,"")</f>
         <v/>
       </c>
       <c r="J45" s="10">
-        <f>IFERROR((J17-J31)/J31,"")</f>
+        <f>IFERROR((J17-J31)/J17,"")</f>
         <v/>
       </c>
       <c r="K45" s="10">
-        <f>IFERROR((K17-K31)/K31,"")</f>
+        <f>IFERROR((K17-K31)/K17,"")</f>
         <v/>
       </c>
       <c r="L45" s="10">
-        <f>IFERROR((L17-L31)/L31,"")</f>
+        <f>IFERROR((L17-L31)/L17,"")</f>
         <v/>
       </c>
       <c r="M45" s="10">
-        <f>IFERROR((M17-M31)/M31,"")</f>
+        <f>IFERROR((M17-M31)/M17,"")</f>
         <v/>
       </c>
     </row>
@@ -3074,7 +3074,7 @@
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>% Diff  =  (ours − client) ÷ client      [green ≤2%  ·  amber 2–5%  ·  red &gt;5%]</t>
+          <t>% Diff  =  (ours − client) ÷ ours      [green ≤2%  ·  amber 2–5%  ·  red &gt;5%]</t>
         </is>
       </c>
     </row>
@@ -3152,51 +3152,51 @@
         </is>
       </c>
       <c r="B79" s="10">
-        <f>IFERROR((B51-B65)/B65,"")</f>
+        <f>IFERROR((B51-B65)/B51,"")</f>
         <v/>
       </c>
       <c r="C79" s="10">
-        <f>IFERROR((C51-C65)/C65,"")</f>
+        <f>IFERROR((C51-C65)/C51,"")</f>
         <v/>
       </c>
       <c r="D79" s="10">
-        <f>IFERROR((D51-D65)/D65,"")</f>
+        <f>IFERROR((D51-D65)/D51,"")</f>
         <v/>
       </c>
       <c r="E79" s="10">
-        <f>IFERROR((E51-E65)/E65,"")</f>
+        <f>IFERROR((E51-E65)/E51,"")</f>
         <v/>
       </c>
       <c r="F79" s="10">
-        <f>IFERROR((F51-F65)/F65,"")</f>
+        <f>IFERROR((F51-F65)/F51,"")</f>
         <v/>
       </c>
       <c r="G79" s="10">
-        <f>IFERROR((G51-G65)/G65,"")</f>
+        <f>IFERROR((G51-G65)/G51,"")</f>
         <v/>
       </c>
       <c r="H79" s="10">
-        <f>IFERROR((H51-H65)/H65,"")</f>
+        <f>IFERROR((H51-H65)/H51,"")</f>
         <v/>
       </c>
       <c r="I79" s="10">
-        <f>IFERROR((I51-I65)/I65,"")</f>
+        <f>IFERROR((I51-I65)/I51,"")</f>
         <v/>
       </c>
       <c r="J79" s="10">
-        <f>IFERROR((J51-J65)/J65,"")</f>
+        <f>IFERROR((J51-J65)/J51,"")</f>
         <v/>
       </c>
       <c r="K79" s="10">
-        <f>IFERROR((K51-K65)/K65,"")</f>
+        <f>IFERROR((K51-K65)/K51,"")</f>
         <v/>
       </c>
       <c r="L79" s="10">
-        <f>IFERROR((L51-L65)/L65,"")</f>
+        <f>IFERROR((L51-L65)/L51,"")</f>
         <v/>
       </c>
       <c r="M79" s="10">
-        <f>IFERROR((M51-M65)/M65,"")</f>
+        <f>IFERROR((M51-M65)/M51,"")</f>
         <v/>
       </c>
     </row>
@@ -3207,51 +3207,51 @@
         </is>
       </c>
       <c r="B80" s="10">
-        <f>IFERROR((B52-B66)/B66,"")</f>
+        <f>IFERROR((B52-B66)/B52,"")</f>
         <v/>
       </c>
       <c r="C80" s="10">
-        <f>IFERROR((C52-C66)/C66,"")</f>
+        <f>IFERROR((C52-C66)/C52,"")</f>
         <v/>
       </c>
       <c r="D80" s="10">
-        <f>IFERROR((D52-D66)/D66,"")</f>
+        <f>IFERROR((D52-D66)/D52,"")</f>
         <v/>
       </c>
       <c r="E80" s="10">
-        <f>IFERROR((E52-E66)/E66,"")</f>
+        <f>IFERROR((E52-E66)/E52,"")</f>
         <v/>
       </c>
       <c r="F80" s="10">
-        <f>IFERROR((F52-F66)/F66,"")</f>
+        <f>IFERROR((F52-F66)/F52,"")</f>
         <v/>
       </c>
       <c r="G80" s="10">
-        <f>IFERROR((G52-G66)/G66,"")</f>
+        <f>IFERROR((G52-G66)/G52,"")</f>
         <v/>
       </c>
       <c r="H80" s="10">
-        <f>IFERROR((H52-H66)/H66,"")</f>
+        <f>IFERROR((H52-H66)/H52,"")</f>
         <v/>
       </c>
       <c r="I80" s="10">
-        <f>IFERROR((I52-I66)/I66,"")</f>
+        <f>IFERROR((I52-I66)/I52,"")</f>
         <v/>
       </c>
       <c r="J80" s="10">
-        <f>IFERROR((J52-J66)/J66,"")</f>
+        <f>IFERROR((J52-J66)/J52,"")</f>
         <v/>
       </c>
       <c r="K80" s="10">
-        <f>IFERROR((K52-K66)/K66,"")</f>
+        <f>IFERROR((K52-K66)/K52,"")</f>
         <v/>
       </c>
       <c r="L80" s="10">
-        <f>IFERROR((L52-L66)/L66,"")</f>
+        <f>IFERROR((L52-L66)/L52,"")</f>
         <v/>
       </c>
       <c r="M80" s="10">
-        <f>IFERROR((M52-M66)/M66,"")</f>
+        <f>IFERROR((M52-M66)/M52,"")</f>
         <v/>
       </c>
     </row>
@@ -3262,51 +3262,51 @@
         </is>
       </c>
       <c r="B81" s="10">
-        <f>IFERROR((B53-B67)/B67,"")</f>
+        <f>IFERROR((B53-B67)/B53,"")</f>
         <v/>
       </c>
       <c r="C81" s="10">
-        <f>IFERROR((C53-C67)/C67,"")</f>
+        <f>IFERROR((C53-C67)/C53,"")</f>
         <v/>
       </c>
       <c r="D81" s="10">
-        <f>IFERROR((D53-D67)/D67,"")</f>
+        <f>IFERROR((D53-D67)/D53,"")</f>
         <v/>
       </c>
       <c r="E81" s="10">
-        <f>IFERROR((E53-E67)/E67,"")</f>
+        <f>IFERROR((E53-E67)/E53,"")</f>
         <v/>
       </c>
       <c r="F81" s="10">
-        <f>IFERROR((F53-F67)/F67,"")</f>
+        <f>IFERROR((F53-F67)/F53,"")</f>
         <v/>
       </c>
       <c r="G81" s="10">
-        <f>IFERROR((G53-G67)/G67,"")</f>
+        <f>IFERROR((G53-G67)/G53,"")</f>
         <v/>
       </c>
       <c r="H81" s="10">
-        <f>IFERROR((H53-H67)/H67,"")</f>
+        <f>IFERROR((H53-H67)/H53,"")</f>
         <v/>
       </c>
       <c r="I81" s="10">
-        <f>IFERROR((I53-I67)/I67,"")</f>
+        <f>IFERROR((I53-I67)/I53,"")</f>
         <v/>
       </c>
       <c r="J81" s="10">
-        <f>IFERROR((J53-J67)/J67,"")</f>
+        <f>IFERROR((J53-J67)/J53,"")</f>
         <v/>
       </c>
       <c r="K81" s="10">
-        <f>IFERROR((K53-K67)/K67,"")</f>
+        <f>IFERROR((K53-K67)/K53,"")</f>
         <v/>
       </c>
       <c r="L81" s="10">
-        <f>IFERROR((L53-L67)/L67,"")</f>
+        <f>IFERROR((L53-L67)/L53,"")</f>
         <v/>
       </c>
       <c r="M81" s="10">
-        <f>IFERROR((M53-M67)/M67,"")</f>
+        <f>IFERROR((M53-M67)/M53,"")</f>
         <v/>
       </c>
     </row>
@@ -3317,51 +3317,51 @@
         </is>
       </c>
       <c r="B82" s="10">
-        <f>IFERROR((B54-B68)/B68,"")</f>
+        <f>IFERROR((B54-B68)/B54,"")</f>
         <v/>
       </c>
       <c r="C82" s="10">
-        <f>IFERROR((C54-C68)/C68,"")</f>
+        <f>IFERROR((C54-C68)/C54,"")</f>
         <v/>
       </c>
       <c r="D82" s="10">
-        <f>IFERROR((D54-D68)/D68,"")</f>
+        <f>IFERROR((D54-D68)/D54,"")</f>
         <v/>
       </c>
       <c r="E82" s="10">
-        <f>IFERROR((E54-E68)/E68,"")</f>
+        <f>IFERROR((E54-E68)/E54,"")</f>
         <v/>
       </c>
       <c r="F82" s="10">
-        <f>IFERROR((F54-F68)/F68,"")</f>
+        <f>IFERROR((F54-F68)/F54,"")</f>
         <v/>
       </c>
       <c r="G82" s="10">
-        <f>IFERROR((G54-G68)/G68,"")</f>
+        <f>IFERROR((G54-G68)/G54,"")</f>
         <v/>
       </c>
       <c r="H82" s="10">
-        <f>IFERROR((H54-H68)/H68,"")</f>
+        <f>IFERROR((H54-H68)/H54,"")</f>
         <v/>
       </c>
       <c r="I82" s="10">
-        <f>IFERROR((I54-I68)/I68,"")</f>
+        <f>IFERROR((I54-I68)/I54,"")</f>
         <v/>
       </c>
       <c r="J82" s="10">
-        <f>IFERROR((J54-J68)/J68,"")</f>
+        <f>IFERROR((J54-J68)/J54,"")</f>
         <v/>
       </c>
       <c r="K82" s="10">
-        <f>IFERROR((K54-K68)/K68,"")</f>
+        <f>IFERROR((K54-K68)/K54,"")</f>
         <v/>
       </c>
       <c r="L82" s="10">
-        <f>IFERROR((L54-L68)/L68,"")</f>
+        <f>IFERROR((L54-L68)/L54,"")</f>
         <v/>
       </c>
       <c r="M82" s="10">
-        <f>IFERROR((M54-M68)/M68,"")</f>
+        <f>IFERROR((M54-M68)/M54,"")</f>
         <v/>
       </c>
     </row>
@@ -3372,51 +3372,51 @@
         </is>
       </c>
       <c r="B83" s="10">
-        <f>IFERROR((B55-B69)/B69,"")</f>
+        <f>IFERROR((B55-B69)/B55,"")</f>
         <v/>
       </c>
       <c r="C83" s="10">
-        <f>IFERROR((C55-C69)/C69,"")</f>
+        <f>IFERROR((C55-C69)/C55,"")</f>
         <v/>
       </c>
       <c r="D83" s="10">
-        <f>IFERROR((D55-D69)/D69,"")</f>
+        <f>IFERROR((D55-D69)/D55,"")</f>
         <v/>
       </c>
       <c r="E83" s="10">
-        <f>IFERROR((E55-E69)/E69,"")</f>
+        <f>IFERROR((E55-E69)/E55,"")</f>
         <v/>
       </c>
       <c r="F83" s="10">
-        <f>IFERROR((F55-F69)/F69,"")</f>
+        <f>IFERROR((F55-F69)/F55,"")</f>
         <v/>
       </c>
       <c r="G83" s="10">
-        <f>IFERROR((G55-G69)/G69,"")</f>
+        <f>IFERROR((G55-G69)/G55,"")</f>
         <v/>
       </c>
       <c r="H83" s="10">
-        <f>IFERROR((H55-H69)/H69,"")</f>
+        <f>IFERROR((H55-H69)/H55,"")</f>
         <v/>
       </c>
       <c r="I83" s="10">
-        <f>IFERROR((I55-I69)/I69,"")</f>
+        <f>IFERROR((I55-I69)/I55,"")</f>
         <v/>
       </c>
       <c r="J83" s="10">
-        <f>IFERROR((J55-J69)/J69,"")</f>
+        <f>IFERROR((J55-J69)/J55,"")</f>
         <v/>
       </c>
       <c r="K83" s="10">
-        <f>IFERROR((K55-K69)/K69,"")</f>
+        <f>IFERROR((K55-K69)/K55,"")</f>
         <v/>
       </c>
       <c r="L83" s="10">
-        <f>IFERROR((L55-L69)/L69,"")</f>
+        <f>IFERROR((L55-L69)/L55,"")</f>
         <v/>
       </c>
       <c r="M83" s="10">
-        <f>IFERROR((M55-M69)/M69,"")</f>
+        <f>IFERROR((M55-M69)/M55,"")</f>
         <v/>
       </c>
     </row>
@@ -3427,51 +3427,51 @@
         </is>
       </c>
       <c r="B84" s="10">
-        <f>IFERROR((B56-B70)/B70,"")</f>
+        <f>IFERROR((B56-B70)/B56,"")</f>
         <v/>
       </c>
       <c r="C84" s="10">
-        <f>IFERROR((C56-C70)/C70,"")</f>
+        <f>IFERROR((C56-C70)/C56,"")</f>
         <v/>
       </c>
       <c r="D84" s="10">
-        <f>IFERROR((D56-D70)/D70,"")</f>
+        <f>IFERROR((D56-D70)/D56,"")</f>
         <v/>
       </c>
       <c r="E84" s="10">
-        <f>IFERROR((E56-E70)/E70,"")</f>
+        <f>IFERROR((E56-E70)/E56,"")</f>
         <v/>
       </c>
       <c r="F84" s="10">
-        <f>IFERROR((F56-F70)/F70,"")</f>
+        <f>IFERROR((F56-F70)/F56,"")</f>
         <v/>
       </c>
       <c r="G84" s="10">
-        <f>IFERROR((G56-G70)/G70,"")</f>
+        <f>IFERROR((G56-G70)/G56,"")</f>
         <v/>
       </c>
       <c r="H84" s="10">
-        <f>IFERROR((H56-H70)/H70,"")</f>
+        <f>IFERROR((H56-H70)/H56,"")</f>
         <v/>
       </c>
       <c r="I84" s="10">
-        <f>IFERROR((I56-I70)/I70,"")</f>
+        <f>IFERROR((I56-I70)/I56,"")</f>
         <v/>
       </c>
       <c r="J84" s="10">
-        <f>IFERROR((J56-J70)/J70,"")</f>
+        <f>IFERROR((J56-J70)/J56,"")</f>
         <v/>
       </c>
       <c r="K84" s="10">
-        <f>IFERROR((K56-K70)/K70,"")</f>
+        <f>IFERROR((K56-K70)/K56,"")</f>
         <v/>
       </c>
       <c r="L84" s="10">
-        <f>IFERROR((L56-L70)/L70,"")</f>
+        <f>IFERROR((L56-L70)/L56,"")</f>
         <v/>
       </c>
       <c r="M84" s="10">
-        <f>IFERROR((M56-M70)/M70,"")</f>
+        <f>IFERROR((M56-M70)/M56,"")</f>
         <v/>
       </c>
     </row>
@@ -3482,51 +3482,51 @@
         </is>
       </c>
       <c r="B85" s="10">
-        <f>IFERROR((B57-B71)/B71,"")</f>
+        <f>IFERROR((B57-B71)/B57,"")</f>
         <v/>
       </c>
       <c r="C85" s="10">
-        <f>IFERROR((C57-C71)/C71,"")</f>
+        <f>IFERROR((C57-C71)/C57,"")</f>
         <v/>
       </c>
       <c r="D85" s="10">
-        <f>IFERROR((D57-D71)/D71,"")</f>
+        <f>IFERROR((D57-D71)/D57,"")</f>
         <v/>
       </c>
       <c r="E85" s="10">
-        <f>IFERROR((E57-E71)/E71,"")</f>
+        <f>IFERROR((E57-E71)/E57,"")</f>
         <v/>
       </c>
       <c r="F85" s="10">
-        <f>IFERROR((F57-F71)/F71,"")</f>
+        <f>IFERROR((F57-F71)/F57,"")</f>
         <v/>
       </c>
       <c r="G85" s="10">
-        <f>IFERROR((G57-G71)/G71,"")</f>
+        <f>IFERROR((G57-G71)/G57,"")</f>
         <v/>
       </c>
       <c r="H85" s="10">
-        <f>IFERROR((H57-H71)/H71,"")</f>
+        <f>IFERROR((H57-H71)/H57,"")</f>
         <v/>
       </c>
       <c r="I85" s="10">
-        <f>IFERROR((I57-I71)/I71,"")</f>
+        <f>IFERROR((I57-I71)/I57,"")</f>
         <v/>
       </c>
       <c r="J85" s="10">
-        <f>IFERROR((J57-J71)/J71,"")</f>
+        <f>IFERROR((J57-J71)/J57,"")</f>
         <v/>
       </c>
       <c r="K85" s="10">
-        <f>IFERROR((K57-K71)/K71,"")</f>
+        <f>IFERROR((K57-K71)/K57,"")</f>
         <v/>
       </c>
       <c r="L85" s="10">
-        <f>IFERROR((L57-L71)/L71,"")</f>
+        <f>IFERROR((L57-L71)/L57,"")</f>
         <v/>
       </c>
       <c r="M85" s="10">
-        <f>IFERROR((M57-M71)/M71,"")</f>
+        <f>IFERROR((M57-M71)/M57,"")</f>
         <v/>
       </c>
     </row>
@@ -3537,51 +3537,51 @@
         </is>
       </c>
       <c r="B86" s="10">
-        <f>IFERROR((B58-B72)/B72,"")</f>
+        <f>IFERROR((B58-B72)/B58,"")</f>
         <v/>
       </c>
       <c r="C86" s="10">
-        <f>IFERROR((C58-C72)/C72,"")</f>
+        <f>IFERROR((C58-C72)/C58,"")</f>
         <v/>
       </c>
       <c r="D86" s="10">
-        <f>IFERROR((D58-D72)/D72,"")</f>
+        <f>IFERROR((D58-D72)/D58,"")</f>
         <v/>
       </c>
       <c r="E86" s="10">
-        <f>IFERROR((E58-E72)/E72,"")</f>
+        <f>IFERROR((E58-E72)/E58,"")</f>
         <v/>
       </c>
       <c r="F86" s="10">
-        <f>IFERROR((F58-F72)/F72,"")</f>
+        <f>IFERROR((F58-F72)/F58,"")</f>
         <v/>
       </c>
       <c r="G86" s="10">
-        <f>IFERROR((G58-G72)/G72,"")</f>
+        <f>IFERROR((G58-G72)/G58,"")</f>
         <v/>
       </c>
       <c r="H86" s="10">
-        <f>IFERROR((H58-H72)/H72,"")</f>
+        <f>IFERROR((H58-H72)/H58,"")</f>
         <v/>
       </c>
       <c r="I86" s="10">
-        <f>IFERROR((I58-I72)/I72,"")</f>
+        <f>IFERROR((I58-I72)/I58,"")</f>
         <v/>
       </c>
       <c r="J86" s="10">
-        <f>IFERROR((J58-J72)/J72,"")</f>
+        <f>IFERROR((J58-J72)/J58,"")</f>
         <v/>
       </c>
       <c r="K86" s="10">
-        <f>IFERROR((K58-K72)/K72,"")</f>
+        <f>IFERROR((K58-K72)/K58,"")</f>
         <v/>
       </c>
       <c r="L86" s="10">
-        <f>IFERROR((L58-L72)/L72,"")</f>
+        <f>IFERROR((L58-L72)/L58,"")</f>
         <v/>
       </c>
       <c r="M86" s="10">
-        <f>IFERROR((M58-M72)/M72,"")</f>
+        <f>IFERROR((M58-M72)/M58,"")</f>
         <v/>
       </c>
     </row>
@@ -3592,51 +3592,51 @@
         </is>
       </c>
       <c r="B87" s="10">
-        <f>IFERROR((B59-B73)/B73,"")</f>
+        <f>IFERROR((B59-B73)/B59,"")</f>
         <v/>
       </c>
       <c r="C87" s="10">
-        <f>IFERROR((C59-C73)/C73,"")</f>
+        <f>IFERROR((C59-C73)/C59,"")</f>
         <v/>
       </c>
       <c r="D87" s="10">
-        <f>IFERROR((D59-D73)/D73,"")</f>
+        <f>IFERROR((D59-D73)/D59,"")</f>
         <v/>
       </c>
       <c r="E87" s="10">
-        <f>IFERROR((E59-E73)/E73,"")</f>
+        <f>IFERROR((E59-E73)/E59,"")</f>
         <v/>
       </c>
       <c r="F87" s="10">
-        <f>IFERROR((F59-F73)/F73,"")</f>
+        <f>IFERROR((F59-F73)/F59,"")</f>
         <v/>
       </c>
       <c r="G87" s="10">
-        <f>IFERROR((G59-G73)/G73,"")</f>
+        <f>IFERROR((G59-G73)/G59,"")</f>
         <v/>
       </c>
       <c r="H87" s="10">
-        <f>IFERROR((H59-H73)/H73,"")</f>
+        <f>IFERROR((H59-H73)/H59,"")</f>
         <v/>
       </c>
       <c r="I87" s="10">
-        <f>IFERROR((I59-I73)/I73,"")</f>
+        <f>IFERROR((I59-I73)/I59,"")</f>
         <v/>
       </c>
       <c r="J87" s="10">
-        <f>IFERROR((J59-J73)/J73,"")</f>
+        <f>IFERROR((J59-J73)/J59,"")</f>
         <v/>
       </c>
       <c r="K87" s="10">
-        <f>IFERROR((K59-K73)/K73,"")</f>
+        <f>IFERROR((K59-K73)/K59,"")</f>
         <v/>
       </c>
       <c r="L87" s="10">
-        <f>IFERROR((L59-L73)/L73,"")</f>
+        <f>IFERROR((L59-L73)/L59,"")</f>
         <v/>
       </c>
       <c r="M87" s="10">
-        <f>IFERROR((M59-M73)/M73,"")</f>
+        <f>IFERROR((M59-M73)/M59,"")</f>
         <v/>
       </c>
     </row>
@@ -3647,51 +3647,51 @@
         </is>
       </c>
       <c r="B88" s="10">
-        <f>IFERROR((B60-B74)/B74,"")</f>
+        <f>IFERROR((B60-B74)/B60,"")</f>
         <v/>
       </c>
       <c r="C88" s="10">
-        <f>IFERROR((C60-C74)/C74,"")</f>
+        <f>IFERROR((C60-C74)/C60,"")</f>
         <v/>
       </c>
       <c r="D88" s="10">
-        <f>IFERROR((D60-D74)/D74,"")</f>
+        <f>IFERROR((D60-D74)/D60,"")</f>
         <v/>
       </c>
       <c r="E88" s="10">
-        <f>IFERROR((E60-E74)/E74,"")</f>
+        <f>IFERROR((E60-E74)/E60,"")</f>
         <v/>
       </c>
       <c r="F88" s="10">
-        <f>IFERROR((F60-F74)/F74,"")</f>
+        <f>IFERROR((F60-F74)/F60,"")</f>
         <v/>
       </c>
       <c r="G88" s="10">
-        <f>IFERROR((G60-G74)/G74,"")</f>
+        <f>IFERROR((G60-G74)/G60,"")</f>
         <v/>
       </c>
       <c r="H88" s="10">
-        <f>IFERROR((H60-H74)/H74,"")</f>
+        <f>IFERROR((H60-H74)/H60,"")</f>
         <v/>
       </c>
       <c r="I88" s="10">
-        <f>IFERROR((I60-I74)/I74,"")</f>
+        <f>IFERROR((I60-I74)/I60,"")</f>
         <v/>
       </c>
       <c r="J88" s="10">
-        <f>IFERROR((J60-J74)/J74,"")</f>
+        <f>IFERROR((J60-J74)/J60,"")</f>
         <v/>
       </c>
       <c r="K88" s="10">
-        <f>IFERROR((K60-K74)/K74,"")</f>
+        <f>IFERROR((K60-K74)/K60,"")</f>
         <v/>
       </c>
       <c r="L88" s="10">
-        <f>IFERROR((L60-L74)/L74,"")</f>
+        <f>IFERROR((L60-L74)/L60,"")</f>
         <v/>
       </c>
       <c r="M88" s="10">
-        <f>IFERROR((M60-M74)/M74,"")</f>
+        <f>IFERROR((M60-M74)/M60,"")</f>
         <v/>
       </c>
     </row>
@@ -3702,51 +3702,51 @@
         </is>
       </c>
       <c r="B89" s="10">
-        <f>IFERROR((B61-B75)/B75,"")</f>
+        <f>IFERROR((B61-B75)/B61,"")</f>
         <v/>
       </c>
       <c r="C89" s="10">
-        <f>IFERROR((C61-C75)/C75,"")</f>
+        <f>IFERROR((C61-C75)/C61,"")</f>
         <v/>
       </c>
       <c r="D89" s="10">
-        <f>IFERROR((D61-D75)/D75,"")</f>
+        <f>IFERROR((D61-D75)/D61,"")</f>
         <v/>
       </c>
       <c r="E89" s="10">
-        <f>IFERROR((E61-E75)/E75,"")</f>
+        <f>IFERROR((E61-E75)/E61,"")</f>
         <v/>
       </c>
       <c r="F89" s="10">
-        <f>IFERROR((F61-F75)/F75,"")</f>
+        <f>IFERROR((F61-F75)/F61,"")</f>
         <v/>
       </c>
       <c r="G89" s="10">
-        <f>IFERROR((G61-G75)/G75,"")</f>
+        <f>IFERROR((G61-G75)/G61,"")</f>
         <v/>
       </c>
       <c r="H89" s="10">
-        <f>IFERROR((H61-H75)/H75,"")</f>
+        <f>IFERROR((H61-H75)/H61,"")</f>
         <v/>
       </c>
       <c r="I89" s="10">
-        <f>IFERROR((I61-I75)/I75,"")</f>
+        <f>IFERROR((I61-I75)/I61,"")</f>
         <v/>
       </c>
       <c r="J89" s="10">
-        <f>IFERROR((J61-J75)/J75,"")</f>
+        <f>IFERROR((J61-J75)/J61,"")</f>
         <v/>
       </c>
       <c r="K89" s="10">
-        <f>IFERROR((K61-K75)/K75,"")</f>
+        <f>IFERROR((K61-K75)/K61,"")</f>
         <v/>
       </c>
       <c r="L89" s="10">
-        <f>IFERROR((L61-L75)/L75,"")</f>
+        <f>IFERROR((L61-L75)/L61,"")</f>
         <v/>
       </c>
       <c r="M89" s="10">
-        <f>IFERROR((M61-M75)/M75,"")</f>
+        <f>IFERROR((M61-M75)/M61,"")</f>
         <v/>
       </c>
     </row>
@@ -4672,7 +4672,7 @@
     <row r="121">
       <c r="A121" s="4" t="inlineStr">
         <is>
-          <t>% Diff  =  (ours − client) ÷ client      [green ≤2%  ·  amber 2–5%  ·  red &gt;5%]</t>
+          <t>% Diff  =  (ours − client) ÷ ours      [green ≤2%  ·  amber 2–5%  ·  red &gt;5%]</t>
         </is>
       </c>
     </row>
@@ -4750,51 +4750,51 @@
         </is>
       </c>
       <c r="B123" s="10">
-        <f>IFERROR((B95-B109)/B109,"")</f>
+        <f>IFERROR((B95-B109)/B95,"")</f>
         <v/>
       </c>
       <c r="C123" s="10">
-        <f>IFERROR((C95-C109)/C109,"")</f>
+        <f>IFERROR((C95-C109)/C95,"")</f>
         <v/>
       </c>
       <c r="D123" s="10">
-        <f>IFERROR((D95-D109)/D109,"")</f>
+        <f>IFERROR((D95-D109)/D95,"")</f>
         <v/>
       </c>
       <c r="E123" s="10">
-        <f>IFERROR((E95-E109)/E109,"")</f>
+        <f>IFERROR((E95-E109)/E95,"")</f>
         <v/>
       </c>
       <c r="F123" s="10">
-        <f>IFERROR((F95-F109)/F109,"")</f>
+        <f>IFERROR((F95-F109)/F95,"")</f>
         <v/>
       </c>
       <c r="G123" s="10">
-        <f>IFERROR((G95-G109)/G109,"")</f>
+        <f>IFERROR((G95-G109)/G95,"")</f>
         <v/>
       </c>
       <c r="H123" s="10">
-        <f>IFERROR((H95-H109)/H109,"")</f>
+        <f>IFERROR((H95-H109)/H95,"")</f>
         <v/>
       </c>
       <c r="I123" s="10">
-        <f>IFERROR((I95-I109)/I109,"")</f>
+        <f>IFERROR((I95-I109)/I95,"")</f>
         <v/>
       </c>
       <c r="J123" s="10">
-        <f>IFERROR((J95-J109)/J109,"")</f>
+        <f>IFERROR((J95-J109)/J95,"")</f>
         <v/>
       </c>
       <c r="K123" s="10">
-        <f>IFERROR((K95-K109)/K109,"")</f>
+        <f>IFERROR((K95-K109)/K95,"")</f>
         <v/>
       </c>
       <c r="L123" s="10">
-        <f>IFERROR((L95-L109)/L109,"")</f>
+        <f>IFERROR((L95-L109)/L95,"")</f>
         <v/>
       </c>
       <c r="M123" s="10">
-        <f>IFERROR((M95-M109)/M109,"")</f>
+        <f>IFERROR((M95-M109)/M95,"")</f>
         <v/>
       </c>
     </row>
@@ -4805,51 +4805,51 @@
         </is>
       </c>
       <c r="B124" s="10">
-        <f>IFERROR((B96-B110)/B110,"")</f>
+        <f>IFERROR((B96-B110)/B96,"")</f>
         <v/>
       </c>
       <c r="C124" s="10">
-        <f>IFERROR((C96-C110)/C110,"")</f>
+        <f>IFERROR((C96-C110)/C96,"")</f>
         <v/>
       </c>
       <c r="D124" s="10">
-        <f>IFERROR((D96-D110)/D110,"")</f>
+        <f>IFERROR((D96-D110)/D96,"")</f>
         <v/>
       </c>
       <c r="E124" s="10">
-        <f>IFERROR((E96-E110)/E110,"")</f>
+        <f>IFERROR((E96-E110)/E96,"")</f>
         <v/>
       </c>
       <c r="F124" s="10">
-        <f>IFERROR((F96-F110)/F110,"")</f>
+        <f>IFERROR((F96-F110)/F96,"")</f>
         <v/>
       </c>
       <c r="G124" s="10">
-        <f>IFERROR((G96-G110)/G110,"")</f>
+        <f>IFERROR((G96-G110)/G96,"")</f>
         <v/>
       </c>
       <c r="H124" s="10">
-        <f>IFERROR((H96-H110)/H110,"")</f>
+        <f>IFERROR((H96-H110)/H96,"")</f>
         <v/>
       </c>
       <c r="I124" s="10">
-        <f>IFERROR((I96-I110)/I110,"")</f>
+        <f>IFERROR((I96-I110)/I96,"")</f>
         <v/>
       </c>
       <c r="J124" s="10">
-        <f>IFERROR((J96-J110)/J110,"")</f>
+        <f>IFERROR((J96-J110)/J96,"")</f>
         <v/>
       </c>
       <c r="K124" s="10">
-        <f>IFERROR((K96-K110)/K110,"")</f>
+        <f>IFERROR((K96-K110)/K96,"")</f>
         <v/>
       </c>
       <c r="L124" s="10">
-        <f>IFERROR((L96-L110)/L110,"")</f>
+        <f>IFERROR((L96-L110)/L96,"")</f>
         <v/>
       </c>
       <c r="M124" s="10">
-        <f>IFERROR((M96-M110)/M110,"")</f>
+        <f>IFERROR((M96-M110)/M96,"")</f>
         <v/>
       </c>
     </row>
@@ -4860,51 +4860,51 @@
         </is>
       </c>
       <c r="B125" s="10">
-        <f>IFERROR((B97-B111)/B111,"")</f>
+        <f>IFERROR((B97-B111)/B97,"")</f>
         <v/>
       </c>
       <c r="C125" s="10">
-        <f>IFERROR((C97-C111)/C111,"")</f>
+        <f>IFERROR((C97-C111)/C97,"")</f>
         <v/>
       </c>
       <c r="D125" s="10">
-        <f>IFERROR((D97-D111)/D111,"")</f>
+        <f>IFERROR((D97-D111)/D97,"")</f>
         <v/>
       </c>
       <c r="E125" s="10">
-        <f>IFERROR((E97-E111)/E111,"")</f>
+        <f>IFERROR((E97-E111)/E97,"")</f>
         <v/>
       </c>
       <c r="F125" s="10">
-        <f>IFERROR((F97-F111)/F111,"")</f>
+        <f>IFERROR((F97-F111)/F97,"")</f>
         <v/>
       </c>
       <c r="G125" s="10">
-        <f>IFERROR((G97-G111)/G111,"")</f>
+        <f>IFERROR((G97-G111)/G97,"")</f>
         <v/>
       </c>
       <c r="H125" s="10">
-        <f>IFERROR((H97-H111)/H111,"")</f>
+        <f>IFERROR((H97-H111)/H97,"")</f>
         <v/>
       </c>
       <c r="I125" s="10">
-        <f>IFERROR((I97-I111)/I111,"")</f>
+        <f>IFERROR((I97-I111)/I97,"")</f>
         <v/>
       </c>
       <c r="J125" s="10">
-        <f>IFERROR((J97-J111)/J111,"")</f>
+        <f>IFERROR((J97-J111)/J97,"")</f>
         <v/>
       </c>
       <c r="K125" s="10">
-        <f>IFERROR((K97-K111)/K111,"")</f>
+        <f>IFERROR((K97-K111)/K97,"")</f>
         <v/>
       </c>
       <c r="L125" s="10">
-        <f>IFERROR((L97-L111)/L111,"")</f>
+        <f>IFERROR((L97-L111)/L97,"")</f>
         <v/>
       </c>
       <c r="M125" s="10">
-        <f>IFERROR((M97-M111)/M111,"")</f>
+        <f>IFERROR((M97-M111)/M97,"")</f>
         <v/>
       </c>
     </row>
@@ -4915,51 +4915,51 @@
         </is>
       </c>
       <c r="B126" s="10">
-        <f>IFERROR((B98-B112)/B112,"")</f>
+        <f>IFERROR((B98-B112)/B98,"")</f>
         <v/>
       </c>
       <c r="C126" s="10">
-        <f>IFERROR((C98-C112)/C112,"")</f>
+        <f>IFERROR((C98-C112)/C98,"")</f>
         <v/>
       </c>
       <c r="D126" s="10">
-        <f>IFERROR((D98-D112)/D112,"")</f>
+        <f>IFERROR((D98-D112)/D98,"")</f>
         <v/>
       </c>
       <c r="E126" s="10">
-        <f>IFERROR((E98-E112)/E112,"")</f>
+        <f>IFERROR((E98-E112)/E98,"")</f>
         <v/>
       </c>
       <c r="F126" s="10">
-        <f>IFERROR((F98-F112)/F112,"")</f>
+        <f>IFERROR((F98-F112)/F98,"")</f>
         <v/>
       </c>
       <c r="G126" s="10">
-        <f>IFERROR((G98-G112)/G112,"")</f>
+        <f>IFERROR((G98-G112)/G98,"")</f>
         <v/>
       </c>
       <c r="H126" s="10">
-        <f>IFERROR((H98-H112)/H112,"")</f>
+        <f>IFERROR((H98-H112)/H98,"")</f>
         <v/>
       </c>
       <c r="I126" s="10">
-        <f>IFERROR((I98-I112)/I112,"")</f>
+        <f>IFERROR((I98-I112)/I98,"")</f>
         <v/>
       </c>
       <c r="J126" s="10">
-        <f>IFERROR((J98-J112)/J112,"")</f>
+        <f>IFERROR((J98-J112)/J98,"")</f>
         <v/>
       </c>
       <c r="K126" s="10">
-        <f>IFERROR((K98-K112)/K112,"")</f>
+        <f>IFERROR((K98-K112)/K98,"")</f>
         <v/>
       </c>
       <c r="L126" s="10">
-        <f>IFERROR((L98-L112)/L112,"")</f>
+        <f>IFERROR((L98-L112)/L98,"")</f>
         <v/>
       </c>
       <c r="M126" s="10">
-        <f>IFERROR((M98-M112)/M112,"")</f>
+        <f>IFERROR((M98-M112)/M98,"")</f>
         <v/>
       </c>
     </row>
@@ -4970,51 +4970,51 @@
         </is>
       </c>
       <c r="B127" s="10">
-        <f>IFERROR((B99-B113)/B113,"")</f>
+        <f>IFERROR((B99-B113)/B99,"")</f>
         <v/>
       </c>
       <c r="C127" s="10">
-        <f>IFERROR((C99-C113)/C113,"")</f>
+        <f>IFERROR((C99-C113)/C99,"")</f>
         <v/>
       </c>
       <c r="D127" s="10">
-        <f>IFERROR((D99-D113)/D113,"")</f>
+        <f>IFERROR((D99-D113)/D99,"")</f>
         <v/>
       </c>
       <c r="E127" s="10">
-        <f>IFERROR((E99-E113)/E113,"")</f>
+        <f>IFERROR((E99-E113)/E99,"")</f>
         <v/>
       </c>
       <c r="F127" s="10">
-        <f>IFERROR((F99-F113)/F113,"")</f>
+        <f>IFERROR((F99-F113)/F99,"")</f>
         <v/>
       </c>
       <c r="G127" s="10">
-        <f>IFERROR((G99-G113)/G113,"")</f>
+        <f>IFERROR((G99-G113)/G99,"")</f>
         <v/>
       </c>
       <c r="H127" s="10">
-        <f>IFERROR((H99-H113)/H113,"")</f>
+        <f>IFERROR((H99-H113)/H99,"")</f>
         <v/>
       </c>
       <c r="I127" s="10">
-        <f>IFERROR((I99-I113)/I113,"")</f>
+        <f>IFERROR((I99-I113)/I99,"")</f>
         <v/>
       </c>
       <c r="J127" s="10">
-        <f>IFERROR((J99-J113)/J113,"")</f>
+        <f>IFERROR((J99-J113)/J99,"")</f>
         <v/>
       </c>
       <c r="K127" s="10">
-        <f>IFERROR((K99-K113)/K113,"")</f>
+        <f>IFERROR((K99-K113)/K99,"")</f>
         <v/>
       </c>
       <c r="L127" s="10">
-        <f>IFERROR((L99-L113)/L113,"")</f>
+        <f>IFERROR((L99-L113)/L99,"")</f>
         <v/>
       </c>
       <c r="M127" s="10">
-        <f>IFERROR((M99-M113)/M113,"")</f>
+        <f>IFERROR((M99-M113)/M99,"")</f>
         <v/>
       </c>
     </row>
@@ -5025,51 +5025,51 @@
         </is>
       </c>
       <c r="B128" s="10">
-        <f>IFERROR((B100-B114)/B114,"")</f>
+        <f>IFERROR((B100-B114)/B100,"")</f>
         <v/>
       </c>
       <c r="C128" s="10">
-        <f>IFERROR((C100-C114)/C114,"")</f>
+        <f>IFERROR((C100-C114)/C100,"")</f>
         <v/>
       </c>
       <c r="D128" s="10">
-        <f>IFERROR((D100-D114)/D114,"")</f>
+        <f>IFERROR((D100-D114)/D100,"")</f>
         <v/>
       </c>
       <c r="E128" s="10">
-        <f>IFERROR((E100-E114)/E114,"")</f>
+        <f>IFERROR((E100-E114)/E100,"")</f>
         <v/>
       </c>
       <c r="F128" s="10">
-        <f>IFERROR((F100-F114)/F114,"")</f>
+        <f>IFERROR((F100-F114)/F100,"")</f>
         <v/>
       </c>
       <c r="G128" s="10">
-        <f>IFERROR((G100-G114)/G114,"")</f>
+        <f>IFERROR((G100-G114)/G100,"")</f>
         <v/>
       </c>
       <c r="H128" s="10">
-        <f>IFERROR((H100-H114)/H114,"")</f>
+        <f>IFERROR((H100-H114)/H100,"")</f>
         <v/>
       </c>
       <c r="I128" s="10">
-        <f>IFERROR((I100-I114)/I114,"")</f>
+        <f>IFERROR((I100-I114)/I100,"")</f>
         <v/>
       </c>
       <c r="J128" s="10">
-        <f>IFERROR((J100-J114)/J114,"")</f>
+        <f>IFERROR((J100-J114)/J100,"")</f>
         <v/>
       </c>
       <c r="K128" s="10">
-        <f>IFERROR((K100-K114)/K114,"")</f>
+        <f>IFERROR((K100-K114)/K100,"")</f>
         <v/>
       </c>
       <c r="L128" s="10">
-        <f>IFERROR((L100-L114)/L114,"")</f>
+        <f>IFERROR((L100-L114)/L100,"")</f>
         <v/>
       </c>
       <c r="M128" s="10">
-        <f>IFERROR((M100-M114)/M114,"")</f>
+        <f>IFERROR((M100-M114)/M100,"")</f>
         <v/>
       </c>
     </row>
@@ -5080,51 +5080,51 @@
         </is>
       </c>
       <c r="B129" s="10">
-        <f>IFERROR((B101-B115)/B115,"")</f>
+        <f>IFERROR((B101-B115)/B101,"")</f>
         <v/>
       </c>
       <c r="C129" s="10">
-        <f>IFERROR((C101-C115)/C115,"")</f>
+        <f>IFERROR((C101-C115)/C101,"")</f>
         <v/>
       </c>
       <c r="D129" s="10">
-        <f>IFERROR((D101-D115)/D115,"")</f>
+        <f>IFERROR((D101-D115)/D101,"")</f>
         <v/>
       </c>
       <c r="E129" s="10">
-        <f>IFERROR((E101-E115)/E115,"")</f>
+        <f>IFERROR((E101-E115)/E101,"")</f>
         <v/>
       </c>
       <c r="F129" s="10">
-        <f>IFERROR((F101-F115)/F115,"")</f>
+        <f>IFERROR((F101-F115)/F101,"")</f>
         <v/>
       </c>
       <c r="G129" s="10">
-        <f>IFERROR((G101-G115)/G115,"")</f>
+        <f>IFERROR((G101-G115)/G101,"")</f>
         <v/>
       </c>
       <c r="H129" s="10">
-        <f>IFERROR((H101-H115)/H115,"")</f>
+        <f>IFERROR((H101-H115)/H101,"")</f>
         <v/>
       </c>
       <c r="I129" s="10">
-        <f>IFERROR((I101-I115)/I115,"")</f>
+        <f>IFERROR((I101-I115)/I101,"")</f>
         <v/>
       </c>
       <c r="J129" s="10">
-        <f>IFERROR((J101-J115)/J115,"")</f>
+        <f>IFERROR((J101-J115)/J101,"")</f>
         <v/>
       </c>
       <c r="K129" s="10">
-        <f>IFERROR((K101-K115)/K115,"")</f>
+        <f>IFERROR((K101-K115)/K101,"")</f>
         <v/>
       </c>
       <c r="L129" s="10">
-        <f>IFERROR((L101-L115)/L115,"")</f>
+        <f>IFERROR((L101-L115)/L101,"")</f>
         <v/>
       </c>
       <c r="M129" s="10">
-        <f>IFERROR((M101-M115)/M115,"")</f>
+        <f>IFERROR((M101-M115)/M101,"")</f>
         <v/>
       </c>
     </row>
@@ -5135,51 +5135,51 @@
         </is>
       </c>
       <c r="B130" s="10">
-        <f>IFERROR((B102-B116)/B116,"")</f>
+        <f>IFERROR((B102-B116)/B102,"")</f>
         <v/>
       </c>
       <c r="C130" s="10">
-        <f>IFERROR((C102-C116)/C116,"")</f>
+        <f>IFERROR((C102-C116)/C102,"")</f>
         <v/>
       </c>
       <c r="D130" s="10">
-        <f>IFERROR((D102-D116)/D116,"")</f>
+        <f>IFERROR((D102-D116)/D102,"")</f>
         <v/>
       </c>
       <c r="E130" s="10">
-        <f>IFERROR((E102-E116)/E116,"")</f>
+        <f>IFERROR((E102-E116)/E102,"")</f>
         <v/>
       </c>
       <c r="F130" s="10">
-        <f>IFERROR((F102-F116)/F116,"")</f>
+        <f>IFERROR((F102-F116)/F102,"")</f>
         <v/>
       </c>
       <c r="G130" s="10">
-        <f>IFERROR((G102-G116)/G116,"")</f>
+        <f>IFERROR((G102-G116)/G102,"")</f>
         <v/>
       </c>
       <c r="H130" s="10">
-        <f>IFERROR((H102-H116)/H116,"")</f>
+        <f>IFERROR((H102-H116)/H102,"")</f>
         <v/>
       </c>
       <c r="I130" s="10">
-        <f>IFERROR((I102-I116)/I116,"")</f>
+        <f>IFERROR((I102-I116)/I102,"")</f>
         <v/>
       </c>
       <c r="J130" s="10">
-        <f>IFERROR((J102-J116)/J116,"")</f>
+        <f>IFERROR((J102-J116)/J102,"")</f>
         <v/>
       </c>
       <c r="K130" s="10">
-        <f>IFERROR((K102-K116)/K116,"")</f>
+        <f>IFERROR((K102-K116)/K102,"")</f>
         <v/>
       </c>
       <c r="L130" s="10">
-        <f>IFERROR((L102-L116)/L116,"")</f>
+        <f>IFERROR((L102-L116)/L102,"")</f>
         <v/>
       </c>
       <c r="M130" s="10">
-        <f>IFERROR((M102-M116)/M116,"")</f>
+        <f>IFERROR((M102-M116)/M102,"")</f>
         <v/>
       </c>
     </row>
@@ -5190,51 +5190,51 @@
         </is>
       </c>
       <c r="B131" s="10">
-        <f>IFERROR((B103-B117)/B117,"")</f>
+        <f>IFERROR((B103-B117)/B103,"")</f>
         <v/>
       </c>
       <c r="C131" s="10">
-        <f>IFERROR((C103-C117)/C117,"")</f>
+        <f>IFERROR((C103-C117)/C103,"")</f>
         <v/>
       </c>
       <c r="D131" s="10">
-        <f>IFERROR((D103-D117)/D117,"")</f>
+        <f>IFERROR((D103-D117)/D103,"")</f>
         <v/>
       </c>
       <c r="E131" s="10">
-        <f>IFERROR((E103-E117)/E117,"")</f>
+        <f>IFERROR((E103-E117)/E103,"")</f>
         <v/>
       </c>
       <c r="F131" s="10">
-        <f>IFERROR((F103-F117)/F117,"")</f>
+        <f>IFERROR((F103-F117)/F103,"")</f>
         <v/>
       </c>
       <c r="G131" s="10">
-        <f>IFERROR((G103-G117)/G117,"")</f>
+        <f>IFERROR((G103-G117)/G103,"")</f>
         <v/>
       </c>
       <c r="H131" s="10">
-        <f>IFERROR((H103-H117)/H117,"")</f>
+        <f>IFERROR((H103-H117)/H103,"")</f>
         <v/>
       </c>
       <c r="I131" s="10">
-        <f>IFERROR((I103-I117)/I117,"")</f>
+        <f>IFERROR((I103-I117)/I103,"")</f>
         <v/>
       </c>
       <c r="J131" s="10">
-        <f>IFERROR((J103-J117)/J117,"")</f>
+        <f>IFERROR((J103-J117)/J103,"")</f>
         <v/>
       </c>
       <c r="K131" s="10">
-        <f>IFERROR((K103-K117)/K117,"")</f>
+        <f>IFERROR((K103-K117)/K103,"")</f>
         <v/>
       </c>
       <c r="L131" s="10">
-        <f>IFERROR((L103-L117)/L117,"")</f>
+        <f>IFERROR((L103-L117)/L103,"")</f>
         <v/>
       </c>
       <c r="M131" s="10">
-        <f>IFERROR((M103-M117)/M117,"")</f>
+        <f>IFERROR((M103-M117)/M103,"")</f>
         <v/>
       </c>
     </row>
@@ -5245,51 +5245,51 @@
         </is>
       </c>
       <c r="B132" s="10">
-        <f>IFERROR((B104-B118)/B118,"")</f>
+        <f>IFERROR((B104-B118)/B104,"")</f>
         <v/>
       </c>
       <c r="C132" s="10">
-        <f>IFERROR((C104-C118)/C118,"")</f>
+        <f>IFERROR((C104-C118)/C104,"")</f>
         <v/>
       </c>
       <c r="D132" s="10">
-        <f>IFERROR((D104-D118)/D118,"")</f>
+        <f>IFERROR((D104-D118)/D104,"")</f>
         <v/>
       </c>
       <c r="E132" s="10">
-        <f>IFERROR((E104-E118)/E118,"")</f>
+        <f>IFERROR((E104-E118)/E104,"")</f>
         <v/>
       </c>
       <c r="F132" s="10">
-        <f>IFERROR((F104-F118)/F118,"")</f>
+        <f>IFERROR((F104-F118)/F104,"")</f>
         <v/>
       </c>
       <c r="G132" s="10">
-        <f>IFERROR((G104-G118)/G118,"")</f>
+        <f>IFERROR((G104-G118)/G104,"")</f>
         <v/>
       </c>
       <c r="H132" s="10">
-        <f>IFERROR((H104-H118)/H118,"")</f>
+        <f>IFERROR((H104-H118)/H104,"")</f>
         <v/>
       </c>
       <c r="I132" s="10">
-        <f>IFERROR((I104-I118)/I118,"")</f>
+        <f>IFERROR((I104-I118)/I104,"")</f>
         <v/>
       </c>
       <c r="J132" s="10">
-        <f>IFERROR((J104-J118)/J118,"")</f>
+        <f>IFERROR((J104-J118)/J104,"")</f>
         <v/>
       </c>
       <c r="K132" s="10">
-        <f>IFERROR((K104-K118)/K118,"")</f>
+        <f>IFERROR((K104-K118)/K104,"")</f>
         <v/>
       </c>
       <c r="L132" s="10">
-        <f>IFERROR((L104-L118)/L118,"")</f>
+        <f>IFERROR((L104-L118)/L104,"")</f>
         <v/>
       </c>
       <c r="M132" s="10">
-        <f>IFERROR((M104-M118)/M118,"")</f>
+        <f>IFERROR((M104-M118)/M104,"")</f>
         <v/>
       </c>
     </row>
@@ -5300,51 +5300,51 @@
         </is>
       </c>
       <c r="B133" s="10">
-        <f>IFERROR((B105-B119)/B119,"")</f>
+        <f>IFERROR((B105-B119)/B105,"")</f>
         <v/>
       </c>
       <c r="C133" s="10">
-        <f>IFERROR((C105-C119)/C119,"")</f>
+        <f>IFERROR((C105-C119)/C105,"")</f>
         <v/>
       </c>
       <c r="D133" s="10">
-        <f>IFERROR((D105-D119)/D119,"")</f>
+        <f>IFERROR((D105-D119)/D105,"")</f>
         <v/>
       </c>
       <c r="E133" s="10">
-        <f>IFERROR((E105-E119)/E119,"")</f>
+        <f>IFERROR((E105-E119)/E105,"")</f>
         <v/>
       </c>
       <c r="F133" s="10">
-        <f>IFERROR((F105-F119)/F119,"")</f>
+        <f>IFERROR((F105-F119)/F105,"")</f>
         <v/>
       </c>
       <c r="G133" s="10">
-        <f>IFERROR((G105-G119)/G119,"")</f>
+        <f>IFERROR((G105-G119)/G105,"")</f>
         <v/>
       </c>
       <c r="H133" s="10">
-        <f>IFERROR((H105-H119)/H119,"")</f>
+        <f>IFERROR((H105-H119)/H105,"")</f>
         <v/>
       </c>
       <c r="I133" s="10">
-        <f>IFERROR((I105-I119)/I119,"")</f>
+        <f>IFERROR((I105-I119)/I105,"")</f>
         <v/>
       </c>
       <c r="J133" s="10">
-        <f>IFERROR((J105-J119)/J119,"")</f>
+        <f>IFERROR((J105-J119)/J105,"")</f>
         <v/>
       </c>
       <c r="K133" s="10">
-        <f>IFERROR((K105-K119)/K119,"")</f>
+        <f>IFERROR((K105-K119)/K105,"")</f>
         <v/>
       </c>
       <c r="L133" s="10">
-        <f>IFERROR((L105-L119)/L119,"")</f>
+        <f>IFERROR((L105-L119)/L105,"")</f>
         <v/>
       </c>
       <c r="M133" s="10">
-        <f>IFERROR((M105-M119)/M119,"")</f>
+        <f>IFERROR((M105-M119)/M105,"")</f>
         <v/>
       </c>
     </row>
@@ -6346,7 +6346,7 @@
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>% Diff  =  (ours − client) ÷ client      [green ≤2%  ·  amber 2–5%  ·  red &gt;5%]</t>
+          <t>% Diff  =  (ours − client) ÷ ours      [green ≤2%  ·  amber 2–5%  ·  red &gt;5%]</t>
         </is>
       </c>
     </row>
@@ -6424,51 +6424,51 @@
         </is>
       </c>
       <c r="B35" s="10">
-        <f>IFERROR((B7-B21)/B21,"")</f>
+        <f>IFERROR((B7-B21)/B7,"")</f>
         <v/>
       </c>
       <c r="C35" s="10">
-        <f>IFERROR((C7-C21)/C21,"")</f>
+        <f>IFERROR((C7-C21)/C7,"")</f>
         <v/>
       </c>
       <c r="D35" s="10">
-        <f>IFERROR((D7-D21)/D21,"")</f>
+        <f>IFERROR((D7-D21)/D7,"")</f>
         <v/>
       </c>
       <c r="E35" s="10">
-        <f>IFERROR((E7-E21)/E21,"")</f>
+        <f>IFERROR((E7-E21)/E7,"")</f>
         <v/>
       </c>
       <c r="F35" s="10">
-        <f>IFERROR((F7-F21)/F21,"")</f>
+        <f>IFERROR((F7-F21)/F7,"")</f>
         <v/>
       </c>
       <c r="G35" s="10">
-        <f>IFERROR((G7-G21)/G21,"")</f>
+        <f>IFERROR((G7-G21)/G7,"")</f>
         <v/>
       </c>
       <c r="H35" s="10">
-        <f>IFERROR((H7-H21)/H21,"")</f>
+        <f>IFERROR((H7-H21)/H7,"")</f>
         <v/>
       </c>
       <c r="I35" s="10">
-        <f>IFERROR((I7-I21)/I21,"")</f>
+        <f>IFERROR((I7-I21)/I7,"")</f>
         <v/>
       </c>
       <c r="J35" s="10">
-        <f>IFERROR((J7-J21)/J21,"")</f>
+        <f>IFERROR((J7-J21)/J7,"")</f>
         <v/>
       </c>
       <c r="K35" s="10">
-        <f>IFERROR((K7-K21)/K21,"")</f>
+        <f>IFERROR((K7-K21)/K7,"")</f>
         <v/>
       </c>
       <c r="L35" s="10">
-        <f>IFERROR((L7-L21)/L21,"")</f>
+        <f>IFERROR((L7-L21)/L7,"")</f>
         <v/>
       </c>
       <c r="M35" s="10">
-        <f>IFERROR((M7-M21)/M21,"")</f>
+        <f>IFERROR((M7-M21)/M7,"")</f>
         <v/>
       </c>
     </row>
@@ -6479,51 +6479,51 @@
         </is>
       </c>
       <c r="B36" s="10">
-        <f>IFERROR((B8-B22)/B22,"")</f>
+        <f>IFERROR((B8-B22)/B8,"")</f>
         <v/>
       </c>
       <c r="C36" s="10">
-        <f>IFERROR((C8-C22)/C22,"")</f>
+        <f>IFERROR((C8-C22)/C8,"")</f>
         <v/>
       </c>
       <c r="D36" s="10">
-        <f>IFERROR((D8-D22)/D22,"")</f>
+        <f>IFERROR((D8-D22)/D8,"")</f>
         <v/>
       </c>
       <c r="E36" s="10">
-        <f>IFERROR((E8-E22)/E22,"")</f>
+        <f>IFERROR((E8-E22)/E8,"")</f>
         <v/>
       </c>
       <c r="F36" s="10">
-        <f>IFERROR((F8-F22)/F22,"")</f>
+        <f>IFERROR((F8-F22)/F8,"")</f>
         <v/>
       </c>
       <c r="G36" s="10">
-        <f>IFERROR((G8-G22)/G22,"")</f>
+        <f>IFERROR((G8-G22)/G8,"")</f>
         <v/>
       </c>
       <c r="H36" s="10">
-        <f>IFERROR((H8-H22)/H22,"")</f>
+        <f>IFERROR((H8-H22)/H8,"")</f>
         <v/>
       </c>
       <c r="I36" s="10">
-        <f>IFERROR((I8-I22)/I22,"")</f>
+        <f>IFERROR((I8-I22)/I8,"")</f>
         <v/>
       </c>
       <c r="J36" s="10">
-        <f>IFERROR((J8-J22)/J22,"")</f>
+        <f>IFERROR((J8-J22)/J8,"")</f>
         <v/>
       </c>
       <c r="K36" s="10">
-        <f>IFERROR((K8-K22)/K22,"")</f>
+        <f>IFERROR((K8-K22)/K8,"")</f>
         <v/>
       </c>
       <c r="L36" s="10">
-        <f>IFERROR((L8-L22)/L22,"")</f>
+        <f>IFERROR((L8-L22)/L8,"")</f>
         <v/>
       </c>
       <c r="M36" s="10">
-        <f>IFERROR((M8-M22)/M22,"")</f>
+        <f>IFERROR((M8-M22)/M8,"")</f>
         <v/>
       </c>
     </row>
@@ -6534,51 +6534,51 @@
         </is>
       </c>
       <c r="B37" s="10">
-        <f>IFERROR((B9-B23)/B23,"")</f>
+        <f>IFERROR((B9-B23)/B9,"")</f>
         <v/>
       </c>
       <c r="C37" s="10">
-        <f>IFERROR((C9-C23)/C23,"")</f>
+        <f>IFERROR((C9-C23)/C9,"")</f>
         <v/>
       </c>
       <c r="D37" s="10">
-        <f>IFERROR((D9-D23)/D23,"")</f>
+        <f>IFERROR((D9-D23)/D9,"")</f>
         <v/>
       </c>
       <c r="E37" s="10">
-        <f>IFERROR((E9-E23)/E23,"")</f>
+        <f>IFERROR((E9-E23)/E9,"")</f>
         <v/>
       </c>
       <c r="F37" s="10">
-        <f>IFERROR((F9-F23)/F23,"")</f>
+        <f>IFERROR((F9-F23)/F9,"")</f>
         <v/>
       </c>
       <c r="G37" s="10">
-        <f>IFERROR((G9-G23)/G23,"")</f>
+        <f>IFERROR((G9-G23)/G9,"")</f>
         <v/>
       </c>
       <c r="H37" s="10">
-        <f>IFERROR((H9-H23)/H23,"")</f>
+        <f>IFERROR((H9-H23)/H9,"")</f>
         <v/>
       </c>
       <c r="I37" s="10">
-        <f>IFERROR((I9-I23)/I23,"")</f>
+        <f>IFERROR((I9-I23)/I9,"")</f>
         <v/>
       </c>
       <c r="J37" s="10">
-        <f>IFERROR((J9-J23)/J23,"")</f>
+        <f>IFERROR((J9-J23)/J9,"")</f>
         <v/>
       </c>
       <c r="K37" s="10">
-        <f>IFERROR((K9-K23)/K23,"")</f>
+        <f>IFERROR((K9-K23)/K9,"")</f>
         <v/>
       </c>
       <c r="L37" s="10">
-        <f>IFERROR((L9-L23)/L23,"")</f>
+        <f>IFERROR((L9-L23)/L9,"")</f>
         <v/>
       </c>
       <c r="M37" s="10">
-        <f>IFERROR((M9-M23)/M23,"")</f>
+        <f>IFERROR((M9-M23)/M9,"")</f>
         <v/>
       </c>
     </row>
@@ -6589,51 +6589,51 @@
         </is>
       </c>
       <c r="B38" s="10">
-        <f>IFERROR((B10-B24)/B24,"")</f>
+        <f>IFERROR((B10-B24)/B10,"")</f>
         <v/>
       </c>
       <c r="C38" s="10">
-        <f>IFERROR((C10-C24)/C24,"")</f>
+        <f>IFERROR((C10-C24)/C10,"")</f>
         <v/>
       </c>
       <c r="D38" s="10">
-        <f>IFERROR((D10-D24)/D24,"")</f>
+        <f>IFERROR((D10-D24)/D10,"")</f>
         <v/>
       </c>
       <c r="E38" s="10">
-        <f>IFERROR((E10-E24)/E24,"")</f>
+        <f>IFERROR((E10-E24)/E10,"")</f>
         <v/>
       </c>
       <c r="F38" s="10">
-        <f>IFERROR((F10-F24)/F24,"")</f>
+        <f>IFERROR((F10-F24)/F10,"")</f>
         <v/>
       </c>
       <c r="G38" s="10">
-        <f>IFERROR((G10-G24)/G24,"")</f>
+        <f>IFERROR((G10-G24)/G10,"")</f>
         <v/>
       </c>
       <c r="H38" s="10">
-        <f>IFERROR((H10-H24)/H24,"")</f>
+        <f>IFERROR((H10-H24)/H10,"")</f>
         <v/>
       </c>
       <c r="I38" s="10">
-        <f>IFERROR((I10-I24)/I24,"")</f>
+        <f>IFERROR((I10-I24)/I10,"")</f>
         <v/>
       </c>
       <c r="J38" s="10">
-        <f>IFERROR((J10-J24)/J24,"")</f>
+        <f>IFERROR((J10-J24)/J10,"")</f>
         <v/>
       </c>
       <c r="K38" s="10">
-        <f>IFERROR((K10-K24)/K24,"")</f>
+        <f>IFERROR((K10-K24)/K10,"")</f>
         <v/>
       </c>
       <c r="L38" s="10">
-        <f>IFERROR((L10-L24)/L24,"")</f>
+        <f>IFERROR((L10-L24)/L10,"")</f>
         <v/>
       </c>
       <c r="M38" s="10">
-        <f>IFERROR((M10-M24)/M24,"")</f>
+        <f>IFERROR((M10-M24)/M10,"")</f>
         <v/>
       </c>
     </row>
@@ -6644,51 +6644,51 @@
         </is>
       </c>
       <c r="B39" s="10">
-        <f>IFERROR((B11-B25)/B25,"")</f>
+        <f>IFERROR((B11-B25)/B11,"")</f>
         <v/>
       </c>
       <c r="C39" s="10">
-        <f>IFERROR((C11-C25)/C25,"")</f>
+        <f>IFERROR((C11-C25)/C11,"")</f>
         <v/>
       </c>
       <c r="D39" s="10">
-        <f>IFERROR((D11-D25)/D25,"")</f>
+        <f>IFERROR((D11-D25)/D11,"")</f>
         <v/>
       </c>
       <c r="E39" s="10">
-        <f>IFERROR((E11-E25)/E25,"")</f>
+        <f>IFERROR((E11-E25)/E11,"")</f>
         <v/>
       </c>
       <c r="F39" s="10">
-        <f>IFERROR((F11-F25)/F25,"")</f>
+        <f>IFERROR((F11-F25)/F11,"")</f>
         <v/>
       </c>
       <c r="G39" s="10">
-        <f>IFERROR((G11-G25)/G25,"")</f>
+        <f>IFERROR((G11-G25)/G11,"")</f>
         <v/>
       </c>
       <c r="H39" s="10">
-        <f>IFERROR((H11-H25)/H25,"")</f>
+        <f>IFERROR((H11-H25)/H11,"")</f>
         <v/>
       </c>
       <c r="I39" s="10">
-        <f>IFERROR((I11-I25)/I25,"")</f>
+        <f>IFERROR((I11-I25)/I11,"")</f>
         <v/>
       </c>
       <c r="J39" s="10">
-        <f>IFERROR((J11-J25)/J25,"")</f>
+        <f>IFERROR((J11-J25)/J11,"")</f>
         <v/>
       </c>
       <c r="K39" s="10">
-        <f>IFERROR((K11-K25)/K25,"")</f>
+        <f>IFERROR((K11-K25)/K11,"")</f>
         <v/>
       </c>
       <c r="L39" s="10">
-        <f>IFERROR((L11-L25)/L25,"")</f>
+        <f>IFERROR((L11-L25)/L11,"")</f>
         <v/>
       </c>
       <c r="M39" s="10">
-        <f>IFERROR((M11-M25)/M25,"")</f>
+        <f>IFERROR((M11-M25)/M11,"")</f>
         <v/>
       </c>
     </row>
@@ -6699,51 +6699,51 @@
         </is>
       </c>
       <c r="B40" s="10">
-        <f>IFERROR((B12-B26)/B26,"")</f>
+        <f>IFERROR((B12-B26)/B12,"")</f>
         <v/>
       </c>
       <c r="C40" s="10">
-        <f>IFERROR((C12-C26)/C26,"")</f>
+        <f>IFERROR((C12-C26)/C12,"")</f>
         <v/>
       </c>
       <c r="D40" s="10">
-        <f>IFERROR((D12-D26)/D26,"")</f>
+        <f>IFERROR((D12-D26)/D12,"")</f>
         <v/>
       </c>
       <c r="E40" s="10">
-        <f>IFERROR((E12-E26)/E26,"")</f>
+        <f>IFERROR((E12-E26)/E12,"")</f>
         <v/>
       </c>
       <c r="F40" s="10">
-        <f>IFERROR((F12-F26)/F26,"")</f>
+        <f>IFERROR((F12-F26)/F12,"")</f>
         <v/>
       </c>
       <c r="G40" s="10">
-        <f>IFERROR((G12-G26)/G26,"")</f>
+        <f>IFERROR((G12-G26)/G12,"")</f>
         <v/>
       </c>
       <c r="H40" s="10">
-        <f>IFERROR((H12-H26)/H26,"")</f>
+        <f>IFERROR((H12-H26)/H12,"")</f>
         <v/>
       </c>
       <c r="I40" s="10">
-        <f>IFERROR((I12-I26)/I26,"")</f>
+        <f>IFERROR((I12-I26)/I12,"")</f>
         <v/>
       </c>
       <c r="J40" s="10">
-        <f>IFERROR((J12-J26)/J26,"")</f>
+        <f>IFERROR((J12-J26)/J12,"")</f>
         <v/>
       </c>
       <c r="K40" s="10">
-        <f>IFERROR((K12-K26)/K26,"")</f>
+        <f>IFERROR((K12-K26)/K12,"")</f>
         <v/>
       </c>
       <c r="L40" s="10">
-        <f>IFERROR((L12-L26)/L26,"")</f>
+        <f>IFERROR((L12-L26)/L12,"")</f>
         <v/>
       </c>
       <c r="M40" s="10">
-        <f>IFERROR((M12-M26)/M26,"")</f>
+        <f>IFERROR((M12-M26)/M12,"")</f>
         <v/>
       </c>
     </row>
@@ -6754,51 +6754,51 @@
         </is>
       </c>
       <c r="B41" s="10">
-        <f>IFERROR((B13-B27)/B27,"")</f>
+        <f>IFERROR((B13-B27)/B13,"")</f>
         <v/>
       </c>
       <c r="C41" s="10">
-        <f>IFERROR((C13-C27)/C27,"")</f>
+        <f>IFERROR((C13-C27)/C13,"")</f>
         <v/>
       </c>
       <c r="D41" s="10">
-        <f>IFERROR((D13-D27)/D27,"")</f>
+        <f>IFERROR((D13-D27)/D13,"")</f>
         <v/>
       </c>
       <c r="E41" s="10">
-        <f>IFERROR((E13-E27)/E27,"")</f>
+        <f>IFERROR((E13-E27)/E13,"")</f>
         <v/>
       </c>
       <c r="F41" s="10">
-        <f>IFERROR((F13-F27)/F27,"")</f>
+        <f>IFERROR((F13-F27)/F13,"")</f>
         <v/>
       </c>
       <c r="G41" s="10">
-        <f>IFERROR((G13-G27)/G27,"")</f>
+        <f>IFERROR((G13-G27)/G13,"")</f>
         <v/>
       </c>
       <c r="H41" s="10">
-        <f>IFERROR((H13-H27)/H27,"")</f>
+        <f>IFERROR((H13-H27)/H13,"")</f>
         <v/>
       </c>
       <c r="I41" s="10">
-        <f>IFERROR((I13-I27)/I27,"")</f>
+        <f>IFERROR((I13-I27)/I13,"")</f>
         <v/>
       </c>
       <c r="J41" s="10">
-        <f>IFERROR((J13-J27)/J27,"")</f>
+        <f>IFERROR((J13-J27)/J13,"")</f>
         <v/>
       </c>
       <c r="K41" s="10">
-        <f>IFERROR((K13-K27)/K27,"")</f>
+        <f>IFERROR((K13-K27)/K13,"")</f>
         <v/>
       </c>
       <c r="L41" s="10">
-        <f>IFERROR((L13-L27)/L27,"")</f>
+        <f>IFERROR((L13-L27)/L13,"")</f>
         <v/>
       </c>
       <c r="M41" s="10">
-        <f>IFERROR((M13-M27)/M27,"")</f>
+        <f>IFERROR((M13-M27)/M13,"")</f>
         <v/>
       </c>
     </row>
@@ -6809,51 +6809,51 @@
         </is>
       </c>
       <c r="B42" s="10">
-        <f>IFERROR((B14-B28)/B28,"")</f>
+        <f>IFERROR((B14-B28)/B14,"")</f>
         <v/>
       </c>
       <c r="C42" s="10">
-        <f>IFERROR((C14-C28)/C28,"")</f>
+        <f>IFERROR((C14-C28)/C14,"")</f>
         <v/>
       </c>
       <c r="D42" s="10">
-        <f>IFERROR((D14-D28)/D28,"")</f>
+        <f>IFERROR((D14-D28)/D14,"")</f>
         <v/>
       </c>
       <c r="E42" s="10">
-        <f>IFERROR((E14-E28)/E28,"")</f>
+        <f>IFERROR((E14-E28)/E14,"")</f>
         <v/>
       </c>
       <c r="F42" s="10">
-        <f>IFERROR((F14-F28)/F28,"")</f>
+        <f>IFERROR((F14-F28)/F14,"")</f>
         <v/>
       </c>
       <c r="G42" s="10">
-        <f>IFERROR((G14-G28)/G28,"")</f>
+        <f>IFERROR((G14-G28)/G14,"")</f>
         <v/>
       </c>
       <c r="H42" s="10">
-        <f>IFERROR((H14-H28)/H28,"")</f>
+        <f>IFERROR((H14-H28)/H14,"")</f>
         <v/>
       </c>
       <c r="I42" s="10">
-        <f>IFERROR((I14-I28)/I28,"")</f>
+        <f>IFERROR((I14-I28)/I14,"")</f>
         <v/>
       </c>
       <c r="J42" s="10">
-        <f>IFERROR((J14-J28)/J28,"")</f>
+        <f>IFERROR((J14-J28)/J14,"")</f>
         <v/>
       </c>
       <c r="K42" s="10">
-        <f>IFERROR((K14-K28)/K28,"")</f>
+        <f>IFERROR((K14-K28)/K14,"")</f>
         <v/>
       </c>
       <c r="L42" s="10">
-        <f>IFERROR((L14-L28)/L28,"")</f>
+        <f>IFERROR((L14-L28)/L14,"")</f>
         <v/>
       </c>
       <c r="M42" s="10">
-        <f>IFERROR((M14-M28)/M28,"")</f>
+        <f>IFERROR((M14-M28)/M14,"")</f>
         <v/>
       </c>
     </row>
@@ -6864,51 +6864,51 @@
         </is>
       </c>
       <c r="B43" s="10">
-        <f>IFERROR((B15-B29)/B29,"")</f>
+        <f>IFERROR((B15-B29)/B15,"")</f>
         <v/>
       </c>
       <c r="C43" s="10">
-        <f>IFERROR((C15-C29)/C29,"")</f>
+        <f>IFERROR((C15-C29)/C15,"")</f>
         <v/>
       </c>
       <c r="D43" s="10">
-        <f>IFERROR((D15-D29)/D29,"")</f>
+        <f>IFERROR((D15-D29)/D15,"")</f>
         <v/>
       </c>
       <c r="E43" s="10">
-        <f>IFERROR((E15-E29)/E29,"")</f>
+        <f>IFERROR((E15-E29)/E15,"")</f>
         <v/>
       </c>
       <c r="F43" s="10">
-        <f>IFERROR((F15-F29)/F29,"")</f>
+        <f>IFERROR((F15-F29)/F15,"")</f>
         <v/>
       </c>
       <c r="G43" s="10">
-        <f>IFERROR((G15-G29)/G29,"")</f>
+        <f>IFERROR((G15-G29)/G15,"")</f>
         <v/>
       </c>
       <c r="H43" s="10">
-        <f>IFERROR((H15-H29)/H29,"")</f>
+        <f>IFERROR((H15-H29)/H15,"")</f>
         <v/>
       </c>
       <c r="I43" s="10">
-        <f>IFERROR((I15-I29)/I29,"")</f>
+        <f>IFERROR((I15-I29)/I15,"")</f>
         <v/>
       </c>
       <c r="J43" s="10">
-        <f>IFERROR((J15-J29)/J29,"")</f>
+        <f>IFERROR((J15-J29)/J15,"")</f>
         <v/>
       </c>
       <c r="K43" s="10">
-        <f>IFERROR((K15-K29)/K29,"")</f>
+        <f>IFERROR((K15-K29)/K15,"")</f>
         <v/>
       </c>
       <c r="L43" s="10">
-        <f>IFERROR((L15-L29)/L29,"")</f>
+        <f>IFERROR((L15-L29)/L15,"")</f>
         <v/>
       </c>
       <c r="M43" s="10">
-        <f>IFERROR((M15-M29)/M29,"")</f>
+        <f>IFERROR((M15-M29)/M15,"")</f>
         <v/>
       </c>
     </row>
@@ -6919,51 +6919,51 @@
         </is>
       </c>
       <c r="B44" s="10">
-        <f>IFERROR((B16-B30)/B30,"")</f>
+        <f>IFERROR((B16-B30)/B16,"")</f>
         <v/>
       </c>
       <c r="C44" s="10">
-        <f>IFERROR((C16-C30)/C30,"")</f>
+        <f>IFERROR((C16-C30)/C16,"")</f>
         <v/>
       </c>
       <c r="D44" s="10">
-        <f>IFERROR((D16-D30)/D30,"")</f>
+        <f>IFERROR((D16-D30)/D16,"")</f>
         <v/>
       </c>
       <c r="E44" s="10">
-        <f>IFERROR((E16-E30)/E30,"")</f>
+        <f>IFERROR((E16-E30)/E16,"")</f>
         <v/>
       </c>
       <c r="F44" s="10">
-        <f>IFERROR((F16-F30)/F30,"")</f>
+        <f>IFERROR((F16-F30)/F16,"")</f>
         <v/>
       </c>
       <c r="G44" s="10">
-        <f>IFERROR((G16-G30)/G30,"")</f>
+        <f>IFERROR((G16-G30)/G16,"")</f>
         <v/>
       </c>
       <c r="H44" s="10">
-        <f>IFERROR((H16-H30)/H30,"")</f>
+        <f>IFERROR((H16-H30)/H16,"")</f>
         <v/>
       </c>
       <c r="I44" s="10">
-        <f>IFERROR((I16-I30)/I30,"")</f>
+        <f>IFERROR((I16-I30)/I16,"")</f>
         <v/>
       </c>
       <c r="J44" s="10">
-        <f>IFERROR((J16-J30)/J30,"")</f>
+        <f>IFERROR((J16-J30)/J16,"")</f>
         <v/>
       </c>
       <c r="K44" s="10">
-        <f>IFERROR((K16-K30)/K30,"")</f>
+        <f>IFERROR((K16-K30)/K16,"")</f>
         <v/>
       </c>
       <c r="L44" s="10">
-        <f>IFERROR((L16-L30)/L30,"")</f>
+        <f>IFERROR((L16-L30)/L16,"")</f>
         <v/>
       </c>
       <c r="M44" s="10">
-        <f>IFERROR((M16-M30)/M30,"")</f>
+        <f>IFERROR((M16-M30)/M16,"")</f>
         <v/>
       </c>
     </row>
@@ -6974,51 +6974,51 @@
         </is>
       </c>
       <c r="B45" s="10">
-        <f>IFERROR((B17-B31)/B31,"")</f>
+        <f>IFERROR((B17-B31)/B17,"")</f>
         <v/>
       </c>
       <c r="C45" s="10">
-        <f>IFERROR((C17-C31)/C31,"")</f>
+        <f>IFERROR((C17-C31)/C17,"")</f>
         <v/>
       </c>
       <c r="D45" s="10">
-        <f>IFERROR((D17-D31)/D31,"")</f>
+        <f>IFERROR((D17-D31)/D17,"")</f>
         <v/>
       </c>
       <c r="E45" s="10">
-        <f>IFERROR((E17-E31)/E31,"")</f>
+        <f>IFERROR((E17-E31)/E17,"")</f>
         <v/>
       </c>
       <c r="F45" s="10">
-        <f>IFERROR((F17-F31)/F31,"")</f>
+        <f>IFERROR((F17-F31)/F17,"")</f>
         <v/>
       </c>
       <c r="G45" s="10">
-        <f>IFERROR((G17-G31)/G31,"")</f>
+        <f>IFERROR((G17-G31)/G17,"")</f>
         <v/>
       </c>
       <c r="H45" s="10">
-        <f>IFERROR((H17-H31)/H31,"")</f>
+        <f>IFERROR((H17-H31)/H17,"")</f>
         <v/>
       </c>
       <c r="I45" s="10">
-        <f>IFERROR((I17-I31)/I31,"")</f>
+        <f>IFERROR((I17-I31)/I17,"")</f>
         <v/>
       </c>
       <c r="J45" s="10">
-        <f>IFERROR((J17-J31)/J31,"")</f>
+        <f>IFERROR((J17-J31)/J17,"")</f>
         <v/>
       </c>
       <c r="K45" s="10">
-        <f>IFERROR((K17-K31)/K31,"")</f>
+        <f>IFERROR((K17-K31)/K17,"")</f>
         <v/>
       </c>
       <c r="L45" s="10">
-        <f>IFERROR((L17-L31)/L31,"")</f>
+        <f>IFERROR((L17-L31)/L17,"")</f>
         <v/>
       </c>
       <c r="M45" s="10">
-        <f>IFERROR((M17-M31)/M31,"")</f>
+        <f>IFERROR((M17-M31)/M17,"")</f>
         <v/>
       </c>
     </row>
@@ -7944,7 +7944,7 @@
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>% Diff  =  (ours − client) ÷ client      [green ≤2%  ·  amber 2–5%  ·  red &gt;5%]</t>
+          <t>% Diff  =  (ours − client) ÷ ours      [green ≤2%  ·  amber 2–5%  ·  red &gt;5%]</t>
         </is>
       </c>
     </row>
@@ -8022,51 +8022,51 @@
         </is>
       </c>
       <c r="B79" s="10">
-        <f>IFERROR((B51-B65)/B65,"")</f>
+        <f>IFERROR((B51-B65)/B51,"")</f>
         <v/>
       </c>
       <c r="C79" s="10">
-        <f>IFERROR((C51-C65)/C65,"")</f>
+        <f>IFERROR((C51-C65)/C51,"")</f>
         <v/>
       </c>
       <c r="D79" s="10">
-        <f>IFERROR((D51-D65)/D65,"")</f>
+        <f>IFERROR((D51-D65)/D51,"")</f>
         <v/>
       </c>
       <c r="E79" s="10">
-        <f>IFERROR((E51-E65)/E65,"")</f>
+        <f>IFERROR((E51-E65)/E51,"")</f>
         <v/>
       </c>
       <c r="F79" s="10">
-        <f>IFERROR((F51-F65)/F65,"")</f>
+        <f>IFERROR((F51-F65)/F51,"")</f>
         <v/>
       </c>
       <c r="G79" s="10">
-        <f>IFERROR((G51-G65)/G65,"")</f>
+        <f>IFERROR((G51-G65)/G51,"")</f>
         <v/>
       </c>
       <c r="H79" s="10">
-        <f>IFERROR((H51-H65)/H65,"")</f>
+        <f>IFERROR((H51-H65)/H51,"")</f>
         <v/>
       </c>
       <c r="I79" s="10">
-        <f>IFERROR((I51-I65)/I65,"")</f>
+        <f>IFERROR((I51-I65)/I51,"")</f>
         <v/>
       </c>
       <c r="J79" s="10">
-        <f>IFERROR((J51-J65)/J65,"")</f>
+        <f>IFERROR((J51-J65)/J51,"")</f>
         <v/>
       </c>
       <c r="K79" s="10">
-        <f>IFERROR((K51-K65)/K65,"")</f>
+        <f>IFERROR((K51-K65)/K51,"")</f>
         <v/>
       </c>
       <c r="L79" s="10">
-        <f>IFERROR((L51-L65)/L65,"")</f>
+        <f>IFERROR((L51-L65)/L51,"")</f>
         <v/>
       </c>
       <c r="M79" s="10">
-        <f>IFERROR((M51-M65)/M65,"")</f>
+        <f>IFERROR((M51-M65)/M51,"")</f>
         <v/>
       </c>
     </row>
@@ -8077,51 +8077,51 @@
         </is>
       </c>
       <c r="B80" s="10">
-        <f>IFERROR((B52-B66)/B66,"")</f>
+        <f>IFERROR((B52-B66)/B52,"")</f>
         <v/>
       </c>
       <c r="C80" s="10">
-        <f>IFERROR((C52-C66)/C66,"")</f>
+        <f>IFERROR((C52-C66)/C52,"")</f>
         <v/>
       </c>
       <c r="D80" s="10">
-        <f>IFERROR((D52-D66)/D66,"")</f>
+        <f>IFERROR((D52-D66)/D52,"")</f>
         <v/>
       </c>
       <c r="E80" s="10">
-        <f>IFERROR((E52-E66)/E66,"")</f>
+        <f>IFERROR((E52-E66)/E52,"")</f>
         <v/>
       </c>
       <c r="F80" s="10">
-        <f>IFERROR((F52-F66)/F66,"")</f>
+        <f>IFERROR((F52-F66)/F52,"")</f>
         <v/>
       </c>
       <c r="G80" s="10">
-        <f>IFERROR((G52-G66)/G66,"")</f>
+        <f>IFERROR((G52-G66)/G52,"")</f>
         <v/>
       </c>
       <c r="H80" s="10">
-        <f>IFERROR((H52-H66)/H66,"")</f>
+        <f>IFERROR((H52-H66)/H52,"")</f>
         <v/>
       </c>
       <c r="I80" s="10">
-        <f>IFERROR((I52-I66)/I66,"")</f>
+        <f>IFERROR((I52-I66)/I52,"")</f>
         <v/>
       </c>
       <c r="J80" s="10">
-        <f>IFERROR((J52-J66)/J66,"")</f>
+        <f>IFERROR((J52-J66)/J52,"")</f>
         <v/>
       </c>
       <c r="K80" s="10">
-        <f>IFERROR((K52-K66)/K66,"")</f>
+        <f>IFERROR((K52-K66)/K52,"")</f>
         <v/>
       </c>
       <c r="L80" s="10">
-        <f>IFERROR((L52-L66)/L66,"")</f>
+        <f>IFERROR((L52-L66)/L52,"")</f>
         <v/>
       </c>
       <c r="M80" s="10">
-        <f>IFERROR((M52-M66)/M66,"")</f>
+        <f>IFERROR((M52-M66)/M52,"")</f>
         <v/>
       </c>
     </row>
@@ -8132,51 +8132,51 @@
         </is>
       </c>
       <c r="B81" s="10">
-        <f>IFERROR((B53-B67)/B67,"")</f>
+        <f>IFERROR((B53-B67)/B53,"")</f>
         <v/>
       </c>
       <c r="C81" s="10">
-        <f>IFERROR((C53-C67)/C67,"")</f>
+        <f>IFERROR((C53-C67)/C53,"")</f>
         <v/>
       </c>
       <c r="D81" s="10">
-        <f>IFERROR((D53-D67)/D67,"")</f>
+        <f>IFERROR((D53-D67)/D53,"")</f>
         <v/>
       </c>
       <c r="E81" s="10">
-        <f>IFERROR((E53-E67)/E67,"")</f>
+        <f>IFERROR((E53-E67)/E53,"")</f>
         <v/>
       </c>
       <c r="F81" s="10">
-        <f>IFERROR((F53-F67)/F67,"")</f>
+        <f>IFERROR((F53-F67)/F53,"")</f>
         <v/>
       </c>
       <c r="G81" s="10">
-        <f>IFERROR((G53-G67)/G67,"")</f>
+        <f>IFERROR((G53-G67)/G53,"")</f>
         <v/>
       </c>
       <c r="H81" s="10">
-        <f>IFERROR((H53-H67)/H67,"")</f>
+        <f>IFERROR((H53-H67)/H53,"")</f>
         <v/>
       </c>
       <c r="I81" s="10">
-        <f>IFERROR((I53-I67)/I67,"")</f>
+        <f>IFERROR((I53-I67)/I53,"")</f>
         <v/>
       </c>
       <c r="J81" s="10">
-        <f>IFERROR((J53-J67)/J67,"")</f>
+        <f>IFERROR((J53-J67)/J53,"")</f>
         <v/>
       </c>
       <c r="K81" s="10">
-        <f>IFERROR((K53-K67)/K67,"")</f>
+        <f>IFERROR((K53-K67)/K53,"")</f>
         <v/>
       </c>
       <c r="L81" s="10">
-        <f>IFERROR((L53-L67)/L67,"")</f>
+        <f>IFERROR((L53-L67)/L53,"")</f>
         <v/>
       </c>
       <c r="M81" s="10">
-        <f>IFERROR((M53-M67)/M67,"")</f>
+        <f>IFERROR((M53-M67)/M53,"")</f>
         <v/>
       </c>
     </row>
@@ -8187,51 +8187,51 @@
         </is>
       </c>
       <c r="B82" s="10">
-        <f>IFERROR((B54-B68)/B68,"")</f>
+        <f>IFERROR((B54-B68)/B54,"")</f>
         <v/>
       </c>
       <c r="C82" s="10">
-        <f>IFERROR((C54-C68)/C68,"")</f>
+        <f>IFERROR((C54-C68)/C54,"")</f>
         <v/>
       </c>
       <c r="D82" s="10">
-        <f>IFERROR((D54-D68)/D68,"")</f>
+        <f>IFERROR((D54-D68)/D54,"")</f>
         <v/>
       </c>
       <c r="E82" s="10">
-        <f>IFERROR((E54-E68)/E68,"")</f>
+        <f>IFERROR((E54-E68)/E54,"")</f>
         <v/>
       </c>
       <c r="F82" s="10">
-        <f>IFERROR((F54-F68)/F68,"")</f>
+        <f>IFERROR((F54-F68)/F54,"")</f>
         <v/>
       </c>
       <c r="G82" s="10">
-        <f>IFERROR((G54-G68)/G68,"")</f>
+        <f>IFERROR((G54-G68)/G54,"")</f>
         <v/>
       </c>
       <c r="H82" s="10">
-        <f>IFERROR((H54-H68)/H68,"")</f>
+        <f>IFERROR((H54-H68)/H54,"")</f>
         <v/>
       </c>
       <c r="I82" s="10">
-        <f>IFERROR((I54-I68)/I68,"")</f>
+        <f>IFERROR((I54-I68)/I54,"")</f>
         <v/>
       </c>
       <c r="J82" s="10">
-        <f>IFERROR((J54-J68)/J68,"")</f>
+        <f>IFERROR((J54-J68)/J54,"")</f>
         <v/>
       </c>
       <c r="K82" s="10">
-        <f>IFERROR((K54-K68)/K68,"")</f>
+        <f>IFERROR((K54-K68)/K54,"")</f>
         <v/>
       </c>
       <c r="L82" s="10">
-        <f>IFERROR((L54-L68)/L68,"")</f>
+        <f>IFERROR((L54-L68)/L54,"")</f>
         <v/>
       </c>
       <c r="M82" s="10">
-        <f>IFERROR((M54-M68)/M68,"")</f>
+        <f>IFERROR((M54-M68)/M54,"")</f>
         <v/>
       </c>
     </row>
@@ -8242,51 +8242,51 @@
         </is>
       </c>
       <c r="B83" s="10">
-        <f>IFERROR((B55-B69)/B69,"")</f>
+        <f>IFERROR((B55-B69)/B55,"")</f>
         <v/>
       </c>
       <c r="C83" s="10">
-        <f>IFERROR((C55-C69)/C69,"")</f>
+        <f>IFERROR((C55-C69)/C55,"")</f>
         <v/>
       </c>
       <c r="D83" s="10">
-        <f>IFERROR((D55-D69)/D69,"")</f>
+        <f>IFERROR((D55-D69)/D55,"")</f>
         <v/>
       </c>
       <c r="E83" s="10">
-        <f>IFERROR((E55-E69)/E69,"")</f>
+        <f>IFERROR((E55-E69)/E55,"")</f>
         <v/>
       </c>
       <c r="F83" s="10">
-        <f>IFERROR((F55-F69)/F69,"")</f>
+        <f>IFERROR((F55-F69)/F55,"")</f>
         <v/>
       </c>
       <c r="G83" s="10">
-        <f>IFERROR((G55-G69)/G69,"")</f>
+        <f>IFERROR((G55-G69)/G55,"")</f>
         <v/>
       </c>
       <c r="H83" s="10">
-        <f>IFERROR((H55-H69)/H69,"")</f>
+        <f>IFERROR((H55-H69)/H55,"")</f>
         <v/>
       </c>
       <c r="I83" s="10">
-        <f>IFERROR((I55-I69)/I69,"")</f>
+        <f>IFERROR((I55-I69)/I55,"")</f>
         <v/>
       </c>
       <c r="J83" s="10">
-        <f>IFERROR((J55-J69)/J69,"")</f>
+        <f>IFERROR((J55-J69)/J55,"")</f>
         <v/>
       </c>
       <c r="K83" s="10">
-        <f>IFERROR((K55-K69)/K69,"")</f>
+        <f>IFERROR((K55-K69)/K55,"")</f>
         <v/>
       </c>
       <c r="L83" s="10">
-        <f>IFERROR((L55-L69)/L69,"")</f>
+        <f>IFERROR((L55-L69)/L55,"")</f>
         <v/>
       </c>
       <c r="M83" s="10">
-        <f>IFERROR((M55-M69)/M69,"")</f>
+        <f>IFERROR((M55-M69)/M55,"")</f>
         <v/>
       </c>
     </row>
@@ -8297,51 +8297,51 @@
         </is>
       </c>
       <c r="B84" s="10">
-        <f>IFERROR((B56-B70)/B70,"")</f>
+        <f>IFERROR((B56-B70)/B56,"")</f>
         <v/>
       </c>
       <c r="C84" s="10">
-        <f>IFERROR((C56-C70)/C70,"")</f>
+        <f>IFERROR((C56-C70)/C56,"")</f>
         <v/>
       </c>
       <c r="D84" s="10">
-        <f>IFERROR((D56-D70)/D70,"")</f>
+        <f>IFERROR((D56-D70)/D56,"")</f>
         <v/>
       </c>
       <c r="E84" s="10">
-        <f>IFERROR((E56-E70)/E70,"")</f>
+        <f>IFERROR((E56-E70)/E56,"")</f>
         <v/>
       </c>
       <c r="F84" s="10">
-        <f>IFERROR((F56-F70)/F70,"")</f>
+        <f>IFERROR((F56-F70)/F56,"")</f>
         <v/>
       </c>
       <c r="G84" s="10">
-        <f>IFERROR((G56-G70)/G70,"")</f>
+        <f>IFERROR((G56-G70)/G56,"")</f>
         <v/>
       </c>
       <c r="H84" s="10">
-        <f>IFERROR((H56-H70)/H70,"")</f>
+        <f>IFERROR((H56-H70)/H56,"")</f>
         <v/>
       </c>
       <c r="I84" s="10">
-        <f>IFERROR((I56-I70)/I70,"")</f>
+        <f>IFERROR((I56-I70)/I56,"")</f>
         <v/>
       </c>
       <c r="J84" s="10">
-        <f>IFERROR((J56-J70)/J70,"")</f>
+        <f>IFERROR((J56-J70)/J56,"")</f>
         <v/>
       </c>
       <c r="K84" s="10">
-        <f>IFERROR((K56-K70)/K70,"")</f>
+        <f>IFERROR((K56-K70)/K56,"")</f>
         <v/>
       </c>
       <c r="L84" s="10">
-        <f>IFERROR((L56-L70)/L70,"")</f>
+        <f>IFERROR((L56-L70)/L56,"")</f>
         <v/>
       </c>
       <c r="M84" s="10">
-        <f>IFERROR((M56-M70)/M70,"")</f>
+        <f>IFERROR((M56-M70)/M56,"")</f>
         <v/>
       </c>
     </row>
@@ -8352,51 +8352,51 @@
         </is>
       </c>
       <c r="B85" s="10">
-        <f>IFERROR((B57-B71)/B71,"")</f>
+        <f>IFERROR((B57-B71)/B57,"")</f>
         <v/>
       </c>
       <c r="C85" s="10">
-        <f>IFERROR((C57-C71)/C71,"")</f>
+        <f>IFERROR((C57-C71)/C57,"")</f>
         <v/>
       </c>
       <c r="D85" s="10">
-        <f>IFERROR((D57-D71)/D71,"")</f>
+        <f>IFERROR((D57-D71)/D57,"")</f>
         <v/>
       </c>
       <c r="E85" s="10">
-        <f>IFERROR((E57-E71)/E71,"")</f>
+        <f>IFERROR((E57-E71)/E57,"")</f>
         <v/>
       </c>
       <c r="F85" s="10">
-        <f>IFERROR((F57-F71)/F71,"")</f>
+        <f>IFERROR((F57-F71)/F57,"")</f>
         <v/>
       </c>
       <c r="G85" s="10">
-        <f>IFERROR((G57-G71)/G71,"")</f>
+        <f>IFERROR((G57-G71)/G57,"")</f>
         <v/>
       </c>
       <c r="H85" s="10">
-        <f>IFERROR((H57-H71)/H71,"")</f>
+        <f>IFERROR((H57-H71)/H57,"")</f>
         <v/>
       </c>
       <c r="I85" s="10">
-        <f>IFERROR((I57-I71)/I71,"")</f>
+        <f>IFERROR((I57-I71)/I57,"")</f>
         <v/>
       </c>
       <c r="J85" s="10">
-        <f>IFERROR((J57-J71)/J71,"")</f>
+        <f>IFERROR((J57-J71)/J57,"")</f>
         <v/>
       </c>
       <c r="K85" s="10">
-        <f>IFERROR((K57-K71)/K71,"")</f>
+        <f>IFERROR((K57-K71)/K57,"")</f>
         <v/>
       </c>
       <c r="L85" s="10">
-        <f>IFERROR((L57-L71)/L71,"")</f>
+        <f>IFERROR((L57-L71)/L57,"")</f>
         <v/>
       </c>
       <c r="M85" s="10">
-        <f>IFERROR((M57-M71)/M71,"")</f>
+        <f>IFERROR((M57-M71)/M57,"")</f>
         <v/>
       </c>
     </row>
@@ -8407,51 +8407,51 @@
         </is>
       </c>
       <c r="B86" s="10">
-        <f>IFERROR((B58-B72)/B72,"")</f>
+        <f>IFERROR((B58-B72)/B58,"")</f>
         <v/>
       </c>
       <c r="C86" s="10">
-        <f>IFERROR((C58-C72)/C72,"")</f>
+        <f>IFERROR((C58-C72)/C58,"")</f>
         <v/>
       </c>
       <c r="D86" s="10">
-        <f>IFERROR((D58-D72)/D72,"")</f>
+        <f>IFERROR((D58-D72)/D58,"")</f>
         <v/>
       </c>
       <c r="E86" s="10">
-        <f>IFERROR((E58-E72)/E72,"")</f>
+        <f>IFERROR((E58-E72)/E58,"")</f>
         <v/>
       </c>
       <c r="F86" s="10">
-        <f>IFERROR((F58-F72)/F72,"")</f>
+        <f>IFERROR((F58-F72)/F58,"")</f>
         <v/>
       </c>
       <c r="G86" s="10">
-        <f>IFERROR((G58-G72)/G72,"")</f>
+        <f>IFERROR((G58-G72)/G58,"")</f>
         <v/>
       </c>
       <c r="H86" s="10">
-        <f>IFERROR((H58-H72)/H72,"")</f>
+        <f>IFERROR((H58-H72)/H58,"")</f>
         <v/>
       </c>
       <c r="I86" s="10">
-        <f>IFERROR((I58-I72)/I72,"")</f>
+        <f>IFERROR((I58-I72)/I58,"")</f>
         <v/>
       </c>
       <c r="J86" s="10">
-        <f>IFERROR((J58-J72)/J72,"")</f>
+        <f>IFERROR((J58-J72)/J58,"")</f>
         <v/>
       </c>
       <c r="K86" s="10">
-        <f>IFERROR((K58-K72)/K72,"")</f>
+        <f>IFERROR((K58-K72)/K58,"")</f>
         <v/>
       </c>
       <c r="L86" s="10">
-        <f>IFERROR((L58-L72)/L72,"")</f>
+        <f>IFERROR((L58-L72)/L58,"")</f>
         <v/>
       </c>
       <c r="M86" s="10">
-        <f>IFERROR((M58-M72)/M72,"")</f>
+        <f>IFERROR((M58-M72)/M58,"")</f>
         <v/>
       </c>
     </row>
@@ -8462,51 +8462,51 @@
         </is>
       </c>
       <c r="B87" s="10">
-        <f>IFERROR((B59-B73)/B73,"")</f>
+        <f>IFERROR((B59-B73)/B59,"")</f>
         <v/>
       </c>
       <c r="C87" s="10">
-        <f>IFERROR((C59-C73)/C73,"")</f>
+        <f>IFERROR((C59-C73)/C59,"")</f>
         <v/>
       </c>
       <c r="D87" s="10">
-        <f>IFERROR((D59-D73)/D73,"")</f>
+        <f>IFERROR((D59-D73)/D59,"")</f>
         <v/>
       </c>
       <c r="E87" s="10">
-        <f>IFERROR((E59-E73)/E73,"")</f>
+        <f>IFERROR((E59-E73)/E59,"")</f>
         <v/>
       </c>
       <c r="F87" s="10">
-        <f>IFERROR((F59-F73)/F73,"")</f>
+        <f>IFERROR((F59-F73)/F59,"")</f>
         <v/>
       </c>
       <c r="G87" s="10">
-        <f>IFERROR((G59-G73)/G73,"")</f>
+        <f>IFERROR((G59-G73)/G59,"")</f>
         <v/>
       </c>
       <c r="H87" s="10">
-        <f>IFERROR((H59-H73)/H73,"")</f>
+        <f>IFERROR((H59-H73)/H59,"")</f>
         <v/>
       </c>
       <c r="I87" s="10">
-        <f>IFERROR((I59-I73)/I73,"")</f>
+        <f>IFERROR((I59-I73)/I59,"")</f>
         <v/>
       </c>
       <c r="J87" s="10">
-        <f>IFERROR((J59-J73)/J73,"")</f>
+        <f>IFERROR((J59-J73)/J59,"")</f>
         <v/>
       </c>
       <c r="K87" s="10">
-        <f>IFERROR((K59-K73)/K73,"")</f>
+        <f>IFERROR((K59-K73)/K59,"")</f>
         <v/>
       </c>
       <c r="L87" s="10">
-        <f>IFERROR((L59-L73)/L73,"")</f>
+        <f>IFERROR((L59-L73)/L59,"")</f>
         <v/>
       </c>
       <c r="M87" s="10">
-        <f>IFERROR((M59-M73)/M73,"")</f>
+        <f>IFERROR((M59-M73)/M59,"")</f>
         <v/>
       </c>
     </row>
@@ -8517,51 +8517,51 @@
         </is>
       </c>
       <c r="B88" s="10">
-        <f>IFERROR((B60-B74)/B74,"")</f>
+        <f>IFERROR((B60-B74)/B60,"")</f>
         <v/>
       </c>
       <c r="C88" s="10">
-        <f>IFERROR((C60-C74)/C74,"")</f>
+        <f>IFERROR((C60-C74)/C60,"")</f>
         <v/>
       </c>
       <c r="D88" s="10">
-        <f>IFERROR((D60-D74)/D74,"")</f>
+        <f>IFERROR((D60-D74)/D60,"")</f>
         <v/>
       </c>
       <c r="E88" s="10">
-        <f>IFERROR((E60-E74)/E74,"")</f>
+        <f>IFERROR((E60-E74)/E60,"")</f>
         <v/>
       </c>
       <c r="F88" s="10">
-        <f>IFERROR((F60-F74)/F74,"")</f>
+        <f>IFERROR((F60-F74)/F60,"")</f>
         <v/>
       </c>
       <c r="G88" s="10">
-        <f>IFERROR((G60-G74)/G74,"")</f>
+        <f>IFERROR((G60-G74)/G60,"")</f>
         <v/>
       </c>
       <c r="H88" s="10">
-        <f>IFERROR((H60-H74)/H74,"")</f>
+        <f>IFERROR((H60-H74)/H60,"")</f>
         <v/>
       </c>
       <c r="I88" s="10">
-        <f>IFERROR((I60-I74)/I74,"")</f>
+        <f>IFERROR((I60-I74)/I60,"")</f>
         <v/>
       </c>
       <c r="J88" s="10">
-        <f>IFERROR((J60-J74)/J74,"")</f>
+        <f>IFERROR((J60-J74)/J60,"")</f>
         <v/>
       </c>
       <c r="K88" s="10">
-        <f>IFERROR((K60-K74)/K74,"")</f>
+        <f>IFERROR((K60-K74)/K60,"")</f>
         <v/>
       </c>
       <c r="L88" s="10">
-        <f>IFERROR((L60-L74)/L74,"")</f>
+        <f>IFERROR((L60-L74)/L60,"")</f>
         <v/>
       </c>
       <c r="M88" s="10">
-        <f>IFERROR((M60-M74)/M74,"")</f>
+        <f>IFERROR((M60-M74)/M60,"")</f>
         <v/>
       </c>
     </row>
@@ -8572,51 +8572,51 @@
         </is>
       </c>
       <c r="B89" s="10">
-        <f>IFERROR((B61-B75)/B75,"")</f>
+        <f>IFERROR((B61-B75)/B61,"")</f>
         <v/>
       </c>
       <c r="C89" s="10">
-        <f>IFERROR((C61-C75)/C75,"")</f>
+        <f>IFERROR((C61-C75)/C61,"")</f>
         <v/>
       </c>
       <c r="D89" s="10">
-        <f>IFERROR((D61-D75)/D75,"")</f>
+        <f>IFERROR((D61-D75)/D61,"")</f>
         <v/>
       </c>
       <c r="E89" s="10">
-        <f>IFERROR((E61-E75)/E75,"")</f>
+        <f>IFERROR((E61-E75)/E61,"")</f>
         <v/>
       </c>
       <c r="F89" s="10">
-        <f>IFERROR((F61-F75)/F75,"")</f>
+        <f>IFERROR((F61-F75)/F61,"")</f>
         <v/>
       </c>
       <c r="G89" s="10">
-        <f>IFERROR((G61-G75)/G75,"")</f>
+        <f>IFERROR((G61-G75)/G61,"")</f>
         <v/>
       </c>
       <c r="H89" s="10">
-        <f>IFERROR((H61-H75)/H75,"")</f>
+        <f>IFERROR((H61-H75)/H61,"")</f>
         <v/>
       </c>
       <c r="I89" s="10">
-        <f>IFERROR((I61-I75)/I75,"")</f>
+        <f>IFERROR((I61-I75)/I61,"")</f>
         <v/>
       </c>
       <c r="J89" s="10">
-        <f>IFERROR((J61-J75)/J75,"")</f>
+        <f>IFERROR((J61-J75)/J61,"")</f>
         <v/>
       </c>
       <c r="K89" s="10">
-        <f>IFERROR((K61-K75)/K75,"")</f>
+        <f>IFERROR((K61-K75)/K61,"")</f>
         <v/>
       </c>
       <c r="L89" s="10">
-        <f>IFERROR((L61-L75)/L75,"")</f>
+        <f>IFERROR((L61-L75)/L61,"")</f>
         <v/>
       </c>
       <c r="M89" s="10">
-        <f>IFERROR((M61-M75)/M75,"")</f>
+        <f>IFERROR((M61-M75)/M61,"")</f>
         <v/>
       </c>
     </row>
@@ -9542,7 +9542,7 @@
     <row r="121">
       <c r="A121" s="4" t="inlineStr">
         <is>
-          <t>% Diff  =  (ours − client) ÷ client      [green ≤2%  ·  amber 2–5%  ·  red &gt;5%]</t>
+          <t>% Diff  =  (ours − client) ÷ ours      [green ≤2%  ·  amber 2–5%  ·  red &gt;5%]</t>
         </is>
       </c>
     </row>
@@ -9620,51 +9620,51 @@
         </is>
       </c>
       <c r="B123" s="10">
-        <f>IFERROR((B95-B109)/B109,"")</f>
+        <f>IFERROR((B95-B109)/B95,"")</f>
         <v/>
       </c>
       <c r="C123" s="10">
-        <f>IFERROR((C95-C109)/C109,"")</f>
+        <f>IFERROR((C95-C109)/C95,"")</f>
         <v/>
       </c>
       <c r="D123" s="10">
-        <f>IFERROR((D95-D109)/D109,"")</f>
+        <f>IFERROR((D95-D109)/D95,"")</f>
         <v/>
       </c>
       <c r="E123" s="10">
-        <f>IFERROR((E95-E109)/E109,"")</f>
+        <f>IFERROR((E95-E109)/E95,"")</f>
         <v/>
       </c>
       <c r="F123" s="10">
-        <f>IFERROR((F95-F109)/F109,"")</f>
+        <f>IFERROR((F95-F109)/F95,"")</f>
         <v/>
       </c>
       <c r="G123" s="10">
-        <f>IFERROR((G95-G109)/G109,"")</f>
+        <f>IFERROR((G95-G109)/G95,"")</f>
         <v/>
       </c>
       <c r="H123" s="10">
-        <f>IFERROR((H95-H109)/H109,"")</f>
+        <f>IFERROR((H95-H109)/H95,"")</f>
         <v/>
       </c>
       <c r="I123" s="10">
-        <f>IFERROR((I95-I109)/I109,"")</f>
+        <f>IFERROR((I95-I109)/I95,"")</f>
         <v/>
       </c>
       <c r="J123" s="10">
-        <f>IFERROR((J95-J109)/J109,"")</f>
+        <f>IFERROR((J95-J109)/J95,"")</f>
         <v/>
       </c>
       <c r="K123" s="10">
-        <f>IFERROR((K95-K109)/K109,"")</f>
+        <f>IFERROR((K95-K109)/K95,"")</f>
         <v/>
       </c>
       <c r="L123" s="10">
-        <f>IFERROR((L95-L109)/L109,"")</f>
+        <f>IFERROR((L95-L109)/L95,"")</f>
         <v/>
       </c>
       <c r="M123" s="10">
-        <f>IFERROR((M95-M109)/M109,"")</f>
+        <f>IFERROR((M95-M109)/M95,"")</f>
         <v/>
       </c>
     </row>
@@ -9675,51 +9675,51 @@
         </is>
       </c>
       <c r="B124" s="10">
-        <f>IFERROR((B96-B110)/B110,"")</f>
+        <f>IFERROR((B96-B110)/B96,"")</f>
         <v/>
       </c>
       <c r="C124" s="10">
-        <f>IFERROR((C96-C110)/C110,"")</f>
+        <f>IFERROR((C96-C110)/C96,"")</f>
         <v/>
       </c>
       <c r="D124" s="10">
-        <f>IFERROR((D96-D110)/D110,"")</f>
+        <f>IFERROR((D96-D110)/D96,"")</f>
         <v/>
       </c>
       <c r="E124" s="10">
-        <f>IFERROR((E96-E110)/E110,"")</f>
+        <f>IFERROR((E96-E110)/E96,"")</f>
         <v/>
       </c>
       <c r="F124" s="10">
-        <f>IFERROR((F96-F110)/F110,"")</f>
+        <f>IFERROR((F96-F110)/F96,"")</f>
         <v/>
       </c>
       <c r="G124" s="10">
-        <f>IFERROR((G96-G110)/G110,"")</f>
+        <f>IFERROR((G96-G110)/G96,"")</f>
         <v/>
       </c>
       <c r="H124" s="10">
-        <f>IFERROR((H96-H110)/H110,"")</f>
+        <f>IFERROR((H96-H110)/H96,"")</f>
         <v/>
       </c>
       <c r="I124" s="10">
-        <f>IFERROR((I96-I110)/I110,"")</f>
+        <f>IFERROR((I96-I110)/I96,"")</f>
         <v/>
       </c>
       <c r="J124" s="10">
-        <f>IFERROR((J96-J110)/J110,"")</f>
+        <f>IFERROR((J96-J110)/J96,"")</f>
         <v/>
       </c>
       <c r="K124" s="10">
-        <f>IFERROR((K96-K110)/K110,"")</f>
+        <f>IFERROR((K96-K110)/K96,"")</f>
         <v/>
       </c>
       <c r="L124" s="10">
-        <f>IFERROR((L96-L110)/L110,"")</f>
+        <f>IFERROR((L96-L110)/L96,"")</f>
         <v/>
       </c>
       <c r="M124" s="10">
-        <f>IFERROR((M96-M110)/M110,"")</f>
+        <f>IFERROR((M96-M110)/M96,"")</f>
         <v/>
       </c>
     </row>
@@ -9730,51 +9730,51 @@
         </is>
       </c>
       <c r="B125" s="10">
-        <f>IFERROR((B97-B111)/B111,"")</f>
+        <f>IFERROR((B97-B111)/B97,"")</f>
         <v/>
       </c>
       <c r="C125" s="10">
-        <f>IFERROR((C97-C111)/C111,"")</f>
+        <f>IFERROR((C97-C111)/C97,"")</f>
         <v/>
       </c>
       <c r="D125" s="10">
-        <f>IFERROR((D97-D111)/D111,"")</f>
+        <f>IFERROR((D97-D111)/D97,"")</f>
         <v/>
       </c>
       <c r="E125" s="10">
-        <f>IFERROR((E97-E111)/E111,"")</f>
+        <f>IFERROR((E97-E111)/E97,"")</f>
         <v/>
       </c>
       <c r="F125" s="10">
-        <f>IFERROR((F97-F111)/F111,"")</f>
+        <f>IFERROR((F97-F111)/F97,"")</f>
         <v/>
       </c>
       <c r="G125" s="10">
-        <f>IFERROR((G97-G111)/G111,"")</f>
+        <f>IFERROR((G97-G111)/G97,"")</f>
         <v/>
       </c>
       <c r="H125" s="10">
-        <f>IFERROR((H97-H111)/H111,"")</f>
+        <f>IFERROR((H97-H111)/H97,"")</f>
         <v/>
       </c>
       <c r="I125" s="10">
-        <f>IFERROR((I97-I111)/I111,"")</f>
+        <f>IFERROR((I97-I111)/I97,"")</f>
         <v/>
       </c>
       <c r="J125" s="10">
-        <f>IFERROR((J97-J111)/J111,"")</f>
+        <f>IFERROR((J97-J111)/J97,"")</f>
         <v/>
       </c>
       <c r="K125" s="10">
-        <f>IFERROR((K97-K111)/K111,"")</f>
+        <f>IFERROR((K97-K111)/K97,"")</f>
         <v/>
       </c>
       <c r="L125" s="10">
-        <f>IFERROR((L97-L111)/L111,"")</f>
+        <f>IFERROR((L97-L111)/L97,"")</f>
         <v/>
       </c>
       <c r="M125" s="10">
-        <f>IFERROR((M97-M111)/M111,"")</f>
+        <f>IFERROR((M97-M111)/M97,"")</f>
         <v/>
       </c>
     </row>
@@ -9785,51 +9785,51 @@
         </is>
       </c>
       <c r="B126" s="10">
-        <f>IFERROR((B98-B112)/B112,"")</f>
+        <f>IFERROR((B98-B112)/B98,"")</f>
         <v/>
       </c>
       <c r="C126" s="10">
-        <f>IFERROR((C98-C112)/C112,"")</f>
+        <f>IFERROR((C98-C112)/C98,"")</f>
         <v/>
       </c>
       <c r="D126" s="10">
-        <f>IFERROR((D98-D112)/D112,"")</f>
+        <f>IFERROR((D98-D112)/D98,"")</f>
         <v/>
       </c>
       <c r="E126" s="10">
-        <f>IFERROR((E98-E112)/E112,"")</f>
+        <f>IFERROR((E98-E112)/E98,"")</f>
         <v/>
       </c>
       <c r="F126" s="10">
-        <f>IFERROR((F98-F112)/F112,"")</f>
+        <f>IFERROR((F98-F112)/F98,"")</f>
         <v/>
       </c>
       <c r="G126" s="10">
-        <f>IFERROR((G98-G112)/G112,"")</f>
+        <f>IFERROR((G98-G112)/G98,"")</f>
         <v/>
       </c>
       <c r="H126" s="10">
-        <f>IFERROR((H98-H112)/H112,"")</f>
+        <f>IFERROR((H98-H112)/H98,"")</f>
         <v/>
       </c>
       <c r="I126" s="10">
-        <f>IFERROR((I98-I112)/I112,"")</f>
+        <f>IFERROR((I98-I112)/I98,"")</f>
         <v/>
       </c>
       <c r="J126" s="10">
-        <f>IFERROR((J98-J112)/J112,"")</f>
+        <f>IFERROR((J98-J112)/J98,"")</f>
         <v/>
       </c>
       <c r="K126" s="10">
-        <f>IFERROR((K98-K112)/K112,"")</f>
+        <f>IFERROR((K98-K112)/K98,"")</f>
         <v/>
       </c>
       <c r="L126" s="10">
-        <f>IFERROR((L98-L112)/L112,"")</f>
+        <f>IFERROR((L98-L112)/L98,"")</f>
         <v/>
       </c>
       <c r="M126" s="10">
-        <f>IFERROR((M98-M112)/M112,"")</f>
+        <f>IFERROR((M98-M112)/M98,"")</f>
         <v/>
       </c>
     </row>
@@ -9840,51 +9840,51 @@
         </is>
       </c>
       <c r="B127" s="10">
-        <f>IFERROR((B99-B113)/B113,"")</f>
+        <f>IFERROR((B99-B113)/B99,"")</f>
         <v/>
       </c>
       <c r="C127" s="10">
-        <f>IFERROR((C99-C113)/C113,"")</f>
+        <f>IFERROR((C99-C113)/C99,"")</f>
         <v/>
       </c>
       <c r="D127" s="10">
-        <f>IFERROR((D99-D113)/D113,"")</f>
+        <f>IFERROR((D99-D113)/D99,"")</f>
         <v/>
       </c>
       <c r="E127" s="10">
-        <f>IFERROR((E99-E113)/E113,"")</f>
+        <f>IFERROR((E99-E113)/E99,"")</f>
         <v/>
       </c>
       <c r="F127" s="10">
-        <f>IFERROR((F99-F113)/F113,"")</f>
+        <f>IFERROR((F99-F113)/F99,"")</f>
         <v/>
       </c>
       <c r="G127" s="10">
-        <f>IFERROR((G99-G113)/G113,"")</f>
+        <f>IFERROR((G99-G113)/G99,"")</f>
         <v/>
       </c>
       <c r="H127" s="10">
-        <f>IFERROR((H99-H113)/H113,"")</f>
+        <f>IFERROR((H99-H113)/H99,"")</f>
         <v/>
       </c>
       <c r="I127" s="10">
-        <f>IFERROR((I99-I113)/I113,"")</f>
+        <f>IFERROR((I99-I113)/I99,"")</f>
         <v/>
       </c>
       <c r="J127" s="10">
-        <f>IFERROR((J99-J113)/J113,"")</f>
+        <f>IFERROR((J99-J113)/J99,"")</f>
         <v/>
       </c>
       <c r="K127" s="10">
-        <f>IFERROR((K99-K113)/K113,"")</f>
+        <f>IFERROR((K99-K113)/K99,"")</f>
         <v/>
       </c>
       <c r="L127" s="10">
-        <f>IFERROR((L99-L113)/L113,"")</f>
+        <f>IFERROR((L99-L113)/L99,"")</f>
         <v/>
       </c>
       <c r="M127" s="10">
-        <f>IFERROR((M99-M113)/M113,"")</f>
+        <f>IFERROR((M99-M113)/M99,"")</f>
         <v/>
       </c>
     </row>
@@ -9895,51 +9895,51 @@
         </is>
       </c>
       <c r="B128" s="10">
-        <f>IFERROR((B100-B114)/B114,"")</f>
+        <f>IFERROR((B100-B114)/B100,"")</f>
         <v/>
       </c>
       <c r="C128" s="10">
-        <f>IFERROR((C100-C114)/C114,"")</f>
+        <f>IFERROR((C100-C114)/C100,"")</f>
         <v/>
       </c>
       <c r="D128" s="10">
-        <f>IFERROR((D100-D114)/D114,"")</f>
+        <f>IFERROR((D100-D114)/D100,"")</f>
         <v/>
       </c>
       <c r="E128" s="10">
-        <f>IFERROR((E100-E114)/E114,"")</f>
+        <f>IFERROR((E100-E114)/E100,"")</f>
         <v/>
       </c>
       <c r="F128" s="10">
-        <f>IFERROR((F100-F114)/F114,"")</f>
+        <f>IFERROR((F100-F114)/F100,"")</f>
         <v/>
       </c>
       <c r="G128" s="10">
-        <f>IFERROR((G100-G114)/G114,"")</f>
+        <f>IFERROR((G100-G114)/G100,"")</f>
         <v/>
       </c>
       <c r="H128" s="10">
-        <f>IFERROR((H100-H114)/H114,"")</f>
+        <f>IFERROR((H100-H114)/H100,"")</f>
         <v/>
       </c>
       <c r="I128" s="10">
-        <f>IFERROR((I100-I114)/I114,"")</f>
+        <f>IFERROR((I100-I114)/I100,"")</f>
         <v/>
       </c>
       <c r="J128" s="10">
-        <f>IFERROR((J100-J114)/J114,"")</f>
+        <f>IFERROR((J100-J114)/J100,"")</f>
         <v/>
       </c>
       <c r="K128" s="10">
-        <f>IFERROR((K100-K114)/K114,"")</f>
+        <f>IFERROR((K100-K114)/K100,"")</f>
         <v/>
       </c>
       <c r="L128" s="10">
-        <f>IFERROR((L100-L114)/L114,"")</f>
+        <f>IFERROR((L100-L114)/L100,"")</f>
         <v/>
       </c>
       <c r="M128" s="10">
-        <f>IFERROR((M100-M114)/M114,"")</f>
+        <f>IFERROR((M100-M114)/M100,"")</f>
         <v/>
       </c>
     </row>
@@ -9950,51 +9950,51 @@
         </is>
       </c>
       <c r="B129" s="10">
-        <f>IFERROR((B101-B115)/B115,"")</f>
+        <f>IFERROR((B101-B115)/B101,"")</f>
         <v/>
       </c>
       <c r="C129" s="10">
-        <f>IFERROR((C101-C115)/C115,"")</f>
+        <f>IFERROR((C101-C115)/C101,"")</f>
         <v/>
       </c>
       <c r="D129" s="10">
-        <f>IFERROR((D101-D115)/D115,"")</f>
+        <f>IFERROR((D101-D115)/D101,"")</f>
         <v/>
       </c>
       <c r="E129" s="10">
-        <f>IFERROR((E101-E115)/E115,"")</f>
+        <f>IFERROR((E101-E115)/E101,"")</f>
         <v/>
       </c>
       <c r="F129" s="10">
-        <f>IFERROR((F101-F115)/F115,"")</f>
+        <f>IFERROR((F101-F115)/F101,"")</f>
         <v/>
       </c>
       <c r="G129" s="10">
-        <f>IFERROR((G101-G115)/G115,"")</f>
+        <f>IFERROR((G101-G115)/G101,"")</f>
         <v/>
       </c>
       <c r="H129" s="10">
-        <f>IFERROR((H101-H115)/H115,"")</f>
+        <f>IFERROR((H101-H115)/H101,"")</f>
         <v/>
       </c>
       <c r="I129" s="10">
-        <f>IFERROR((I101-I115)/I115,"")</f>
+        <f>IFERROR((I101-I115)/I101,"")</f>
         <v/>
       </c>
       <c r="J129" s="10">
-        <f>IFERROR((J101-J115)/J115,"")</f>
+        <f>IFERROR((J101-J115)/J101,"")</f>
         <v/>
       </c>
       <c r="K129" s="10">
-        <f>IFERROR((K101-K115)/K115,"")</f>
+        <f>IFERROR((K101-K115)/K101,"")</f>
         <v/>
       </c>
       <c r="L129" s="10">
-        <f>IFERROR((L101-L115)/L115,"")</f>
+        <f>IFERROR((L101-L115)/L101,"")</f>
         <v/>
       </c>
       <c r="M129" s="10">
-        <f>IFERROR((M101-M115)/M115,"")</f>
+        <f>IFERROR((M101-M115)/M101,"")</f>
         <v/>
       </c>
     </row>
@@ -10005,51 +10005,51 @@
         </is>
       </c>
       <c r="B130" s="10">
-        <f>IFERROR((B102-B116)/B116,"")</f>
+        <f>IFERROR((B102-B116)/B102,"")</f>
         <v/>
       </c>
       <c r="C130" s="10">
-        <f>IFERROR((C102-C116)/C116,"")</f>
+        <f>IFERROR((C102-C116)/C102,"")</f>
         <v/>
       </c>
       <c r="D130" s="10">
-        <f>IFERROR((D102-D116)/D116,"")</f>
+        <f>IFERROR((D102-D116)/D102,"")</f>
         <v/>
       </c>
       <c r="E130" s="10">
-        <f>IFERROR((E102-E116)/E116,"")</f>
+        <f>IFERROR((E102-E116)/E102,"")</f>
         <v/>
       </c>
       <c r="F130" s="10">
-        <f>IFERROR((F102-F116)/F116,"")</f>
+        <f>IFERROR((F102-F116)/F102,"")</f>
         <v/>
       </c>
       <c r="G130" s="10">
-        <f>IFERROR((G102-G116)/G116,"")</f>
+        <f>IFERROR((G102-G116)/G102,"")</f>
         <v/>
       </c>
       <c r="H130" s="10">
-        <f>IFERROR((H102-H116)/H116,"")</f>
+        <f>IFERROR((H102-H116)/H102,"")</f>
         <v/>
       </c>
       <c r="I130" s="10">
-        <f>IFERROR((I102-I116)/I116,"")</f>
+        <f>IFERROR((I102-I116)/I102,"")</f>
         <v/>
       </c>
       <c r="J130" s="10">
-        <f>IFERROR((J102-J116)/J116,"")</f>
+        <f>IFERROR((J102-J116)/J102,"")</f>
         <v/>
       </c>
       <c r="K130" s="10">
-        <f>IFERROR((K102-K116)/K116,"")</f>
+        <f>IFERROR((K102-K116)/K102,"")</f>
         <v/>
       </c>
       <c r="L130" s="10">
-        <f>IFERROR((L102-L116)/L116,"")</f>
+        <f>IFERROR((L102-L116)/L102,"")</f>
         <v/>
       </c>
       <c r="M130" s="10">
-        <f>IFERROR((M102-M116)/M116,"")</f>
+        <f>IFERROR((M102-M116)/M102,"")</f>
         <v/>
       </c>
     </row>
@@ -10060,51 +10060,51 @@
         </is>
       </c>
       <c r="B131" s="10">
-        <f>IFERROR((B103-B117)/B117,"")</f>
+        <f>IFERROR((B103-B117)/B103,"")</f>
         <v/>
       </c>
       <c r="C131" s="10">
-        <f>IFERROR((C103-C117)/C117,"")</f>
+        <f>IFERROR((C103-C117)/C103,"")</f>
         <v/>
       </c>
       <c r="D131" s="10">
-        <f>IFERROR((D103-D117)/D117,"")</f>
+        <f>IFERROR((D103-D117)/D103,"")</f>
         <v/>
       </c>
       <c r="E131" s="10">
-        <f>IFERROR((E103-E117)/E117,"")</f>
+        <f>IFERROR((E103-E117)/E103,"")</f>
         <v/>
       </c>
       <c r="F131" s="10">
-        <f>IFERROR((F103-F117)/F117,"")</f>
+        <f>IFERROR((F103-F117)/F103,"")</f>
         <v/>
       </c>
       <c r="G131" s="10">
-        <f>IFERROR((G103-G117)/G117,"")</f>
+        <f>IFERROR((G103-G117)/G103,"")</f>
         <v/>
       </c>
       <c r="H131" s="10">
-        <f>IFERROR((H103-H117)/H117,"")</f>
+        <f>IFERROR((H103-H117)/H103,"")</f>
         <v/>
       </c>
       <c r="I131" s="10">
-        <f>IFERROR((I103-I117)/I117,"")</f>
+        <f>IFERROR((I103-I117)/I103,"")</f>
         <v/>
       </c>
       <c r="J131" s="10">
-        <f>IFERROR((J103-J117)/J117,"")</f>
+        <f>IFERROR((J103-J117)/J103,"")</f>
         <v/>
       </c>
       <c r="K131" s="10">
-        <f>IFERROR((K103-K117)/K117,"")</f>
+        <f>IFERROR((K103-K117)/K103,"")</f>
         <v/>
       </c>
       <c r="L131" s="10">
-        <f>IFERROR((L103-L117)/L117,"")</f>
+        <f>IFERROR((L103-L117)/L103,"")</f>
         <v/>
       </c>
       <c r="M131" s="10">
-        <f>IFERROR((M103-M117)/M117,"")</f>
+        <f>IFERROR((M103-M117)/M103,"")</f>
         <v/>
       </c>
     </row>
@@ -10115,51 +10115,51 @@
         </is>
       </c>
       <c r="B132" s="10">
-        <f>IFERROR((B104-B118)/B118,"")</f>
+        <f>IFERROR((B104-B118)/B104,"")</f>
         <v/>
       </c>
       <c r="C132" s="10">
-        <f>IFERROR((C104-C118)/C118,"")</f>
+        <f>IFERROR((C104-C118)/C104,"")</f>
         <v/>
       </c>
       <c r="D132" s="10">
-        <f>IFERROR((D104-D118)/D118,"")</f>
+        <f>IFERROR((D104-D118)/D104,"")</f>
         <v/>
       </c>
       <c r="E132" s="10">
-        <f>IFERROR((E104-E118)/E118,"")</f>
+        <f>IFERROR((E104-E118)/E104,"")</f>
         <v/>
       </c>
       <c r="F132" s="10">
-        <f>IFERROR((F104-F118)/F118,"")</f>
+        <f>IFERROR((F104-F118)/F104,"")</f>
         <v/>
       </c>
       <c r="G132" s="10">
-        <f>IFERROR((G104-G118)/G118,"")</f>
+        <f>IFERROR((G104-G118)/G104,"")</f>
         <v/>
       </c>
       <c r="H132" s="10">
-        <f>IFERROR((H104-H118)/H118,"")</f>
+        <f>IFERROR((H104-H118)/H104,"")</f>
         <v/>
       </c>
       <c r="I132" s="10">
-        <f>IFERROR((I104-I118)/I118,"")</f>
+        <f>IFERROR((I104-I118)/I104,"")</f>
         <v/>
       </c>
       <c r="J132" s="10">
-        <f>IFERROR((J104-J118)/J118,"")</f>
+        <f>IFERROR((J104-J118)/J104,"")</f>
         <v/>
       </c>
       <c r="K132" s="10">
-        <f>IFERROR((K104-K118)/K118,"")</f>
+        <f>IFERROR((K104-K118)/K104,"")</f>
         <v/>
       </c>
       <c r="L132" s="10">
-        <f>IFERROR((L104-L118)/L118,"")</f>
+        <f>IFERROR((L104-L118)/L104,"")</f>
         <v/>
       </c>
       <c r="M132" s="10">
-        <f>IFERROR((M104-M118)/M118,"")</f>
+        <f>IFERROR((M104-M118)/M104,"")</f>
         <v/>
       </c>
     </row>
@@ -10170,51 +10170,51 @@
         </is>
       </c>
       <c r="B133" s="10">
-        <f>IFERROR((B105-B119)/B119,"")</f>
+        <f>IFERROR((B105-B119)/B105,"")</f>
         <v/>
       </c>
       <c r="C133" s="10">
-        <f>IFERROR((C105-C119)/C119,"")</f>
+        <f>IFERROR((C105-C119)/C105,"")</f>
         <v/>
       </c>
       <c r="D133" s="10">
-        <f>IFERROR((D105-D119)/D119,"")</f>
+        <f>IFERROR((D105-D119)/D105,"")</f>
         <v/>
       </c>
       <c r="E133" s="10">
-        <f>IFERROR((E105-E119)/E119,"")</f>
+        <f>IFERROR((E105-E119)/E105,"")</f>
         <v/>
       </c>
       <c r="F133" s="10">
-        <f>IFERROR((F105-F119)/F119,"")</f>
+        <f>IFERROR((F105-F119)/F105,"")</f>
         <v/>
       </c>
       <c r="G133" s="10">
-        <f>IFERROR((G105-G119)/G119,"")</f>
+        <f>IFERROR((G105-G119)/G105,"")</f>
         <v/>
       </c>
       <c r="H133" s="10">
-        <f>IFERROR((H105-H119)/H119,"")</f>
+        <f>IFERROR((H105-H119)/H105,"")</f>
         <v/>
       </c>
       <c r="I133" s="10">
-        <f>IFERROR((I105-I119)/I119,"")</f>
+        <f>IFERROR((I105-I119)/I105,"")</f>
         <v/>
       </c>
       <c r="J133" s="10">
-        <f>IFERROR((J105-J119)/J119,"")</f>
+        <f>IFERROR((J105-J119)/J105,"")</f>
         <v/>
       </c>
       <c r="K133" s="10">
-        <f>IFERROR((K105-K119)/K119,"")</f>
+        <f>IFERROR((K105-K119)/K105,"")</f>
         <v/>
       </c>
       <c r="L133" s="10">
-        <f>IFERROR((L105-L119)/L119,"")</f>
+        <f>IFERROR((L105-L119)/L105,"")</f>
         <v/>
       </c>
       <c r="M133" s="10">
-        <f>IFERROR((M105-M119)/M119,"")</f>
+        <f>IFERROR((M105-M119)/M105,"")</f>
         <v/>
       </c>
     </row>
@@ -10262,7 +10262,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A29"/>
+  <dimension ref="A1:A36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="130" customWidth="1" min="1" max="1"/>
@@ -10285,171 +10285,216 @@
     <row r="3">
       <c r="A3" s="12" t="inlineStr">
         <is>
-          <t>% Diff = (ours - client) / client. NOTE: this is the OPPOSITE SIGN to earlier versions of this sheet, which used (client - ours). It now matches the RCA document. A negative % means we are BELOW the client.</t>
+          <t>% Diff = (ours - client) / OURS. This matches the Cohorts Dashboard validation sheet, so the figures tie back to what people already know. A negative % means we are BELOW the client.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="12" t="inlineStr">
         <is>
-          <t>Colour scale is on the ABSOLUTE difference: GREEN within 2%, AMBER 2-5%, RED beyond 5%.</t>
+          <t>Watch the denominator when comparing against anything else. Dividing by the client instead makes every gap look bigger - Sep-25 OTP at M10 is 33% one way and 50% the other, on identical data. It is the same $320,947 gap either way.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="12" t="inlineStr">
         <is>
-          <t>% Diff cells are live formulas and calculate when opened in Excel.</t>
+          <t>Small caveat: this sheet diffs PER-CUSTOMER values, while the Cohorts Dashboard validation sheet diffs TOTAL revenue. Where the two sides have slightly different customer counts the percentages differ by up to about one point (Sep-25 OTP M10: 33.8% here, 33.1% there).</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="inlineStr"/>
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>Colour scale is on the ABSOLUTE difference: GREEN within 2%, AMBER 2-5%, RED beyond 5%.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
         <is>
-          <t>SOURCES - both tabs come from LineItemMaster, so only the logic differs between them.</t>
+          <t>% Diff cells are live formulas and calculate when opened in Excel.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Before tab: sql/10_before_logic_lim.sql - acquisition bucket for life, no Faire.</t>
-        </is>
-      </c>
+      <c r="A8" s="12" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  After tab:  sql/09_production_lim.sql   - attribution fixed, Faire included.</t>
+          <t>SOURCES - both tabs come from LineItemMaster, so only the logic differs between them.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Both were validated against the earlier OrderLinesMaster + ReturnLinesMaster build, which they reproduce to within 0.08% across all 11 cohorts and both buckets. LineItemMaster is simply those two tables combined, so this is a change of source, not of method.</t>
+          <t xml:space="preserve">  Before tab: sql/10_before_logic_lim.sql - acquisition bucket for life, no Faire.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
         <is>
+          <t xml:space="preserve">  After tab:  sql/09_production_lim.sql   - attribution fixed, Faire included.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Both were validated against the earlier OrderLinesMaster + ReturnLinesMaster build, which they reproduce to within 0.08% across all 11 cohorts and both buckets. LineItemMaster is simply those two tables combined, so this is a change of source, not of method.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
           <t xml:space="preserve">  Cross-check that holds in the data: the two tabs have IDENTICAL customer counts before 2026-02, and from 2026-02 the After tab is higher by exactly the Faire retailers - +17 Feb, +33 Mar, +25 Apr, +37 May, +33 Jun, +46 Jul. Subscription M0 is identical on both tabs in every cohort, because every Faire order is OTP.</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="13" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="13" t="inlineStr">
         <is>
           <t>METHOD</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="12" t="inlineStr">
-        <is>
-          <t>LTR = gross sales - item discounts + shipping - shipping tax, net of returns. Shopify only; test orders and gift cards excluded; founding-order revenue bucket "TT New" (TikTok) excluded.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="12" t="inlineStr">
-        <is>
-          <t>The $0 founding-order rule removes a 2026-07-09 free-product promotion (936 customers in July).</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
         <is>
-          <t>The Customers column differs between tabs: the After tab adds Faire retailers, who are excluded from the presentation layer by a channel filter and so appear in neither table.</t>
+          <t>LTR = gross sales - item discounts + shipping - shipping tax, net of returns. Shopify only; test orders and gift cards excluded; founding-order revenue bucket "TT New" (TikTok) excluded.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>October 2026 is a partial month and is excluded, so the last month shown varies by cohort.</t>
+          <t>The $0 founding-order rule removes a 2026-07-09 free-product promotion (936 customers in July).</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
         <is>
+          <t>The Customers column differs between tabs: the After tab adds Faire retailers, who are excluded from the presentation layer by a channel filter and so appear in neither table.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>October 2026 is a partial month and is excluded, so the last month shown varies by cohort.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="12" t="inlineStr">
+        <is>
           <t>Client rows are from Cohorts_Dashboard_Complete_Validation_Sheet "Month View", identical on both tabs.</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="12" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="13" t="inlineStr">
-        <is>
-          <t>RESULT</t>
-        </is>
-      </c>
-    </row>
     <row r="21">
-      <c r="A21" s="12" t="inlineStr">
-        <is>
-          <t>Before: 102 of 198 cells are more than 5% out, worst 51.1%, mean 9.7%.</t>
-        </is>
-      </c>
+      <c r="A21" s="12" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="12" t="inlineStr">
-        <is>
-          <t>After: NO cell above 5%, worst 3.6%, mean 0.94% across all 198 cells (1.11% if measured only at each cohort-s latest month, which is the figure quoted in the RCA document).</t>
+      <c r="A22" s="13" t="inlineStr">
+        <is>
+          <t>CHECKED AGAINST THE LIVE DASHBOARD</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>The attribution rule was chosen by scoring four variants across all eleven cohorts, not on March alone.</t>
+          <t>The Before tab was compared cell by cell against the Cohorts Dashboard block in Cohorts_Dashboard_Complete_Validation_Sheet (OTP and Subscription blocks, overlapping months): 132 cells, mean difference 0.16%, worst 0.48%, none above 1%. The Before tab does reproduce production.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="12" t="inlineStr"/>
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>One deliberate exception: July OTP holds 6,413 customers here against 7,352 on the dashboard. That is the $0 giveaway rule, which production does not apply.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="13" t="inlineStr">
-        <is>
-          <t>OPEN</t>
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>That dashboard extract stops at July 2026; these runs go to September 2026, so the last month or two of each cohort has no dashboard counterpart to compare against.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="12" t="inlineStr">
-        <is>
-          <t>Roughly 115 customers across the non-July cohorts are classified OTP by us and Subscription by the client. 0.10% of base. No exclusion rule can fix a classification difference.</t>
-        </is>
-      </c>
+      <c r="A26" s="12" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="12" t="inlineStr">
-        <is>
-          <t>465 of the 936 July customers removed have a second order. Believed to be a second $0 promotional item rather than a real purchase. Unconfirmed.</t>
+      <c r="A27" s="13" t="inlineStr">
+        <is>
+          <t>RESULT</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="12" t="inlineStr">
         <is>
-          <t>LineItemMaster currently adds refunded shipping on return rows instead of subtracting it - an upstream sign error raised with the DE team. The After tab is built with that shipping ignored, which matches the OrderLinesMaster build. When the fix lands, expect March M4 to move about -425 (OTP) and -1,046 (Subscription).</t>
+          <t>Before: 102 of 198 cells are more than 5% out, worst 51.1%, mean 9.7%.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>After: NO cell above 5%, worst 3.6%, mean 0.94% across all 198 cells (1.11% if measured only at each cohort-s latest month, which is the figure quoted in the RCA document).</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>The attribution rule was chosen by scoring four variants across all eleven cohorts, not on March alone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="12" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="13" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t>Roughly 115 customers across the non-July cohorts are classified OTP by us and Subscription by the client. 0.10% of base. No exclusion rule can fix a classification difference.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>465 of the 936 July customers removed have a second order. Believed to be a second $0 promotional item rather than a real purchase. Unconfirmed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t>LineItemMaster currently adds refunded shipping on return rows instead of subtracting it - an upstream sign error raised with the DE team. The After tab is built with that shipping ignored, which matches the OrderLinesMaster build. When the fix lands, expect March M4 to move about -425 (OTP) and -1,046 (Subscription).</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="12" t="inlineStr">
         <is>
           <t>Nobody has confirmed which model the live dashboard reads, and the published figures these were originally checked against came from our own brief, not a dashboard read.</t>
         </is>
